--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -27587,7 +27587,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Newcastle United;Burnley</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -29261,7 +29261,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Aston Villa;Leicester City</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -30021,7 +30021,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Arsenal;Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Newcastle United;Leicester City</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -1155,14 +1155,10 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>Leeds United;Everton;Newcastle United;Bolton Wanderers</t>
@@ -7673,14 +7669,10 @@
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr"/>
       <c r="AE80" t="inlineStr">
         <is>
           <t>Aston Villa;Middlesbrough</t>
@@ -28889,14 +28881,10 @@
       <c r="AB342" t="inlineStr"/>
       <c r="AC342" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD342" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD342" t="inlineStr"/>
       <c r="AE342" t="inlineStr">
         <is>
           <t>Bolton Wanderers</t>
@@ -36039,14 +36027,10 @@
       <c r="AB436" t="inlineStr"/>
       <c r="AC436" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD436" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD436" t="inlineStr"/>
       <c r="AE436" t="inlineStr">
         <is>
           <t>Nottingham Forest;Sheffield Wednesday;Charlton Athletic;Ipswich Town</t>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="S79" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         </is>
       </c>
       <c r="S102" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         </is>
       </c>
       <c r="S107" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         </is>
       </c>
       <c r="S118" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         </is>
       </c>
       <c r="S168" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         </is>
       </c>
       <c r="S183" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         </is>
       </c>
       <c r="S211" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         </is>
       </c>
       <c r="S300" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="T300" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         </is>
       </c>
       <c r="S337" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         </is>
       </c>
       <c r="S380" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="T380" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         </is>
       </c>
       <c r="S383" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="T383" t="inlineStr">
         <is>
@@ -32436,7 +32436,7 @@
         </is>
       </c>
       <c r="S387" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="T387" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         </is>
       </c>
       <c r="S390" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T390" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         </is>
       </c>
       <c r="S408" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="T408" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         </is>
       </c>
       <c r="S422" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="T422" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="S432" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T432" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         </is>
       </c>
       <c r="S522" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T522" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         </is>
       </c>
       <c r="S553" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="T553" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         </is>
       </c>
       <c r="S557" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T557" t="inlineStr">
         <is>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -26355,10 +26355,14 @@
       </c>
       <c r="AC309" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD309" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="AE309" t="inlineStr">
         <is>
           <t>Aston Villa;Everton</t>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -22194,11 +22194,11 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>243</v>
+        <v>8454</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>David Batty</t>
+          <t>Callum Wilson</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -22208,18 +22208,20 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>1968/12/2</t>
+          <t>1992/2/27</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
+      <c r="I258" t="n">
+        <v>93</v>
+      </c>
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
@@ -22243,18 +22245,22 @@
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>Leeds United;Blackburn Rovers;Newcastle United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
         <is>
-          <t>大卫·巴蒂</t>
+          <t>卡勒姆·威尔逊</t>
         </is>
       </c>
     </row>
@@ -22326,11 +22332,11 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>2274</v>
+        <v>243</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>David Batty</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -22345,7 +22351,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1987/7/14</t>
+          <t>1968/12/2</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -22371,7 +22377,7 @@
       <c r="Z260" t="inlineStr"/>
       <c r="AA260" t="inlineStr"/>
       <c r="AB260" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AC260" t="inlineStr">
         <is>
@@ -22381,22 +22387,22 @@
       <c r="AD260" t="inlineStr"/>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>Middlesbrough;Manchester City;Sunderland</t>
+          <t>Leeds United;Blackburn Rovers;Newcastle United</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
         <is>
-          <t>亚当·约翰逊</t>
+          <t>大卫·巴蒂</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1982</v>
+        <v>1881</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Kieran Richardson</t>
+          <t>Tony Hibbert</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -22411,7 +22417,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>1984/10/21</t>
+          <t>1981/2/20</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -22425,15 +22431,37 @@
       <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr"/>
       <c r="P261" t="inlineStr"/>
-      <c r="Q261" t="inlineStr"/>
-      <c r="R261" t="inlineStr"/>
-      <c r="S261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="R261" t="n">
+        <v>265</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T261" t="inlineStr"/>
-      <c r="U261" t="inlineStr"/>
-      <c r="V261" t="inlineStr"/>
+      <c r="U261" t="n">
+        <v>0</v>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W261" t="inlineStr"/>
-      <c r="X261" t="inlineStr"/>
-      <c r="Y261" t="inlineStr"/>
+      <c r="X261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z261" t="inlineStr"/>
       <c r="AA261" t="inlineStr"/>
       <c r="AB261" t="n">
@@ -22447,22 +22475,22 @@
       <c r="AD261" t="inlineStr"/>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>Manchester United;West Bromwich Albion;Sunderland;Fulham;Aston Villa</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
         <is>
-          <t>基兰·理查德森</t>
+          <t>托尼·希伯特</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>8454</v>
+        <v>1309</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Callum Wilson</t>
+          <t>Darius Vassell</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -22477,15 +22505,13 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>1992/2/27</t>
+          <t>1980/6/13</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
-      <c r="I262" t="n">
-        <v>93</v>
-      </c>
+      <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr"/>
@@ -22509,47 +22535,43 @@
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD262" t="inlineStr">
-        <is>
-          <t>West Ham United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr"/>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
         <is>
-          <t>卡勒姆·威尔逊</t>
+          <t>达里乌斯·瓦塞尔</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1309</v>
+        <v>3653</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Darius Vassell</t>
+          <t>Vincent Kompany</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>1980/6/13</t>
+          <t>1986/4/10</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -22558,20 +22580,60 @@
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
-      <c r="O263" t="inlineStr"/>
-      <c r="P263" t="inlineStr"/>
-      <c r="Q263" t="inlineStr"/>
-      <c r="R263" t="inlineStr"/>
-      <c r="S263" t="inlineStr"/>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>4</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>2011–12, 2013–14, 2017–18, 2018–19</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="R263" t="n">
+        <v>265</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T263" t="inlineStr"/>
-      <c r="U263" t="inlineStr"/>
-      <c r="V263" t="inlineStr"/>
+      <c r="U263" t="n">
+        <v>0</v>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W263" t="inlineStr"/>
-      <c r="X263" t="inlineStr"/>
-      <c r="Y263" t="inlineStr"/>
+      <c r="X263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z263" t="inlineStr"/>
       <c r="AA263" t="inlineStr"/>
       <c r="AB263" t="n">
@@ -22585,22 +22647,22 @@
       <c r="AD263" t="inlineStr"/>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
         <is>
-          <t>达里乌斯·瓦塞尔</t>
+          <t>文森特·孔帕尼</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>331</v>
+        <v>1982</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>David Beckham</t>
+          <t>Kieran Richardson</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -22610,12 +22672,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>1975/5/2</t>
+          <t>1984/10/21</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -22623,57 +22685,21 @@
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>Premier League 10 Seasons Awards</t>
-        </is>
-      </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
       <c r="M264" t="inlineStr"/>
-      <c r="N264" t="n">
-        <v>6</v>
-      </c>
-      <c r="O264" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="P264" t="inlineStr">
-        <is>
-          <t>1995–96, 1996–97, 1998–99, 1999–2000, 2000–01, 2002–03</t>
-        </is>
-      </c>
-      <c r="Q264" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="R264" t="n">
-        <v>265</v>
-      </c>
-      <c r="S264" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
+      <c r="R264" t="inlineStr"/>
+      <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr"/>
-      <c r="U264" t="n">
-        <v>0</v>
-      </c>
-      <c r="V264" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U264" t="inlineStr"/>
+      <c r="V264" t="inlineStr"/>
       <c r="W264" t="inlineStr"/>
-      <c r="X264" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y264" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X264" t="inlineStr"/>
+      <c r="Y264" t="inlineStr"/>
       <c r="Z264" t="inlineStr"/>
       <c r="AA264" t="inlineStr"/>
       <c r="AB264" t="n">
@@ -22687,22 +22713,22 @@
       <c r="AD264" t="inlineStr"/>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Manchester United;West Bromwich Albion;Sunderland;Fulham;Aston Villa</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
         <is>
-          <t>大卫·贝克汉姆</t>
+          <t>基兰·理查德森</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1881</v>
+        <v>331</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Tony Hibbert</t>
+          <t>David Beckham</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -22712,12 +22738,12 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>1981/2/20</t>
+          <t>1975/5/2</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -22725,15 +22751,29 @@
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Premier League 10 Seasons Awards</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr"/>
       <c r="M265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
-      <c r="O265" t="inlineStr"/>
-      <c r="P265" t="inlineStr"/>
+      <c r="N265" t="n">
+        <v>6</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>1995–96, 1996–97, 1998–99, 1999–2000, 2000–01, 2002–03</t>
+        </is>
+      </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="R265" t="n">
@@ -22775,37 +22815,37 @@
       <c r="AD265" t="inlineStr"/>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
         <is>
-          <t>托尼·希伯特</t>
+          <t>大卫·贝克汉姆</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>3653</v>
+        <v>2274</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Vincent Kompany</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>1986/4/10</t>
+          <t>1987/7/14</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -22814,60 +22854,20 @@
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="N266" t="n">
-        <v>4</v>
-      </c>
-      <c r="O266" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="P266" t="inlineStr">
-        <is>
-          <t>2011–12, 2013–14, 2017–18, 2018–19</t>
-        </is>
-      </c>
-      <c r="Q266" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="R266" t="n">
-        <v>265</v>
-      </c>
-      <c r="S266" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
+      <c r="R266" t="inlineStr"/>
+      <c r="S266" t="inlineStr"/>
       <c r="T266" t="inlineStr"/>
-      <c r="U266" t="n">
-        <v>0</v>
-      </c>
-      <c r="V266" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U266" t="inlineStr"/>
+      <c r="V266" t="inlineStr"/>
       <c r="W266" t="inlineStr"/>
-      <c r="X266" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y266" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X266" t="inlineStr"/>
+      <c r="Y266" t="inlineStr"/>
       <c r="Z266" t="inlineStr"/>
       <c r="AA266" t="inlineStr"/>
       <c r="AB266" t="n">
@@ -22881,12 +22881,12 @@
       <c r="AD266" t="inlineStr"/>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Middlesbrough;Manchester City;Sunderland</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
         <is>
-          <t>文森特·孔帕尼</t>
+          <t>亚当·约翰逊</t>
         </is>
       </c>
     </row>
@@ -30416,16 +30416,16 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>2047</v>
+        <v>8868</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Jonathan Walters</t>
+          <t>Jarrod Bowen</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -30435,7 +30435,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>1983/9/20</t>
+          <t>1996/12/20</t>
         </is>
       </c>
       <c r="F362" t="inlineStr"/>
@@ -30451,15 +30451,15 @@
       <c r="P362" t="inlineStr"/>
       <c r="Q362" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="R362" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="T362" t="inlineStr"/>
@@ -30487,33 +30487,37 @@
       </c>
       <c r="AC362" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD362" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD362" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>Burnley;Stoke City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
         <is>
-          <t>乔纳森·沃尔特斯</t>
+          <t>贾罗德·鲍文</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>8868</v>
+        <v>2047</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Jarrod Bowen</t>
+          <t>Jonathan Walters</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -30523,7 +30527,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>1996/12/20</t>
+          <t>1983/9/20</t>
         </is>
       </c>
       <c r="F363" t="inlineStr"/>
@@ -30539,15 +30543,15 @@
       <c r="P363" t="inlineStr"/>
       <c r="Q363" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="R363" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="T363" t="inlineStr"/>
@@ -30571,26 +30575,22 @@
       <c r="Z363" t="inlineStr"/>
       <c r="AA363" t="inlineStr"/>
       <c r="AB363" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AC363" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD363" t="inlineStr">
-        <is>
-          <t>West Ham United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD363" t="inlineStr"/>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley;Stoke City</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
         <is>
-          <t>贾罗德·鲍文</t>
+          <t>乔纳森·沃尔特斯</t>
         </is>
       </c>
     </row>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF463"/>
+  <dimension ref="A1:AF464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="R100" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="R105" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="R111" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="R166" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         </is>
       </c>
       <c r="R208" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -21195,10 +21195,14 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
       <c r="AE245" t="inlineStr">
         <is>
           <t>Tottenham Hotspur;Everton</t>
@@ -23445,37 +23449,15 @@
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr"/>
-      <c r="Q273" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="R273" t="n">
-        <v>262</v>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q273" t="inlineStr"/>
+      <c r="R273" t="inlineStr"/>
+      <c r="S273" t="inlineStr"/>
       <c r="T273" t="inlineStr"/>
-      <c r="U273" t="n">
-        <v>0</v>
-      </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U273" t="inlineStr"/>
+      <c r="V273" t="inlineStr"/>
       <c r="W273" t="inlineStr"/>
-      <c r="X273" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y273" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X273" t="inlineStr"/>
+      <c r="Y273" t="inlineStr"/>
       <c r="Z273" t="inlineStr"/>
       <c r="AA273" t="inlineStr"/>
       <c r="AB273" t="n">
@@ -25087,7 +25069,7 @@
         </is>
       </c>
       <c r="R293" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="S293" t="inlineStr">
         <is>
@@ -27977,7 +27959,7 @@
         </is>
       </c>
       <c r="R330" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="S330" t="inlineStr">
         <is>
@@ -30301,7 +30283,7 @@
         </is>
       </c>
       <c r="R360" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
@@ -31453,7 +31435,7 @@
         </is>
       </c>
       <c r="R375" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S375" t="inlineStr">
         <is>
@@ -31897,7 +31879,7 @@
         </is>
       </c>
       <c r="R380" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="S380" t="inlineStr">
         <is>
@@ -32249,7 +32231,7 @@
         </is>
       </c>
       <c r="R384" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S384" t="inlineStr">
         <is>
@@ -32339,7 +32321,7 @@
         </is>
       </c>
       <c r="R385" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="S385" t="inlineStr">
         <is>
@@ -32515,7 +32497,7 @@
         </is>
       </c>
       <c r="R387" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="S387" t="inlineStr">
         <is>
@@ -33077,7 +33059,7 @@
         </is>
       </c>
       <c r="R393" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="S393" t="inlineStr">
         <is>
@@ -33341,7 +33323,7 @@
         </is>
       </c>
       <c r="R396" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="S396" t="inlineStr">
         <is>
@@ -35075,7 +35057,7 @@
         </is>
       </c>
       <c r="R416" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="S416" t="inlineStr">
         <is>
@@ -35781,7 +35763,7 @@
         </is>
       </c>
       <c r="R424" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -36137,7 +36119,7 @@
         </is>
       </c>
       <c r="R428" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
@@ -36403,7 +36385,7 @@
         </is>
       </c>
       <c r="R431" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="S431" t="inlineStr">
         <is>
@@ -38914,6 +38896,84 @@
         </is>
       </c>
     </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>48285</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Aaron Ramsey</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>2003/1/21</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr"/>
+      <c r="N464" t="inlineStr"/>
+      <c r="O464" t="inlineStr"/>
+      <c r="P464" t="inlineStr"/>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="R464" t="n">
+        <v>262</v>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr"/>
+      <c r="U464" t="n">
+        <v>0</v>
+      </c>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W464" t="inlineStr"/>
+      <c r="X464" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y464" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z464" t="inlineStr"/>
+      <c r="AA464" t="inlineStr"/>
+      <c r="AB464" t="inlineStr"/>
+      <c r="AC464" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD464" t="inlineStr"/>
+      <c r="AE464" t="inlineStr"/>
+      <c r="AF464" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -15884,11 +15884,11 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1890</v>
+        <v>4608</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Titus Bramble</t>
+          <t>Luke Shaw</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1981/7/31</t>
+          <t>1995/7/12</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -15917,15 +15917,37 @@
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="R178" t="n">
+        <v>232</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="T178" t="inlineStr"/>
-      <c r="U178" t="inlineStr"/>
-      <c r="V178" t="inlineStr"/>
+      <c r="U178" t="n">
+        <v>0</v>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W178" t="inlineStr"/>
-      <c r="X178" t="inlineStr"/>
-      <c r="Y178" t="inlineStr"/>
+      <c r="X178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z178" t="inlineStr"/>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="n">
@@ -15933,43 +15955,47 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Manchester United;Southampton</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
         <is>
-          <t>泰图斯·布兰布尔</t>
+          <t>卢克·肖</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>5861</v>
+        <v>1890</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Cheikhou Kouyaté</t>
+          <t>Titus Bramble</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1989/12/21</t>
+          <t>1981/7/31</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -15995,47 +16021,47 @@
       <c r="Z179" t="inlineStr"/>
       <c r="AA179" t="inlineStr"/>
       <c r="AB179" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr"/>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>West Ham United;Crystal Palace;Nottingham Forest</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
         <is>
-          <t>谢库·库亚特</t>
+          <t>泰图斯·布兰布尔</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>4608</v>
+        <v>5861</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Luke Shaw</t>
+          <t>Cheikhou Kouyaté</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1995/7/12</t>
+          <t>1989/12/21</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -16049,37 +16075,15 @@
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="R180" t="n">
-        <v>231</v>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr"/>
-      <c r="U180" t="n">
-        <v>0</v>
-      </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr"/>
       <c r="W180" t="inlineStr"/>
-      <c r="X180" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y180" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X180" t="inlineStr"/>
+      <c r="Y180" t="inlineStr"/>
       <c r="Z180" t="inlineStr"/>
       <c r="AA180" t="inlineStr"/>
       <c r="AB180" t="n">
@@ -16090,19 +16094,15 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AD180" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
+      <c r="AD180" t="inlineStr"/>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>Manchester United;Southampton</t>
+          <t>West Ham United;Crystal Palace;Nottingham Forest</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
         <is>
-          <t>卢克·肖</t>
+          <t>谢库·库亚特</t>
         </is>
       </c>
     </row>
@@ -17100,11 +17100,11 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2574</v>
+        <v>9566</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Joleon Lescott</t>
+          <t>Harry Maguire</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -17119,7 +17119,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>1982/8/16</t>
+          <t>1993/3/5</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -17155,22 +17155,22 @@
       <c r="AD194" t="inlineStr"/>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>Everton;Manchester City;West Bromwich Albion;Aston Villa;Sunderland</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
         <is>
-          <t>乔莱昂·莱斯科特</t>
+          <t>哈里·马奎尔</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>9566</v>
+        <v>2574</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Harry Maguire</t>
+          <t>Joleon Lescott</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -17185,7 +17185,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>1993/3/5</t>
+          <t>1982/8/16</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -17211,7 +17211,7 @@
       <c r="Z195" t="inlineStr"/>
       <c r="AA195" t="inlineStr"/>
       <c r="AB195" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
@@ -17221,22 +17221,22 @@
       <c r="AD195" t="inlineStr"/>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Everton;Manchester City;West Bromwich Albion;Aston Villa;Sunderland</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
         <is>
-          <t>哈里·马奎尔</t>
+          <t>乔莱昂·莱斯科特</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>488</v>
+        <v>4489</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Brian Deane</t>
+          <t>Ashley Westwood</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -17246,12 +17246,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1968/2/7</t>
+          <t>1990/4/1</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -17281,18 +17281,22 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Aston Villa;Burnley</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
         <is>
-          <t>布赖恩·迪恩</t>
+          <t>阿什利·韦斯特伍德</t>
         </is>
       </c>
     </row>
@@ -17366,11 +17370,11 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>4489</v>
+        <v>488</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ashley Westwood</t>
+          <t>Brian Deane</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -17380,12 +17384,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1990/4/1</t>
+          <t>1968/2/7</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -17415,22 +17419,18 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>Charlotte FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr"/>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>Aston Villa;Burnley</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
         <is>
-          <t>阿什利·韦斯特伍德</t>
+          <t>布赖恩·迪恩</t>
         </is>
       </c>
     </row>
@@ -32141,7 +32141,7 @@
         </is>
       </c>
       <c r="R383" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="S383" t="inlineStr">
         <is>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -3094,71 +3094,69 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2651</v>
+        <v>3955</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Petr Cech</t>
+          <t>Kyle Walker</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1982/5/20</t>
+          <t>1990/5/28</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>16.0, 17.0</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
-        <v>207</v>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2004–05, 2005–06, 2009–10, 2014–15</t>
+          <t>2017–18, 2018–19, 2020–21, 2021–22, 2022–23, 2023–24</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>333</v>
+        <v>212</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3181,86 +3179,92 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Burnley FC</t>
+        </is>
+      </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>Chelsea;Arsenal</t>
+          <t>Tottenham Hotspur;Aston Villa;Manchester City;Burnley</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>彼得·切赫</t>
+          <t>凯尔·沃克</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3955</v>
+        <v>2651</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kyle Walker</t>
+          <t>Petr Cech</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1990/5/28</t>
+          <t>1982/5/20</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>16.0, 17.0</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>207</v>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2017–18, 2018–19, 2020–21, 2021–22, 2022–23, 2023–24</t>
+          <t>2004–05, 2005–06, 2009–10, 2014–15</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Tottenham Hotspur</t>
-        </is>
-      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3279,26 +3283,22 @@
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>Burnley FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Aston Villa;Manchester City;Burnley</t>
+          <t>Chelsea;Arsenal</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>凯尔·沃克</t>
+          <t>彼得·切赫</t>
         </is>
       </c>
     </row>
@@ -3776,11 +3776,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>576</v>
+        <v>4617</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Teddy Sheringham</t>
+          <t>James Ward-Prowse</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3790,52 +3790,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1966/4/2</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
+          <t>1994/11/1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="n">
-        <v>146</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>3</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>1998–99, 1999–2000, 2000–01</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>236</v>
+        <v>343</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3860,43 +3840,39 @@
           <t>no</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Burnley FC</t>
+        </is>
+      </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Manchester United;Portsmouth;West Ham United</t>
+          <t>Southampton;West Ham United;Burnley</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>泰迪·谢林汉姆</t>
+          <t>詹姆斯·沃德-普劳斯</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4617</v>
+        <v>576</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>James Ward-Prowse</t>
+          <t>Teddy Sheringham</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3906,32 +3882,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1994/11/1</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+          <t>1966/4/2</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>146</v>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>3</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>1998–99, 1999–2000, 2000–01</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>343</v>
+        <v>236</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3956,29 +3952,33 @@
           <t>no</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="AB37" t="n">
         <v>418</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>Burnley FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>Southampton;West Ham United;Burnley</t>
+          <t>Tottenham Hotspur;Manchester United;Portsmouth;West Ham United</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>詹姆斯·沃德-普劳斯</t>
+          <t>泰迪·谢林汉姆</t>
         </is>
       </c>
     </row>
@@ -4972,11 +4972,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2839</v>
+        <v>3452</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Theo Walcott</t>
+          <t>Danny Welbeck</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4991,13 +4991,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1989/3/16</t>
+          <t>1990/11/26</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>89</v>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -5005,37 +5007,15 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="R49" t="n">
-        <v>270</v>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="n">
@@ -5043,28 +5023,32 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>Arsenal;Everton;Southampton</t>
+          <t>Manchester United;Arsenal;Watford;Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>西奥·沃尔科特</t>
+          <t>丹尼·维尔贝克</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4316</v>
+        <v>2839</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Raheem Sterling</t>
+          <t>Theo Walcott</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5079,39 +5063,27 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1994/12/8</t>
+          <t>1989/3/16</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="n">
-        <v>123</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="n">
-        <v>4</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>2017–18, 2018–19, 2020–21, 2021–22</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5139,36 +5111,32 @@
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>Feyenoord Rotterdam</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>Liverpool;Manchester City;Chelsea;Arsenal</t>
+          <t>Arsenal;Everton;Southampton</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>拉希姆·斯特林</t>
+          <t>西奥·沃尔科特</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3452</v>
+        <v>4316</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Danny Welbeck</t>
+          <t>Raheem Sterling</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5183,31 +5151,63 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1990/11/26</t>
+          <t>1994/12/8</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>4</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2017–18, 2018–19, 2020–21, 2021–22</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>225</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="n">
@@ -5220,17 +5220,17 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Feyenoord Rotterdam</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>Manchester United;Arsenal;Watford;Brighton &amp; Hove Albion</t>
+          <t>Liverpool;Manchester City;Chelsea;Arsenal</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>丹尼·维尔贝克</t>
+          <t>拉希姆·斯特林</t>
         </is>
       </c>
     </row>
@@ -12878,16 +12878,16 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>4845</v>
+        <v>15202</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Christian Eriksen</t>
+          <t>Declan Rice</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>1992/2/14</t>
+          <t>1999/1/14</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -12913,11 +12913,11 @@
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="R142" t="n">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
       <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
@@ -12954,17 +12954,17 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Arsenal FC</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Brentford;Manchester United</t>
+          <t>Arsenal;West Ham United</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>克里斯蒂安·埃里克森</t>
+          <t>德克兰·赖斯</t>
         </is>
       </c>
     </row>
@@ -13058,11 +13058,11 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>307</v>
+        <v>4845</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Peter Schmeichel</t>
+          <t>Christian Eriksen</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -13072,56 +13072,32 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>1963/11/18</t>
+          <t>1992/2/14</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="n">
-        <v>129</v>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Premier League 10 Seasons Awards</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="N144" t="n">
-        <v>5</v>
-      </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>1992–93, 1993–94, 1995–96, 1996–97, 1998–99</t>
-        </is>
-      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="R144" t="n">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -13153,63 +13129,91 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>VfL Wolfsburg</t>
+        </is>
+      </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>Manchester United;Aston Villa;Manchester City</t>
+          <t>Tottenham Hotspur;Brentford;Manchester United</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>彼得·舒梅切尔</t>
+          <t>克里斯蒂安·埃里克森</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>15202</v>
+        <v>307</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Declan Rice</t>
+          <t>Peter Schmeichel</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1999/1/14</t>
+          <t>1963/11/18</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>129</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Premier League 10 Seasons Awards</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>5</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>1992–93, 1993–94, 1995–96, 1996–97, 1998–99</t>
+        </is>
+      </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="R145" t="n">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -13241,22 +13245,18 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>Arsenal FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr"/>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>Arsenal;West Ham United</t>
+          <t>Manchester United;Aston Villa;Manchester City</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>德克兰·赖斯</t>
+          <t>彼得·舒梅切尔</t>
         </is>
       </c>
     </row>
@@ -15440,26 +15440,26 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>4549</v>
+        <v>8163</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Moussa Sissoko</t>
+          <t>Lewis Dunk</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1989/8/16</t>
+          <t>1991/11/21</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -15473,44 +15473,70 @@
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
-      <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="R172" t="n">
+        <v>296</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="T172" t="inlineStr"/>
-      <c r="U172" t="inlineStr"/>
-      <c r="V172" t="inlineStr"/>
+      <c r="U172" t="n">
+        <v>0</v>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W172" t="inlineStr"/>
-      <c r="X172" t="inlineStr"/>
-      <c r="Y172" t="inlineStr"/>
+      <c r="X172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z172" t="inlineStr"/>
       <c r="AA172" t="inlineStr"/>
       <c r="AB172" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>Newcastle United;Tottenham Hotspur;Watford</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
         <is>
-          <t>穆萨·西索科</t>
+          <t>路易斯·邓克</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>8163</v>
+        <v>262</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Lewis Dunk</t>
+          <t>Jamie Redknapp</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -15520,12 +15546,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1991/11/21</t>
+          <t>1973/6/25</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -15541,15 +15567,15 @@
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="R173" t="n">
-        <v>295</v>
+        <v>231</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="T173" t="inlineStr"/>
@@ -15577,22 +15603,18 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD173" t="inlineStr">
-        <is>
-          <t>Brighton &amp; Hove Albion</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr"/>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
         <is>
-          <t>路易斯·邓克</t>
+          <t>杰米·雷德克纳普</t>
         </is>
       </c>
     </row>
@@ -15664,16 +15686,16 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>262</v>
+        <v>4549</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jamie Redknapp</t>
+          <t>Moussa Sissoko</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -15683,7 +15705,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1973/6/25</t>
+          <t>1989/8/16</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -15697,37 +15719,15 @@
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="R175" t="n">
-        <v>231</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
+      <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr"/>
-      <c r="U175" t="n">
-        <v>0</v>
-      </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="inlineStr"/>
       <c r="W175" t="inlineStr"/>
-      <c r="X175" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X175" t="inlineStr"/>
+      <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="inlineStr"/>
       <c r="AA175" t="inlineStr"/>
       <c r="AB175" t="n">
@@ -15741,12 +15741,12 @@
       <c r="AD175" t="inlineStr"/>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Newcastle United;Tottenham Hotspur;Watford</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
         <is>
-          <t>杰米·雷德克纳普</t>
+          <t>穆萨·西索科</t>
         </is>
       </c>
     </row>
@@ -21146,16 +21146,16 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>24630</v>
+        <v>9576</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Richarlison</t>
+          <t>Dominic Calvert-Lewin</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -21165,7 +21165,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>1997/5/10</t>
+          <t>1997/3/16</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -21179,15 +21179,37 @@
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
-      <c r="R245" t="inlineStr"/>
-      <c r="S245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="R245" t="n">
+        <v>239</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T245" t="inlineStr"/>
-      <c r="U245" t="inlineStr"/>
-      <c r="V245" t="inlineStr"/>
+      <c r="U245" t="n">
+        <v>0</v>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W245" t="inlineStr"/>
-      <c r="X245" t="inlineStr"/>
-      <c r="Y245" t="inlineStr"/>
+      <c r="X245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z245" t="inlineStr"/>
       <c r="AA245" t="inlineStr"/>
       <c r="AB245" t="n">
@@ -21200,17 +21222,17 @@
       </c>
       <c r="AD245" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Everton</t>
+          <t>Leeds United;Everton</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
         <is>
-          <t>理查利森</t>
+          <t>多米尼克·卡尔弗特-卢因</t>
         </is>
       </c>
     </row>
@@ -21282,34 +21304,32 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>533</v>
+        <v>24630</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Matthew Le Tissier</t>
+          <t>Richarlison</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>1968/10/14</t>
+          <t>1997/5/10</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
-      <c r="I247" t="n">
-        <v>101</v>
-      </c>
+      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
@@ -21317,71 +21337,53 @@
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="inlineStr"/>
-      <c r="Q247" t="inlineStr">
-        <is>
-          <t>Southampton</t>
-        </is>
-      </c>
-      <c r="R247" t="n">
-        <v>270</v>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr"/>
+      <c r="S247" t="inlineStr"/>
       <c r="T247" t="inlineStr"/>
-      <c r="U247" t="n">
-        <v>0</v>
-      </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U247" t="inlineStr"/>
+      <c r="V247" t="inlineStr"/>
       <c r="W247" t="inlineStr"/>
-      <c r="X247" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X247" t="inlineStr"/>
+      <c r="Y247" t="inlineStr"/>
       <c r="Z247" t="inlineStr"/>
       <c r="AA247" t="inlineStr"/>
       <c r="AB247" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD247" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Tottenham Hotspur;Everton</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
         <is>
-          <t>马修·勒蒂西耶</t>
+          <t>理查利森</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>9576</v>
+        <v>4979</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Dominic Calvert-Lewin</t>
+          <t>Adama Traoré</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -21391,7 +21393,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>1997/3/16</t>
+          <t>1996/1/25</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -21405,41 +21407,19 @@
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="inlineStr"/>
-      <c r="Q248" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="R248" t="n">
-        <v>239</v>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q248" t="inlineStr"/>
+      <c r="R248" t="inlineStr"/>
+      <c r="S248" t="inlineStr"/>
       <c r="T248" t="inlineStr"/>
-      <c r="U248" t="n">
-        <v>0</v>
-      </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U248" t="inlineStr"/>
+      <c r="V248" t="inlineStr"/>
       <c r="W248" t="inlineStr"/>
-      <c r="X248" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X248" t="inlineStr"/>
+      <c r="Y248" t="inlineStr"/>
       <c r="Z248" t="inlineStr"/>
       <c r="AA248" t="inlineStr"/>
       <c r="AB248" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AC248" t="inlineStr">
         <is>
@@ -21448,48 +21428,50 @@
       </c>
       <c r="AD248" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>Leeds United;Everton</t>
+          <t>West Ham United;Fulham</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
         <is>
-          <t>多米尼克·卡尔弗特-卢因</t>
+          <t>阿达马·特拉奥雷</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>4979</v>
+        <v>533</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Adama Traoré</t>
+          <t>Matthew Le Tissier</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>1996/1/25</t>
+          <t>1968/10/14</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
+      <c r="I249" t="n">
+        <v>101</v>
+      </c>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr"/>
@@ -21497,15 +21479,37 @@
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
       <c r="P249" t="inlineStr"/>
-      <c r="Q249" t="inlineStr"/>
-      <c r="R249" t="inlineStr"/>
-      <c r="S249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="R249" t="n">
+        <v>270</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T249" t="inlineStr"/>
-      <c r="U249" t="inlineStr"/>
-      <c r="V249" t="inlineStr"/>
+      <c r="U249" t="n">
+        <v>0</v>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W249" t="inlineStr"/>
-      <c r="X249" t="inlineStr"/>
-      <c r="Y249" t="inlineStr"/>
+      <c r="X249" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z249" t="inlineStr"/>
       <c r="AA249" t="inlineStr"/>
       <c r="AB249" t="n">
@@ -21513,22 +21517,18 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD249" t="inlineStr">
-        <is>
-          <t>West Ham United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr"/>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>West Ham United;Fulham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
         <is>
-          <t>阿达马·特拉奥雷</t>
+          <t>马修·勒蒂西耶</t>
         </is>
       </c>
     </row>
@@ -22091,7 +22091,7 @@
       <c r="Z256" t="inlineStr"/>
       <c r="AA256" t="inlineStr"/>
       <c r="AB256" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AC256" t="inlineStr">
         <is>
@@ -24362,34 +24362,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>13511</v>
+        <v>12136</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Roberto Firmino</t>
+          <t>Granit Xhaka</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>1991/10/2</t>
+          <t>1992/9/27</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr"/>
-      <c r="I285" t="n">
-        <v>82</v>
-      </c>
+      <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr"/>
@@ -24399,11 +24397,11 @@
       <c r="P285" t="inlineStr"/>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="R285" t="n">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="S285" t="inlineStr">
         <is>
@@ -24440,48 +24438,50 @@
       </c>
       <c r="AD285" t="inlineStr">
         <is>
-          <t>Al-Sadd SC</t>
+          <t>Sunderland AFC</t>
         </is>
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sunderland;Arsenal</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
         <is>
-          <t>罗伯托·菲尔米诺</t>
+          <t>格拉尼特·扎卡</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>2537</v>
+        <v>13511</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Asmir Begovic</t>
+          <t>Roberto Firmino</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bosnia &amp; Herzegovina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>1987/6/20</t>
+          <t>1991/10/2</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr"/>
+      <c r="I286" t="n">
+        <v>82</v>
+      </c>
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr"/>
@@ -24489,15 +24489,37 @@
       <c r="N286" t="inlineStr"/>
       <c r="O286" t="inlineStr"/>
       <c r="P286" t="inlineStr"/>
-      <c r="Q286" t="inlineStr"/>
-      <c r="R286" t="inlineStr"/>
-      <c r="S286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="R286" t="n">
+        <v>256</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T286" t="inlineStr"/>
-      <c r="U286" t="inlineStr"/>
-      <c r="V286" t="inlineStr"/>
+      <c r="U286" t="n">
+        <v>0</v>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W286" t="inlineStr"/>
-      <c r="X286" t="inlineStr"/>
-      <c r="Y286" t="inlineStr"/>
+      <c r="X286" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z286" t="inlineStr"/>
       <c r="AA286" t="inlineStr"/>
       <c r="AB286" t="n">
@@ -24510,42 +24532,42 @@
       </c>
       <c r="AD286" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Al-Sadd SC</t>
         </is>
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
         <is>
-          <t>阿斯米尔·贝戈维奇</t>
+          <t>罗伯托·菲尔米诺</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>3</v>
+        <v>2537</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Tony Adams</t>
+          <t>Asmir Begovic</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Bosnia &amp; Herzegovina</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>1966/10/10</t>
+          <t>1987/6/20</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -24553,91 +24575,69 @@
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>Premier League 10 Seasons Awards</t>
-        </is>
-      </c>
+      <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr"/>
       <c r="N287" t="inlineStr"/>
       <c r="O287" t="inlineStr"/>
       <c r="P287" t="inlineStr"/>
-      <c r="Q287" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="R287" t="n">
-        <v>255</v>
-      </c>
-      <c r="S287" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q287" t="inlineStr"/>
+      <c r="R287" t="inlineStr"/>
+      <c r="S287" t="inlineStr"/>
       <c r="T287" t="inlineStr"/>
-      <c r="U287" t="n">
-        <v>0</v>
-      </c>
-      <c r="V287" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U287" t="inlineStr"/>
+      <c r="V287" t="inlineStr"/>
       <c r="W287" t="inlineStr"/>
-      <c r="X287" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y287" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X287" t="inlineStr"/>
+      <c r="Y287" t="inlineStr"/>
       <c r="Z287" t="inlineStr"/>
       <c r="AA287" t="inlineStr"/>
       <c r="AB287" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD287" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>Leicester City</t>
+        </is>
+      </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
         <is>
-          <t>托尼·亚当斯</t>
+          <t>阿斯米尔·贝戈维奇</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>12136</v>
+        <v>3</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Granit Xhaka</t>
+          <t>Tony Adams</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>1992/9/27</t>
+          <t>1966/10/10</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -24645,7 +24645,11 @@
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Premier League 10 Seasons Awards</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr"/>
       <c r="N288" t="inlineStr"/>
@@ -24657,7 +24661,7 @@
         </is>
       </c>
       <c r="R288" t="n">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
@@ -24689,22 +24693,18 @@
       </c>
       <c r="AC288" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD288" t="inlineStr">
-        <is>
-          <t>Sunderland AFC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr"/>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>Sunderland;Arsenal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
         <is>
-          <t>格拉尼特·扎卡</t>
+          <t>托尼·亚当斯</t>
         </is>
       </c>
     </row>
@@ -26570,26 +26570,26 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>3175</v>
+        <v>4985</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Andy Carroll</t>
+          <t>Bernd Leno</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>1989/1/6</t>
+          <t>1992/3/4</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -26619,43 +26619,47 @@
       </c>
       <c r="AC312" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD312" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD312" t="inlineStr">
+        <is>
+          <t>Fulham FC</t>
+        </is>
+      </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>Newcastle United;Liverpool;West Ham United</t>
+          <t>Fulham;Arsenal</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
         <is>
-          <t>安迪·卡罗尔</t>
+          <t>伯恩德·莱诺</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>5175</v>
+        <v>3175</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Kurt Zouma</t>
+          <t>Andy Carroll</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>1994/10/27</t>
+          <t>1989/1/6</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -26681,7 +26685,7 @@
       <c r="Z313" t="inlineStr"/>
       <c r="AA313" t="inlineStr"/>
       <c r="AB313" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AC313" t="inlineStr">
         <is>
@@ -26691,12 +26695,12 @@
       <c r="AD313" t="inlineStr"/>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>Chelsea;Stoke City;Everton;West Ham United</t>
+          <t>Newcastle United;Liverpool;West Ham United</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
         <is>
-          <t>库尔特·祖马</t>
+          <t>安迪·卡罗尔</t>
         </is>
       </c>
     </row>
@@ -26768,26 +26772,26 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>3137</v>
+        <v>5175</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Lucas Leiva</t>
+          <t>Kurt Zouma</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1987/1/9</t>
+          <t>1994/10/27</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -26801,37 +26805,15 @@
       <c r="N315" t="inlineStr"/>
       <c r="O315" t="inlineStr"/>
       <c r="P315" t="inlineStr"/>
-      <c r="Q315" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="R315" t="n">
-        <v>247</v>
-      </c>
-      <c r="S315" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q315" t="inlineStr"/>
+      <c r="R315" t="inlineStr"/>
+      <c r="S315" t="inlineStr"/>
       <c r="T315" t="inlineStr"/>
-      <c r="U315" t="n">
-        <v>0</v>
-      </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U315" t="inlineStr"/>
+      <c r="V315" t="inlineStr"/>
       <c r="W315" t="inlineStr"/>
-      <c r="X315" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y315" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X315" t="inlineStr"/>
+      <c r="Y315" t="inlineStr"/>
       <c r="Z315" t="inlineStr"/>
       <c r="AA315" t="inlineStr"/>
       <c r="AB315" t="n">
@@ -26845,12 +26827,12 @@
       <c r="AD315" t="inlineStr"/>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chelsea;Stoke City;Everton;West Ham United</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
         <is>
-          <t>卢卡斯·莱瓦</t>
+          <t>库尔特·祖马</t>
         </is>
       </c>
     </row>
@@ -26926,26 +26908,26 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>4985</v>
+        <v>847</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Bernd Leno</t>
+          <t>Ian Taylor</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1992/3/4</t>
+          <t>1968/6/4</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -26959,15 +26941,37 @@
       <c r="N317" t="inlineStr"/>
       <c r="O317" t="inlineStr"/>
       <c r="P317" t="inlineStr"/>
-      <c r="Q317" t="inlineStr"/>
-      <c r="R317" t="inlineStr"/>
-      <c r="S317" t="inlineStr"/>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="R317" t="n">
+        <v>234</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T317" t="inlineStr"/>
-      <c r="U317" t="inlineStr"/>
-      <c r="V317" t="inlineStr"/>
+      <c r="U317" t="n">
+        <v>0</v>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W317" t="inlineStr"/>
-      <c r="X317" t="inlineStr"/>
-      <c r="Y317" t="inlineStr"/>
+      <c r="X317" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z317" t="inlineStr"/>
       <c r="AA317" t="inlineStr"/>
       <c r="AB317" t="n">
@@ -26975,37 +26979,33 @@
       </c>
       <c r="AC317" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD317" t="inlineStr">
-        <is>
-          <t>Fulham FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr"/>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>Fulham;Arsenal</t>
+          <t>Derby County;Aston Villa</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
         <is>
-          <t>伯恩德·莱诺</t>
+          <t>伊恩·泰勒</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>847</v>
+        <v>3137</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Ian Taylor</t>
+          <t>Lucas Leiva</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -27015,7 +27015,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>1968/6/4</t>
+          <t>1987/1/9</t>
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
@@ -27031,11 +27031,11 @@
       <c r="P318" t="inlineStr"/>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="R318" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
@@ -27073,12 +27073,12 @@
       <c r="AD318" t="inlineStr"/>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>Derby County;Aston Villa</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
         <is>
-          <t>伊恩·泰勒</t>
+          <t>卢卡斯·莱瓦</t>
         </is>
       </c>
     </row>
@@ -27342,33 +27342,35 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>2928</v>
+        <v>10079</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Stephen Ireland</t>
+          <t>Nick Pope</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>1986/8/22</t>
+          <t>1992/4/19</t>
         </is>
       </c>
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr"/>
-      <c r="J322" t="inlineStr"/>
+      <c r="J322" t="n">
+        <v>82</v>
+      </c>
       <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr"/>
       <c r="M322" t="inlineStr"/>
@@ -27391,43 +27393,47 @@
       </c>
       <c r="AC322" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD322" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>Manchester City;Aston Villa;Newcastle United;Stoke City</t>
+          <t>Newcastle United;Burnley</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
         <is>
-          <t>斯蒂芬·爱尔兰</t>
+          <t>尼克·波普</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>1565</v>
+        <v>2928</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Jonathan Woodgate</t>
+          <t>Stephen Ireland</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>1980/1/22</t>
+          <t>1986/8/22</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -27453,7 +27459,7 @@
       <c r="Z323" t="inlineStr"/>
       <c r="AA323" t="inlineStr"/>
       <c r="AB323" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AC323" t="inlineStr">
         <is>
@@ -27463,46 +27469,44 @@
       <c r="AD323" t="inlineStr"/>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Manchester City;Aston Villa;Newcastle United;Stoke City</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
         <is>
-          <t>乔纳森·伍德盖特</t>
+          <t>斯蒂芬·爱尔兰</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>10079</v>
+        <v>598</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Nick Pope</t>
+          <t>Robbie Earle</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>1992/4/19</t>
+          <t>1965/1/27</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr"/>
-      <c r="J324" t="n">
-        <v>82</v>
-      </c>
+      <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr"/>
       <c r="M324" t="inlineStr"/>
@@ -27525,47 +27529,43 @@
       </c>
       <c r="AC324" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD324" t="inlineStr">
-        <is>
-          <t>Newcastle United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr"/>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>Newcastle United;Burnley</t>
+          <t>Wimbledon</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
         <is>
-          <t>尼克·波普</t>
+          <t>罗比·厄尔</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>598</v>
+        <v>1565</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Robbie Earle</t>
+          <t>Jonathan Woodgate</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>1965/1/27</t>
+          <t>1980/1/22</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
@@ -27601,27 +27601,27 @@
       <c r="AD325" t="inlineStr"/>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>Wimbledon</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
         <is>
-          <t>罗比·厄尔</t>
+          <t>乔纳森·伍德盖特</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>4123</v>
+        <v>22542</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Mousa Dembélé</t>
+          <t>Pascal Groß</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -27631,7 +27631,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>1987/7/16</t>
+          <t>1991/6/15</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
@@ -27647,15 +27647,15 @@
       <c r="P326" t="inlineStr"/>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="R326" t="n">
-        <v>181</v>
+        <v>244</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="T326" t="inlineStr"/>
@@ -27679,22 +27679,26 @@
       <c r="Z326" t="inlineStr"/>
       <c r="AA326" t="inlineStr"/>
       <c r="AB326" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AC326" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD326" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD326" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
         <is>
-          <t>穆萨·登贝莱</t>
+          <t>帕斯卡尔·格罗斯</t>
         </is>
       </c>
     </row>
@@ -27920,16 +27924,16 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>22542</v>
+        <v>4123</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Pascal Groß</t>
+          <t>Mousa Dembélé</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -27939,7 +27943,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>1991/6/15</t>
+          <t>1987/7/16</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
@@ -27955,15 +27959,15 @@
       <c r="P330" t="inlineStr"/>
       <c r="Q330" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="R330" t="n">
-        <v>243</v>
+        <v>181</v>
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="T330" t="inlineStr"/>
@@ -27991,22 +27995,18 @@
       </c>
       <c r="AC330" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD330" t="inlineStr">
-        <is>
-          <t>Brighton &amp; Hove Albion</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD330" t="inlineStr"/>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
         <is>
-          <t>帕斯卡尔·格罗斯</t>
+          <t>穆萨·登贝莱</t>
         </is>
       </c>
     </row>
@@ -28078,26 +28078,26 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>3404</v>
+        <v>19680</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Martin Skrtel</t>
+          <t>Gabriel Jesus</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>1984/12/15</t>
+          <t>1997/4/3</t>
         </is>
       </c>
       <c r="F332" t="inlineStr"/>
@@ -28108,40 +28108,28 @@
       <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr"/>
       <c r="M332" t="inlineStr"/>
-      <c r="N332" t="inlineStr"/>
-      <c r="O332" t="inlineStr"/>
-      <c r="P332" t="inlineStr"/>
-      <c r="Q332" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="R332" t="n">
-        <v>242</v>
-      </c>
-      <c r="S332" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="N332" t="n">
+        <v>4</v>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>2017–18, 2018–19, 2020–21, 2021–22</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr"/>
+      <c r="R332" t="inlineStr"/>
+      <c r="S332" t="inlineStr"/>
       <c r="T332" t="inlineStr"/>
-      <c r="U332" t="n">
-        <v>0</v>
-      </c>
-      <c r="V332" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U332" t="inlineStr"/>
+      <c r="V332" t="inlineStr"/>
       <c r="W332" t="inlineStr"/>
-      <c r="X332" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y332" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X332" t="inlineStr"/>
+      <c r="Y332" t="inlineStr"/>
       <c r="Z332" t="inlineStr"/>
       <c r="AA332" t="inlineStr"/>
       <c r="AB332" t="n">
@@ -28154,42 +28142,42 @@
       </c>
       <c r="AD332" t="inlineStr">
         <is>
-          <t>TJ SPP Velke Bierovce-Opatovce</t>
+          <t>Arsenal FC</t>
         </is>
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arsenal;Manchester City</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
         <is>
-          <t>马丁·斯科特尔</t>
+          <t>加布里埃尔·热苏斯</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>2289</v>
+        <v>3404</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>El Hadji Diouf</t>
+          <t>Martin Skrtel</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>1981/1/15</t>
+          <t>1984/12/15</t>
         </is>
       </c>
       <c r="F333" t="inlineStr"/>
@@ -28203,15 +28191,37 @@
       <c r="N333" t="inlineStr"/>
       <c r="O333" t="inlineStr"/>
       <c r="P333" t="inlineStr"/>
-      <c r="Q333" t="inlineStr"/>
-      <c r="R333" t="inlineStr"/>
-      <c r="S333" t="inlineStr"/>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="R333" t="n">
+        <v>242</v>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T333" t="inlineStr"/>
-      <c r="U333" t="inlineStr"/>
-      <c r="V333" t="inlineStr"/>
+      <c r="U333" t="n">
+        <v>0</v>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W333" t="inlineStr"/>
-      <c r="X333" t="inlineStr"/>
-      <c r="Y333" t="inlineStr"/>
+      <c r="X333" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z333" t="inlineStr"/>
       <c r="AA333" t="inlineStr"/>
       <c r="AB333" t="n">
@@ -28219,18 +28229,22 @@
       </c>
       <c r="AC333" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD333" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD333" t="inlineStr">
+        <is>
+          <t>TJ SPP Velke Bierovce-Opatovce</t>
+        </is>
+      </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
         <is>
-          <t>埃尔哈吉·迪乌夫</t>
+          <t>马丁·斯科特尔</t>
         </is>
       </c>
     </row>
@@ -28302,16 +28316,16 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>1497</v>
+        <v>2289</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Freddie Ljungberg</t>
+          <t>El Hadji Diouf</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -28321,7 +28335,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>1977/4/16</t>
+          <t>1981/1/15</t>
         </is>
       </c>
       <c r="F335" t="inlineStr"/>
@@ -28330,54 +28344,24 @@
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="M335" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
       <c r="N335" t="inlineStr"/>
       <c r="O335" t="inlineStr"/>
       <c r="P335" t="inlineStr"/>
-      <c r="Q335" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="R335" t="n">
-        <v>216</v>
-      </c>
-      <c r="S335" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q335" t="inlineStr"/>
+      <c r="R335" t="inlineStr"/>
+      <c r="S335" t="inlineStr"/>
       <c r="T335" t="inlineStr"/>
-      <c r="U335" t="n">
-        <v>0</v>
-      </c>
-      <c r="V335" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U335" t="inlineStr"/>
+      <c r="V335" t="inlineStr"/>
       <c r="W335" t="inlineStr"/>
-      <c r="X335" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y335" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X335" t="inlineStr"/>
+      <c r="Y335" t="inlineStr"/>
       <c r="Z335" t="inlineStr"/>
       <c r="AA335" t="inlineStr"/>
       <c r="AB335" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AC335" t="inlineStr">
         <is>
@@ -28387,12 +28371,12 @@
       <c r="AD335" t="inlineStr"/>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>Arsenal;West Ham United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
         <is>
-          <t>弗雷迪·永贝里</t>
+          <t>埃尔哈吉·迪乌夫</t>
         </is>
       </c>
     </row>
@@ -28486,26 +28470,26 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>19680</v>
+        <v>1497</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Gabriel Jesus</t>
+          <t>Freddie Ljungberg</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>1997/4/3</t>
+          <t>1977/4/16</t>
         </is>
       </c>
       <c r="F337" t="inlineStr"/>
@@ -28514,30 +28498,50 @@
       <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr"/>
-      <c r="L337" t="inlineStr"/>
-      <c r="M337" t="inlineStr"/>
-      <c r="N337" t="n">
-        <v>4</v>
-      </c>
-      <c r="O337" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="P337" t="inlineStr">
-        <is>
-          <t>2017–18, 2018–19, 2020–21, 2021–22</t>
-        </is>
-      </c>
-      <c r="Q337" t="inlineStr"/>
-      <c r="R337" t="inlineStr"/>
-      <c r="S337" t="inlineStr"/>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr"/>
+      <c r="O337" t="inlineStr"/>
+      <c r="P337" t="inlineStr"/>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="R337" t="n">
+        <v>216</v>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T337" t="inlineStr"/>
-      <c r="U337" t="inlineStr"/>
-      <c r="V337" t="inlineStr"/>
+      <c r="U337" t="n">
+        <v>0</v>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W337" t="inlineStr"/>
-      <c r="X337" t="inlineStr"/>
-      <c r="Y337" t="inlineStr"/>
+      <c r="X337" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z337" t="inlineStr"/>
       <c r="AA337" t="inlineStr"/>
       <c r="AB337" t="n">
@@ -28545,55 +28549,49 @@
       </c>
       <c r="AC337" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD337" t="inlineStr">
-        <is>
-          <t>Arsenal FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD337" t="inlineStr"/>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>Arsenal;Manchester City</t>
+          <t>Arsenal;West Ham United</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
         <is>
-          <t>加布里埃尔·热苏斯</t>
+          <t>弗雷迪·永贝里</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>2845</v>
+        <v>3807</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Emmanuel Adebayor</t>
+          <t>Scott Dann</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>1984/2/26</t>
+          <t>1987/2/14</t>
         </is>
       </c>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr"/>
-      <c r="I338" t="n">
-        <v>97</v>
-      </c>
+      <c r="I338" t="inlineStr"/>
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr"/>
@@ -28623,43 +28621,45 @@
       <c r="AD338" t="inlineStr"/>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>Arsenal;Manchester City;Tottenham Hotspur;Crystal Palace</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
         <is>
-          <t>埃马纽埃尔·阿德巴约</t>
+          <t>斯科特·丹恩</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>3807</v>
+        <v>2845</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Scott Dann</t>
+          <t>Emmanuel Adebayor</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>1987/2/14</t>
+          <t>1984/2/26</t>
         </is>
       </c>
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr"/>
+      <c r="I339" t="n">
+        <v>97</v>
+      </c>
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr"/>
@@ -28689,12 +28689,12 @@
       <c r="AD339" t="inlineStr"/>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Arsenal;Manchester City;Tottenham Hotspur;Crystal Palace</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
         <is>
-          <t>斯科特·丹恩</t>
+          <t>埃马纽埃尔·阿德巴约</t>
         </is>
       </c>
     </row>
@@ -29524,26 +29524,26 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>755</v>
+        <v>20486</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Simon Charlton</t>
+          <t>Leandro Trossard</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>1971/10/25</t>
+          <t>1994/12/4</t>
         </is>
       </c>
       <c r="F351" t="inlineStr"/>
@@ -29569,22 +29569,26 @@
       <c r="Z351" t="inlineStr"/>
       <c r="AA351" t="inlineStr"/>
       <c r="AB351" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AC351" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD351" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD351" t="inlineStr">
+        <is>
+          <t>Arsenal FC</t>
+        </is>
+      </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>Southampton;Birmingham City;Norwich City</t>
+          <t>Arsenal;Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
         <is>
-          <t>西蒙·查尔顿</t>
+          <t>利安德罗·特罗萨德</t>
         </is>
       </c>
     </row>
@@ -29788,26 +29792,26 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>20486</v>
+        <v>755</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Leandro Trossard</t>
+          <t>Simon Charlton</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>1994/12/4</t>
+          <t>1971/10/25</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
@@ -29837,22 +29841,18 @@
       </c>
       <c r="AC354" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD354" t="inlineStr">
-        <is>
-          <t>Arsenal FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD354" t="inlineStr"/>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>Arsenal;Brighton &amp; Hove Albion</t>
+          <t>Southampton;Birmingham City;Norwich City</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
         <is>
-          <t>利安德罗·特罗萨德</t>
+          <t>西蒙·查尔顿</t>
         </is>
       </c>
     </row>
@@ -30283,7 +30283,7 @@
         </is>
       </c>
       <c r="R360" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
       <c r="Z360" t="inlineStr"/>
       <c r="AA360" t="inlineStr"/>
       <c r="AB360" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AC360" t="inlineStr">
         <is>
@@ -30402,26 +30402,26 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>2047</v>
+        <v>14716</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Jonathan Walters</t>
+          <t>Harvey Barnes</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>1983/9/20</t>
+          <t>1997/12/9</t>
         </is>
       </c>
       <c r="F362" t="inlineStr"/>
@@ -30435,66 +30435,48 @@
       <c r="N362" t="inlineStr"/>
       <c r="O362" t="inlineStr"/>
       <c r="P362" t="inlineStr"/>
-      <c r="Q362" t="inlineStr">
-        <is>
-          <t>Stoke City</t>
-        </is>
-      </c>
-      <c r="R362" t="n">
-        <v>226</v>
-      </c>
-      <c r="S362" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q362" t="inlineStr"/>
+      <c r="R362" t="inlineStr"/>
+      <c r="S362" t="inlineStr"/>
       <c r="T362" t="inlineStr"/>
-      <c r="U362" t="n">
-        <v>0</v>
-      </c>
-      <c r="V362" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U362" t="inlineStr"/>
+      <c r="V362" t="inlineStr"/>
       <c r="W362" t="inlineStr"/>
-      <c r="X362" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y362" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X362" t="inlineStr"/>
+      <c r="Y362" t="inlineStr"/>
       <c r="Z362" t="inlineStr"/>
       <c r="AA362" t="inlineStr"/>
       <c r="AB362" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AC362" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD362" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD362" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>Burnley;Stoke City</t>
+          <t>Newcastle United;Leicester City</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
         <is>
-          <t>乔纳森·沃尔特斯</t>
+          <t>哈维·巴恩斯</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>14716</v>
+        <v>8707</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Harvey Barnes</t>
+          <t>Dan Burn</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -30504,12 +30486,12 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>1997/12/9</t>
+          <t>1992/5/9</t>
         </is>
       </c>
       <c r="F363" t="inlineStr"/>
@@ -30549,37 +30531,37 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>Newcastle United;Leicester City</t>
+          <t>Newcastle United;Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
         <is>
-          <t>哈维·巴恩斯</t>
+          <t>丹·伯恩</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>2024</v>
+        <v>2047</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Tugay</t>
+          <t>Jonathan Walters</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Turkiye</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>1970/8/24</t>
+          <t>1983/9/20</t>
         </is>
       </c>
       <c r="F364" t="inlineStr"/>
@@ -30595,11 +30577,11 @@
       <c r="P364" t="inlineStr"/>
       <c r="Q364" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="R364" t="n">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="S364" t="inlineStr">
         <is>
@@ -30637,37 +30619,37 @@
       <c r="AD364" t="inlineStr"/>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Burnley;Stoke City</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
         <is>
-          <t>图盖</t>
+          <t>乔纳森·沃尔特斯</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Olof Mellberg</t>
+          <t>Tugay</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Turkiye</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>1977/9/3</t>
+          <t>1970/8/24</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
@@ -30683,11 +30665,11 @@
       <c r="P365" t="inlineStr"/>
       <c r="Q365" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="R365" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="S365" t="inlineStr">
         <is>
@@ -30715,7 +30697,7 @@
       <c r="Z365" t="inlineStr"/>
       <c r="AA365" t="inlineStr"/>
       <c r="AB365" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AC365" t="inlineStr">
         <is>
@@ -30725,27 +30707,27 @@
       <c r="AD365" t="inlineStr"/>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
         <is>
-          <t>奥洛夫·梅尔伯格</t>
+          <t>图盖</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>8707</v>
+        <v>2012</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Dan Burn</t>
+          <t>Olof Mellberg</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -30755,7 +30737,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>1992/5/9</t>
+          <t>1977/9/3</t>
         </is>
       </c>
       <c r="F366" t="inlineStr"/>
@@ -30769,15 +30751,37 @@
       <c r="N366" t="inlineStr"/>
       <c r="O366" t="inlineStr"/>
       <c r="P366" t="inlineStr"/>
-      <c r="Q366" t="inlineStr"/>
-      <c r="R366" t="inlineStr"/>
-      <c r="S366" t="inlineStr"/>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="R366" t="n">
+        <v>232</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T366" t="inlineStr"/>
-      <c r="U366" t="inlineStr"/>
-      <c r="V366" t="inlineStr"/>
+      <c r="U366" t="n">
+        <v>0</v>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W366" t="inlineStr"/>
-      <c r="X366" t="inlineStr"/>
-      <c r="Y366" t="inlineStr"/>
+      <c r="X366" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z366" t="inlineStr"/>
       <c r="AA366" t="inlineStr"/>
       <c r="AB366" t="n">
@@ -30785,22 +30789,18 @@
       </c>
       <c r="AC366" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD366" t="inlineStr">
-        <is>
-          <t>Newcastle United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD366" t="inlineStr"/>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>Newcastle United;Brighton &amp; Hove Albion</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
         <is>
-          <t>丹·伯恩</t>
+          <t>奥洛夫·梅尔伯格</t>
         </is>
       </c>
     </row>
@@ -31162,26 +31162,26 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>4148</v>
+        <v>14164</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Yaya Touré</t>
+          <t>Aaron Wan-Bissaka</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Cote D’Ivoire</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>1983/5/13</t>
+          <t>1997/11/26</t>
         </is>
       </c>
       <c r="F372" t="inlineStr"/>
@@ -31192,54 +31192,22 @@
       <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr"/>
       <c r="M372" t="inlineStr"/>
-      <c r="N372" t="n">
-        <v>3</v>
-      </c>
-      <c r="O372" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="P372" t="inlineStr">
-        <is>
-          <t>2011–12, 2013–14, 2017–18</t>
-        </is>
-      </c>
-      <c r="Q372" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="R372" t="n">
-        <v>230</v>
-      </c>
-      <c r="S372" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="N372" t="inlineStr"/>
+      <c r="O372" t="inlineStr"/>
+      <c r="P372" t="inlineStr"/>
+      <c r="Q372" t="inlineStr"/>
+      <c r="R372" t="inlineStr"/>
+      <c r="S372" t="inlineStr"/>
       <c r="T372" t="inlineStr"/>
-      <c r="U372" t="n">
-        <v>0</v>
-      </c>
-      <c r="V372" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U372" t="inlineStr"/>
+      <c r="V372" t="inlineStr"/>
       <c r="W372" t="inlineStr"/>
-      <c r="X372" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y372" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X372" t="inlineStr"/>
+      <c r="Y372" t="inlineStr"/>
       <c r="Z372" t="inlineStr"/>
       <c r="AA372" t="inlineStr"/>
       <c r="AB372" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AC372" t="inlineStr">
         <is>
@@ -31249,37 +31217,37 @@
       <c r="AD372" t="inlineStr"/>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
         <is>
-          <t>亚亚·图雷</t>
+          <t>阿隆·万-比萨卡</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>14164</v>
+        <v>11071</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Aaron Wan-Bissaka</t>
+          <t>Raúl Jiménez</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>1997/11/26</t>
+          <t>1991/5/5</t>
         </is>
       </c>
       <c r="F373" t="inlineStr"/>
@@ -31305,47 +31273,51 @@
       <c r="Z373" t="inlineStr"/>
       <c r="AA373" t="inlineStr"/>
       <c r="AB373" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AC373" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD373" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD373" t="inlineStr">
+        <is>
+          <t>Fulham FC</t>
+        </is>
+      </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
         <is>
-          <t>阿隆·万-比萨卡</t>
+          <t>劳尔·希门尼斯</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>11071</v>
+        <v>4148</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Raúl Jiménez</t>
+          <t>Yaya Touré</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Cote D’Ivoire</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>1991/5/5</t>
+          <t>1983/5/13</t>
         </is>
       </c>
       <c r="F374" t="inlineStr"/>
@@ -31356,18 +31328,50 @@
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr"/>
       <c r="M374" t="inlineStr"/>
-      <c r="N374" t="inlineStr"/>
-      <c r="O374" t="inlineStr"/>
-      <c r="P374" t="inlineStr"/>
-      <c r="Q374" t="inlineStr"/>
-      <c r="R374" t="inlineStr"/>
-      <c r="S374" t="inlineStr"/>
+      <c r="N374" t="n">
+        <v>3</v>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>2011–12, 2013–14, 2017–18</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="R374" t="n">
+        <v>230</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T374" t="inlineStr"/>
-      <c r="U374" t="inlineStr"/>
-      <c r="V374" t="inlineStr"/>
+      <c r="U374" t="n">
+        <v>0</v>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W374" t="inlineStr"/>
-      <c r="X374" t="inlineStr"/>
-      <c r="Y374" t="inlineStr"/>
+      <c r="X374" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z374" t="inlineStr"/>
       <c r="AA374" t="inlineStr"/>
       <c r="AB374" t="n">
@@ -31375,22 +31379,18 @@
       </c>
       <c r="AC374" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD374" t="inlineStr">
-        <is>
-          <t>Fulham FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD374" t="inlineStr"/>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
         <is>
-          <t>劳尔·希门尼斯</t>
+          <t>亚亚·图雷</t>
         </is>
       </c>
     </row>
@@ -32321,7 +32321,7 @@
         </is>
       </c>
       <c r="R385" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="S385" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         </is>
       </c>
       <c r="R387" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S387" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         </is>
       </c>
       <c r="R396" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="S396" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         </is>
       </c>
       <c r="R403" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="S403" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         </is>
       </c>
       <c r="R431" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S431" t="inlineStr">
         <is>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -9361,7 +9361,7 @@
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
@@ -9628,34 +9628,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1005</v>
+        <v>10458</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>James Beattie</t>
+          <t>Andy Robertson</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1978/2/27</t>
+          <t>1994/3/11</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="n">
-        <v>90</v>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
@@ -9665,11 +9663,11 @@
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="R104" t="n">
-        <v>202</v>
+        <v>273</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -9701,49 +9699,55 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>Blackburn Rovers;Southampton;Everton;Stoke City</t>
+          <t>Hull City;Liverpool</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>詹姆斯·比蒂</t>
+          <t>安迪·罗伯逊</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>10458</v>
+        <v>1005</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Andy Robertson</t>
+          <t>James Beattie</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1994/3/11</t>
+          <t>1978/2/27</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="n">
+        <v>90</v>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
@@ -9753,11 +9757,11 @@
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="R105" t="n">
-        <v>273</v>
+        <v>202</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -9785,26 +9789,22 @@
       <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="inlineStr"/>
       <c r="AB105" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD105" t="inlineStr">
-        <is>
-          <t>Liverpool FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr"/>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>Hull City;Liverpool</t>
+          <t>Blackburn Rovers;Southampton;Everton;Stoke City</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>安迪·罗伯逊</t>
+          <t>詹姆斯·比蒂</t>
         </is>
       </c>
     </row>
@@ -14684,11 +14684,11 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>300</v>
+        <v>4115</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Garry Flitcroft</t>
+          <t>Ross Barkley</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>1972/11/6</t>
+          <t>1993/12/5</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -14717,66 +14717,48 @@
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="R163" t="n">
-        <v>186</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
-      <c r="U163" t="n">
-        <v>0</v>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
       <c r="W163" t="inlineStr"/>
-      <c r="X163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X163" t="inlineStr"/>
+      <c r="Y163" t="inlineStr"/>
       <c r="Z163" t="inlineStr"/>
       <c r="AA163" t="inlineStr"/>
       <c r="AB163" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Aston Villa;Chelsea</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
         <is>
-          <t>加里·弗利特克罗夫特</t>
+          <t>罗斯·巴克利</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>4115</v>
+        <v>300</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ross Barkley</t>
+          <t>Garry Flitcroft</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -14791,7 +14773,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1993/12/5</t>
+          <t>1972/11/6</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -14805,15 +14787,37 @@
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
-      <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="R164" t="n">
+        <v>186</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T164" t="inlineStr"/>
-      <c r="U164" t="inlineStr"/>
-      <c r="V164" t="inlineStr"/>
+      <c r="U164" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W164" t="inlineStr"/>
-      <c r="X164" t="inlineStr"/>
-      <c r="Y164" t="inlineStr"/>
+      <c r="X164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z164" t="inlineStr"/>
       <c r="AA164" t="inlineStr"/>
       <c r="AB164" t="n">
@@ -14821,22 +14825,18 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr"/>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>Aston Villa;Chelsea</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
         <is>
-          <t>罗斯·巴克利</t>
+          <t>加里·弗利特克罗夫特</t>
         </is>
       </c>
     </row>
@@ -15951,7 +15951,7 @@
       <c r="Z178" t="inlineStr"/>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
       <c r="Z194" t="inlineStr"/>
       <c r="AA194" t="inlineStr"/>
       <c r="AB194" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AC194" t="inlineStr">
         <is>
@@ -21146,16 +21146,16 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>9576</v>
+        <v>24630</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Dominic Calvert-Lewin</t>
+          <t>Richarlison</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -21165,7 +21165,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>1997/3/16</t>
+          <t>1997/5/10</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -21179,41 +21179,19 @@
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="R245" t="n">
-        <v>239</v>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr"/>
+      <c r="S245" t="inlineStr"/>
       <c r="T245" t="inlineStr"/>
-      <c r="U245" t="n">
-        <v>0</v>
-      </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U245" t="inlineStr"/>
+      <c r="V245" t="inlineStr"/>
       <c r="W245" t="inlineStr"/>
-      <c r="X245" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X245" t="inlineStr"/>
+      <c r="Y245" t="inlineStr"/>
       <c r="Z245" t="inlineStr"/>
       <c r="AA245" t="inlineStr"/>
       <c r="AB245" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AC245" t="inlineStr">
         <is>
@@ -21222,17 +21200,17 @@
       </c>
       <c r="AD245" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>Leeds United;Everton</t>
+          <t>Tottenham Hotspur;Everton</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
         <is>
-          <t>多米尼克·卡尔弗特-卢因</t>
+          <t>理查利森</t>
         </is>
       </c>
     </row>
@@ -21304,16 +21282,16 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>24630</v>
+        <v>9576</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Richarlison</t>
+          <t>Dominic Calvert-Lewin</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -21323,7 +21301,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>1997/5/10</t>
+          <t>1997/3/16</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -21337,15 +21315,37 @@
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="inlineStr"/>
-      <c r="Q247" t="inlineStr"/>
-      <c r="R247" t="inlineStr"/>
-      <c r="S247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="R247" t="n">
+        <v>239</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T247" t="inlineStr"/>
-      <c r="U247" t="inlineStr"/>
-      <c r="V247" t="inlineStr"/>
+      <c r="U247" t="n">
+        <v>0</v>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W247" t="inlineStr"/>
-      <c r="X247" t="inlineStr"/>
-      <c r="Y247" t="inlineStr"/>
+      <c r="X247" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z247" t="inlineStr"/>
       <c r="AA247" t="inlineStr"/>
       <c r="AB247" t="n">
@@ -21358,17 +21358,17 @@
       </c>
       <c r="AD247" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Everton</t>
+          <t>Leeds United;Everton</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
         <is>
-          <t>理查利森</t>
+          <t>多米尼克·卡尔弗特-卢因</t>
         </is>
       </c>
     </row>
@@ -28382,16 +28382,16 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>4403</v>
+        <v>3807</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Ashley Williams</t>
+          <t>Scott Dann</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -28401,7 +28401,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>1984/8/23</t>
+          <t>1987/2/14</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
@@ -28415,37 +28415,15 @@
       <c r="N336" t="inlineStr"/>
       <c r="O336" t="inlineStr"/>
       <c r="P336" t="inlineStr"/>
-      <c r="Q336" t="inlineStr">
-        <is>
-          <t>Swansea City</t>
-        </is>
-      </c>
-      <c r="R336" t="n">
-        <v>181</v>
-      </c>
-      <c r="S336" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q336" t="inlineStr"/>
+      <c r="R336" t="inlineStr"/>
+      <c r="S336" t="inlineStr"/>
       <c r="T336" t="inlineStr"/>
-      <c r="U336" t="n">
-        <v>0</v>
-      </c>
-      <c r="V336" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U336" t="inlineStr"/>
+      <c r="V336" t="inlineStr"/>
       <c r="W336" t="inlineStr"/>
-      <c r="X336" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y336" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X336" t="inlineStr"/>
+      <c r="Y336" t="inlineStr"/>
       <c r="Z336" t="inlineStr"/>
       <c r="AA336" t="inlineStr"/>
       <c r="AB336" t="n">
@@ -28459,12 +28437,12 @@
       <c r="AD336" t="inlineStr"/>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
         <is>
-          <t>阿什利·威廉姆斯</t>
+          <t>斯科特·丹恩</t>
         </is>
       </c>
     </row>
@@ -28566,26 +28544,26 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>3807</v>
+        <v>5865</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Scott Dann</t>
+          <t>Youri Tielemans</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>1987/2/14</t>
+          <t>1997/5/7</t>
         </is>
       </c>
       <c r="F338" t="inlineStr"/>
@@ -28615,18 +28593,22 @@
       </c>
       <c r="AC338" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD338" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD338" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Aston Villa;Leicester City</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
         <is>
-          <t>斯科特·丹恩</t>
+          <t>尤里·蒂勒曼斯</t>
         </is>
       </c>
     </row>
@@ -28700,26 +28682,26 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>79</v>
+        <v>4403</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Stuart Ripley</t>
+          <t>Ashley Williams</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>1967/11/20</t>
+          <t>1984/8/23</t>
         </is>
       </c>
       <c r="F340" t="inlineStr"/>
@@ -28735,11 +28717,11 @@
       <c r="P340" t="inlineStr"/>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="R340" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="S340" t="inlineStr">
         <is>
@@ -28767,7 +28749,7 @@
       <c r="Z340" t="inlineStr"/>
       <c r="AA340" t="inlineStr"/>
       <c r="AB340" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AC340" t="inlineStr">
         <is>
@@ -28777,12 +28759,12 @@
       <c r="AD340" t="inlineStr"/>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
         <is>
-          <t>斯图尔特·里普利</t>
+          <t>阿什利·威廉姆斯</t>
         </is>
       </c>
     </row>
@@ -28988,16 +28970,16 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>5865</v>
+        <v>79</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Youri Tielemans</t>
+          <t>Stuart Ripley</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -29007,7 +28989,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>1997/5/7</t>
+          <t>1967/11/20</t>
         </is>
       </c>
       <c r="F344" t="inlineStr"/>
@@ -29021,15 +29003,37 @@
       <c r="N344" t="inlineStr"/>
       <c r="O344" t="inlineStr"/>
       <c r="P344" t="inlineStr"/>
-      <c r="Q344" t="inlineStr"/>
-      <c r="R344" t="inlineStr"/>
-      <c r="S344" t="inlineStr"/>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="R344" t="n">
+        <v>187</v>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T344" t="inlineStr"/>
-      <c r="U344" t="inlineStr"/>
-      <c r="V344" t="inlineStr"/>
+      <c r="U344" t="n">
+        <v>0</v>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W344" t="inlineStr"/>
-      <c r="X344" t="inlineStr"/>
-      <c r="Y344" t="inlineStr"/>
+      <c r="X344" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z344" t="inlineStr"/>
       <c r="AA344" t="inlineStr"/>
       <c r="AB344" t="n">
@@ -29037,22 +29041,18 @@
       </c>
       <c r="AC344" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD344" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD344" t="inlineStr"/>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>Aston Villa;Leicester City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
         <is>
-          <t>尤里·蒂勒曼斯</t>
+          <t>斯图尔特·里普利</t>
         </is>
       </c>
     </row>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF464"/>
+  <dimension ref="A1:AF465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
@@ -7466,26 +7466,26 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1391</v>
+        <v>2148</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Rory Delap</t>
+          <t>Glen Johnson</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1976/7/6</t>
+          <t>1984/8/23</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -7521,37 +7521,37 @@
       <c r="AD78" t="inlineStr"/>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>Derby County;Southampton;Sunderland;Stoke City</t>
+          <t>West Ham United;Chelsea;Portsmouth;Liverpool;Stoke City</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>罗里·德拉普</t>
+          <t>格伦·约翰逊</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2148</v>
+        <v>1391</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Glen Johnson</t>
+          <t>Rory Delap</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1984/8/23</t>
+          <t>1976/7/6</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -7587,12 +7587,12 @@
       <c r="AD79" t="inlineStr"/>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>West Ham United;Chelsea;Portsmouth;Liverpool;Stoke City</t>
+          <t>Derby County;Southampton;Sunderland;Stoke City</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>格伦·约翰逊</t>
+          <t>罗里·德拉普</t>
         </is>
       </c>
     </row>
@@ -9195,7 +9195,7 @@
       <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -9220,26 +9220,26 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2078</v>
+        <v>5140</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Steed Malbranque</t>
+          <t>Virgil van Dijk</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1980/1/6</t>
+          <t>1991/7/8</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -9248,20 +9248,50 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="R99" t="n">
+        <v>269</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
+      <c r="X99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="n">
@@ -9269,43 +9299,47 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD99" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>Fulham;Tottenham Hotspur;Sunderland</t>
+          <t>Southampton;Liverpool</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>斯蒂德·马尔布兰克</t>
+          <t>维吉尔·范迪克</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>5140</v>
+        <v>2078</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Virgil van Dijk</t>
+          <t>Steed Malbranque</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1991/7/8</t>
+          <t>1980/1/6</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -9314,50 +9348,20 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="R100" t="n">
-        <v>268</v>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
-      <c r="U100" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr"/>
-      <c r="X100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="n">
@@ -9365,22 +9369,18 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>Liverpool FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr"/>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>Southampton;Liverpool</t>
+          <t>Fulham;Tottenham Hotspur;Sunderland</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
         <is>
-          <t>维吉尔·范迪克</t>
+          <t>斯蒂德·马尔布兰克</t>
         </is>
       </c>
     </row>
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="R104" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="R166" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
       <c r="Z166" t="inlineStr"/>
       <c r="AA166" t="inlineStr"/>
       <c r="AB166" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AC166" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         </is>
       </c>
       <c r="R178" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -17964,26 +17964,26 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>2613</v>
+        <v>4333</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Sebastian Larsson</t>
+          <t>Michael Keane</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>1985/6/6</t>
+          <t>1993/1/11</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -17997,34 +17997,60 @@
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
-      <c r="R206" t="inlineStr"/>
-      <c r="S206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="R206" t="n">
+        <v>226</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T206" t="inlineStr"/>
-      <c r="U206" t="inlineStr"/>
-      <c r="V206" t="inlineStr"/>
+      <c r="U206" t="n">
+        <v>0</v>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W206" t="inlineStr"/>
-      <c r="X206" t="inlineStr"/>
-      <c r="Y206" t="inlineStr"/>
+      <c r="X206" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z206" t="inlineStr"/>
       <c r="AA206" t="inlineStr"/>
       <c r="AB206" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>Everton FC</t>
+        </is>
+      </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>Arsenal;Birmingham City;Sunderland;Hull City</t>
+          <t>Everton;Burnley</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
         <is>
-          <t>塞巴斯蒂安·拉尔森</t>
+          <t>迈克尔·基恩</t>
         </is>
       </c>
     </row>
@@ -18096,26 +18122,26 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>4333</v>
+        <v>2613</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Michael Keane</t>
+          <t>Sebastian Larsson</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>1993/1/11</t>
+          <t>1985/6/6</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -18129,37 +18155,15 @@
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="R208" t="n">
-        <v>225</v>
-      </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr"/>
       <c r="T208" t="inlineStr"/>
-      <c r="U208" t="n">
-        <v>0</v>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr"/>
       <c r="W208" t="inlineStr"/>
-      <c r="X208" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X208" t="inlineStr"/>
+      <c r="Y208" t="inlineStr"/>
       <c r="Z208" t="inlineStr"/>
       <c r="AA208" t="inlineStr"/>
       <c r="AB208" t="n">
@@ -18167,22 +18171,18 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>Everton FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr"/>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>Everton;Burnley</t>
+          <t>Arsenal;Birmingham City;Sunderland;Hull City</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
         <is>
-          <t>迈克尔·基恩</t>
+          <t>塞巴斯蒂安·拉尔森</t>
         </is>
       </c>
     </row>
@@ -20088,16 +20088,16 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>4328</v>
+        <v>3756</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Sergio Agüero</t>
+          <t>Chris Wood</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -20107,98 +20107,54 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>1988/6/2</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
+          <t>1991/12/7</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
-        <v>184</v>
+        <v>91</v>
       </c>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr"/>
-      <c r="N233" t="n">
-        <v>5</v>
-      </c>
-      <c r="O233" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>2011–12, 2013–14, 2017–18, 2018–19, 2020–21</t>
-        </is>
-      </c>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="R233" t="n">
-        <v>275</v>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
+      <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr"/>
-      <c r="U233" t="n">
-        <v>0</v>
-      </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U233" t="inlineStr"/>
+      <c r="V233" t="inlineStr"/>
       <c r="W233" t="inlineStr"/>
-      <c r="X233" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="AA233" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
+      <c r="X233" t="inlineStr"/>
+      <c r="Y233" t="inlineStr"/>
+      <c r="Z233" t="inlineStr"/>
+      <c r="AA233" t="inlineStr"/>
       <c r="AB233" t="n">
         <v>275</v>
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD233" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
         <is>
-          <t>塞尔吉奥·阿圭罗</t>
+          <t>克里斯·伍德</t>
         </is>
       </c>
     </row>
@@ -20302,46 +20258,66 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>271</v>
+        <v>4328</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Steve McManaman</t>
+          <t>Sergio Agüero</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>1972/2/11</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
+          <t>1988/6/2</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
       <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
+      <c r="I235" t="n">
+        <v>184</v>
+      </c>
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr"/>
+      <c r="N235" t="n">
+        <v>5</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>2011–12, 2013–14, 2017–18, 2018–19, 2020–21</t>
+        </is>
+      </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="R235" t="n">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -20366,8 +20342,16 @@
           <t>no</t>
         </is>
       </c>
-      <c r="Z235" t="inlineStr"/>
-      <c r="AA235" t="inlineStr"/>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
       <c r="AB235" t="n">
         <v>275</v>
       </c>
@@ -20379,12 +20363,12 @@
       <c r="AD235" t="inlineStr"/>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
         <is>
-          <t>史蒂夫·麦克马纳曼</t>
+          <t>塞尔吉奥·阿圭罗</t>
         </is>
       </c>
     </row>
@@ -20488,11 +20472,11 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>4112</v>
+        <v>271</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Eric Dier</t>
+          <t>Steve McManaman</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -20502,12 +20486,12 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>1994/1/15</t>
+          <t>1972/2/11</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -20523,11 +20507,11 @@
       <c r="P237" t="inlineStr"/>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="R237" t="n">
-        <v>274</v>
+        <v>240</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -20555,26 +20539,22 @@
       <c r="Z237" t="inlineStr"/>
       <c r="AA237" t="inlineStr"/>
       <c r="AB237" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD237" t="inlineStr">
-        <is>
-          <t>AS Monaco</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr"/>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
         <is>
-          <t>埃里克·戴尔</t>
+          <t>史蒂夫·麦克马纳曼</t>
         </is>
       </c>
     </row>
@@ -20678,26 +20658,26 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1049</v>
+        <v>4112</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Harry Kewell</t>
+          <t>Eric Dier</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>1978/9/22</t>
+          <t>1994/1/15</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -20713,11 +20693,11 @@
       <c r="P239" t="inlineStr"/>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="R239" t="n">
-        <v>181</v>
+        <v>274</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -20749,43 +20729,47 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD239" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>AS Monaco</t>
+        </is>
+      </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
         <is>
-          <t>哈里·科威尔</t>
+          <t>埃里克·戴尔</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1168</v>
+        <v>1049</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Chris Powell</t>
+          <t>Harry Kewell</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>1969/9/8</t>
+          <t>1978/9/22</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -20801,11 +20785,11 @@
       <c r="P240" t="inlineStr"/>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="R240" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -20843,45 +20827,43 @@
       <c r="AD240" t="inlineStr"/>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>Leicester City;Charlton Athletic</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
         <is>
-          <t>克里斯·鲍威尔</t>
+          <t>哈里·科威尔</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>3756</v>
+        <v>1168</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Chris Wood</t>
+          <t>Chris Powell</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>1991/12/7</t>
+          <t>1969/9/8</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
-      <c r="I241" t="n">
-        <v>91</v>
-      </c>
+      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr"/>
@@ -20889,15 +20871,37 @@
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="inlineStr"/>
-      <c r="R241" t="inlineStr"/>
-      <c r="S241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="R241" t="n">
+        <v>187</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T241" t="inlineStr"/>
-      <c r="U241" t="inlineStr"/>
-      <c r="V241" t="inlineStr"/>
+      <c r="U241" t="n">
+        <v>0</v>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W241" t="inlineStr"/>
-      <c r="X241" t="inlineStr"/>
-      <c r="Y241" t="inlineStr"/>
+      <c r="X241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z241" t="inlineStr"/>
       <c r="AA241" t="inlineStr"/>
       <c r="AB241" t="n">
@@ -20905,22 +20909,18 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>Nottingham Forest</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr"/>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Leicester City;Charlton Athletic</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
         <is>
-          <t>克里斯·伍德</t>
+          <t>克里斯·鲍威尔</t>
         </is>
       </c>
     </row>
@@ -32141,7 +32141,7 @@
         </is>
       </c>
       <c r="R383" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S383" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         </is>
       </c>
       <c r="R384" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="S384" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         </is>
       </c>
       <c r="R390" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="S390" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         </is>
       </c>
       <c r="R393" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="S393" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         </is>
       </c>
       <c r="R416" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S416" t="inlineStr">
         <is>
@@ -36702,26 +36702,26 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>328</v>
+        <v>13344</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Lee Sharpe</t>
+          <t>Matty Cash</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>1971/5/27</t>
+          <t>1997/8/7</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -36732,70 +36732,78 @@
       <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr"/>
       <c r="M435" t="inlineStr"/>
-      <c r="N435" t="n">
-        <v>3</v>
-      </c>
-      <c r="O435" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="P435" t="inlineStr">
-        <is>
-          <t>1992–93, 1993–94, 1995–96</t>
-        </is>
-      </c>
-      <c r="Q435" t="inlineStr"/>
-      <c r="R435" t="inlineStr"/>
-      <c r="S435" t="inlineStr"/>
+      <c r="N435" t="inlineStr"/>
+      <c r="O435" t="inlineStr"/>
+      <c r="P435" t="inlineStr"/>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="R435" t="n">
+        <v>180</v>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="T435" t="inlineStr"/>
-      <c r="U435" t="inlineStr"/>
-      <c r="V435" t="inlineStr"/>
+      <c r="U435" t="n">
+        <v>0</v>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W435" t="inlineStr"/>
-      <c r="X435" t="inlineStr"/>
-      <c r="Y435" t="inlineStr"/>
+      <c r="X435" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y435" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z435" t="inlineStr"/>
       <c r="AA435" t="inlineStr"/>
       <c r="AB435" t="inlineStr"/>
       <c r="AC435" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD435" t="inlineStr"/>
-      <c r="AE435" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="AF435" t="inlineStr">
-        <is>
-          <t>李·夏普</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD435" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="AE435" t="inlineStr"/>
+      <c r="AF435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>16431</v>
+        <v>328</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Rúben Dias</t>
+          <t>Lee Sharpe</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>1997/5/14</t>
+          <t>1971/5/27</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -36804,27 +36812,19 @@
       <c r="I436" t="inlineStr"/>
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr"/>
-      <c r="L436" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="M436" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
       <c r="N436" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="P436" t="inlineStr">
         <is>
-          <t>2020–21, 2021–22, 2022–23, 2023–24</t>
+          <t>1992–93, 1993–94, 1995–96</t>
         </is>
       </c>
       <c r="Q436" t="inlineStr"/>
@@ -36841,47 +36841,43 @@
       <c r="AB436" t="inlineStr"/>
       <c r="AC436" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD436" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD436" t="inlineStr"/>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
         <is>
-          <t>鲁本·迪亚斯</t>
+          <t>李·夏普</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>3513</v>
+        <v>16431</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Gareth Bale</t>
+          <t>Rúben Dias</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>1989/7/16</t>
+          <t>1997/5/14</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -36892,17 +36888,27 @@
       <c r="K437" t="inlineStr"/>
       <c r="L437" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
-        </is>
-      </c>
-      <c r="N437" t="inlineStr"/>
-      <c r="O437" t="inlineStr"/>
-      <c r="P437" t="inlineStr"/>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="N437" t="n">
+        <v>4</v>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>2020–21, 2021–22, 2022–23, 2023–24</t>
+        </is>
+      </c>
       <c r="Q437" t="inlineStr"/>
       <c r="R437" t="inlineStr"/>
       <c r="S437" t="inlineStr"/>
@@ -36917,57 +36923,65 @@
       <c r="AB437" t="inlineStr"/>
       <c r="AC437" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD437" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD437" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
         <is>
-          <t>加雷斯·贝尔</t>
+          <t>鲁本·迪亚斯</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>7975</v>
+        <v>3513</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>David Raya</t>
+          <t>Gareth Bale</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>1995/9/15</t>
+          <t>1989/7/16</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr"/>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>13.0, 16.0</t>
-        </is>
-      </c>
+      <c r="H438" t="inlineStr"/>
       <c r="I438" t="inlineStr"/>
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr"/>
-      <c r="L438" t="inlineStr"/>
-      <c r="M438" t="inlineStr"/>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
       <c r="N438" t="inlineStr"/>
       <c r="O438" t="inlineStr"/>
       <c r="P438" t="inlineStr"/>
@@ -36985,70 +36999,60 @@
       <c r="AB438" t="inlineStr"/>
       <c r="AC438" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD438" t="inlineStr">
-        <is>
-          <t>Arsenal FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD438" t="inlineStr"/>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>Brentford;Arsenal</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
         <is>
-          <t>大卫·拉亚</t>
+          <t>加雷斯·贝尔</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>337</v>
+        <v>7975</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Brian McClair</t>
+          <t>David Raya</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>1963/12/8</t>
+          <t>1995/9/15</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
-      <c r="H439" t="inlineStr"/>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>13.0, 16.0</t>
+        </is>
+      </c>
       <c r="I439" t="inlineStr"/>
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr"/>
       <c r="M439" t="inlineStr"/>
-      <c r="N439" t="n">
-        <v>4</v>
-      </c>
-      <c r="O439" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="P439" t="inlineStr">
-        <is>
-          <t>1992–93, 1993–94, 1995–96, 1996–97</t>
-        </is>
-      </c>
+      <c r="N439" t="inlineStr"/>
+      <c r="O439" t="inlineStr"/>
+      <c r="P439" t="inlineStr"/>
       <c r="Q439" t="inlineStr"/>
       <c r="R439" t="inlineStr"/>
       <c r="S439" t="inlineStr"/>
@@ -37063,43 +37067,47 @@
       <c r="AB439" t="inlineStr"/>
       <c r="AC439" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD439" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD439" t="inlineStr">
+        <is>
+          <t>Arsenal FC</t>
+        </is>
+      </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Brentford;Arsenal</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
         <is>
-          <t>布莱恩·麦克莱尔</t>
+          <t>大卫·拉亚</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>1533</v>
+        <v>337</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Marcel Desailly</t>
+          <t>Brian McClair</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>1968/9/7</t>
+          <t>1963/12/8</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -37107,16 +37115,22 @@
       <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr"/>
       <c r="J440" t="inlineStr"/>
-      <c r="K440" t="inlineStr">
-        <is>
-          <t>Premier League 10 Seasons Awards</t>
-        </is>
-      </c>
+      <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr"/>
       <c r="M440" t="inlineStr"/>
-      <c r="N440" t="inlineStr"/>
-      <c r="O440" t="inlineStr"/>
-      <c r="P440" t="inlineStr"/>
+      <c r="N440" t="n">
+        <v>4</v>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>1992–93, 1993–94, 1995–96, 1996–97</t>
+        </is>
+      </c>
       <c r="Q440" t="inlineStr"/>
       <c r="R440" t="inlineStr"/>
       <c r="S440" t="inlineStr"/>
@@ -37137,22 +37151,22 @@
       <c r="AD440" t="inlineStr"/>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
         <is>
-          <t>马塞尔·德塞利</t>
+          <t>布莱恩·麦克莱尔</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>342</v>
+        <v>1533</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Eric Cantona</t>
+          <t>Marcel Desailly</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -37162,12 +37176,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>1966/5/24</t>
+          <t>1968/9/7</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -37182,19 +37196,9 @@
       </c>
       <c r="L441" t="inlineStr"/>
       <c r="M441" t="inlineStr"/>
-      <c r="N441" t="n">
-        <v>4</v>
-      </c>
-      <c r="O441" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="P441" t="inlineStr">
-        <is>
-          <t>1992–93, 1993–94, 1995–96, 1996–97</t>
-        </is>
-      </c>
+      <c r="N441" t="inlineStr"/>
+      <c r="O441" t="inlineStr"/>
+      <c r="P441" t="inlineStr"/>
       <c r="Q441" t="inlineStr"/>
       <c r="R441" t="inlineStr"/>
       <c r="S441" t="inlineStr"/>
@@ -37215,37 +37219,37 @@
       <c r="AD441" t="inlineStr"/>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
         <is>
-          <t>埃里克·坎通纳</t>
+          <t>马塞尔·德塞利</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>2940</v>
+        <v>342</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Park Ji-Sung</t>
+          <t>Eric Cantona</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>1981/2/25</t>
+          <t>1966/5/24</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -37253,7 +37257,11 @@
       <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr"/>
       <c r="J442" t="inlineStr"/>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Premier League 10 Seasons Awards</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr"/>
       <c r="M442" t="inlineStr"/>
       <c r="N442" t="n">
@@ -37266,7 +37274,7 @@
       </c>
       <c r="P442" t="inlineStr">
         <is>
-          <t>2006–07, 2007–08, 2008–09, 2010–11</t>
+          <t>1992–93, 1993–94, 1995–96, 1996–97</t>
         </is>
       </c>
       <c r="Q442" t="inlineStr"/>
@@ -37294,32 +37302,32 @@
       </c>
       <c r="AF442" t="inlineStr">
         <is>
-          <t>朴智星</t>
+          <t>埃里克·坎通纳</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>1210</v>
+        <v>2940</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Ronny Johnsen</t>
+          <t>Park Ji-Sung</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>1969/6/10</t>
+          <t>1981/2/25</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -37331,7 +37339,7 @@
       <c r="L443" t="inlineStr"/>
       <c r="M443" t="inlineStr"/>
       <c r="N443" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O443" t="inlineStr">
         <is>
@@ -37340,7 +37348,7 @@
       </c>
       <c r="P443" t="inlineStr">
         <is>
-          <t>1996–97, 1998–99, 2000–01</t>
+          <t>2006–07, 2007–08, 2008–09, 2010–11</t>
         </is>
       </c>
       <c r="Q443" t="inlineStr"/>
@@ -37368,63 +37376,55 @@
       </c>
       <c r="AF443" t="inlineStr">
         <is>
-          <t>罗尼·约翰森</t>
+          <t>朴智星</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>2117</v>
+        <v>1210</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Ruud van Nistelrooij</t>
+          <t>Ronny Johnsen</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>1976/7/1</t>
-        </is>
-      </c>
-      <c r="F444" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+          <t>1969/6/10</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr"/>
       <c r="H444" t="inlineStr"/>
-      <c r="I444" t="n">
-        <v>95</v>
-      </c>
+      <c r="I444" t="inlineStr"/>
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr"/>
-      <c r="L444" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="M444" t="inlineStr">
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="n">
+        <v>3</v>
+      </c>
+      <c r="O444" t="inlineStr">
         <is>
           <t>Manchester United</t>
         </is>
       </c>
-      <c r="N444" t="inlineStr"/>
-      <c r="O444" t="inlineStr"/>
-      <c r="P444" t="inlineStr"/>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>1996–97, 1998–99, 2000–01</t>
+        </is>
+      </c>
       <c r="Q444" t="inlineStr"/>
       <c r="R444" t="inlineStr"/>
       <c r="S444" t="inlineStr"/>
@@ -37434,16 +37434,8 @@
       <c r="W444" t="inlineStr"/>
       <c r="X444" t="inlineStr"/>
       <c r="Y444" t="inlineStr"/>
-      <c r="Z444" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="AA444" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="Z444" t="inlineStr"/>
+      <c r="AA444" t="inlineStr"/>
       <c r="AB444" t="inlineStr"/>
       <c r="AC444" t="inlineStr">
         <is>
@@ -37458,55 +37450,63 @@
       </c>
       <c r="AF444" t="inlineStr">
         <is>
-          <t>鲁德·范尼斯特鲁伊</t>
+          <t>罗尼·约翰森</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>19620</v>
+        <v>2117</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Oleksandr Zinchenko</t>
+          <t>Ruud van Nistelrooij</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>1996/12/15</t>
-        </is>
-      </c>
-      <c r="F445" t="inlineStr"/>
-      <c r="G445" t="inlineStr"/>
+          <t>1976/7/1</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="H445" t="inlineStr"/>
-      <c r="I445" t="inlineStr"/>
+      <c r="I445" t="n">
+        <v>95</v>
+      </c>
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr"/>
-      <c r="L445" t="inlineStr"/>
-      <c r="M445" t="inlineStr"/>
-      <c r="N445" t="n">
-        <v>4</v>
-      </c>
-      <c r="O445" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="P445" t="inlineStr">
-        <is>
-          <t>2017–18, 2018–19, 2020–21, 2021–22</t>
-        </is>
-      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr"/>
+      <c r="O445" t="inlineStr"/>
+      <c r="P445" t="inlineStr"/>
       <c r="Q445" t="inlineStr"/>
       <c r="R445" t="inlineStr"/>
       <c r="S445" t="inlineStr"/>
@@ -37516,42 +37516,46 @@
       <c r="W445" t="inlineStr"/>
       <c r="X445" t="inlineStr"/>
       <c r="Y445" t="inlineStr"/>
-      <c r="Z445" t="inlineStr"/>
-      <c r="AA445" t="inlineStr"/>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="AB445" t="inlineStr"/>
       <c r="AC445" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD445" t="inlineStr">
-        <is>
-          <t>Ajax</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD445" t="inlineStr"/>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>Manchester City;Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
         <is>
-          <t>奥列克桑德尔·津琴科</t>
+          <t>鲁德·范尼斯特鲁伊</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>319</v>
+        <v>19620</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Steve Bruce</t>
+          <t>Oleksandr Zinchenko</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -37561,7 +37565,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>1960/12/31</t>
+          <t>1996/12/15</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -37573,16 +37577,16 @@
       <c r="L446" t="inlineStr"/>
       <c r="M446" t="inlineStr"/>
       <c r="N446" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="P446" t="inlineStr">
         <is>
-          <t>1992–93, 1993–94, 1995–96</t>
+          <t>2017–18, 2018–19, 2020–21, 2021–22</t>
         </is>
       </c>
       <c r="Q446" t="inlineStr"/>
@@ -37599,43 +37603,47 @@
       <c r="AB446" t="inlineStr"/>
       <c r="AC446" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD446" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD446" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>Birmingham City;Manchester United</t>
+          <t>Manchester City;Arsenal</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
         <is>
-          <t>史蒂夫·布鲁斯</t>
+          <t>奥列克桑德尔·津琴科</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>3447</v>
+        <v>319</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Nani</t>
+          <t>Steve Bruce</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>1986/11/17</t>
+          <t>1960/12/31</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -37647,7 +37655,7 @@
       <c r="L447" t="inlineStr"/>
       <c r="M447" t="inlineStr"/>
       <c r="N447" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O447" t="inlineStr">
         <is>
@@ -37656,7 +37664,7 @@
       </c>
       <c r="P447" t="inlineStr">
         <is>
-          <t>2007–08, 2008–09, 2010–11, 2012–13</t>
+          <t>1992–93, 1993–94, 1995–96</t>
         </is>
       </c>
       <c r="Q447" t="inlineStr"/>
@@ -37679,27 +37687,27 @@
       <c r="AD447" t="inlineStr"/>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Birmingham City;Manchester United</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
         <is>
-          <t>纳尼</t>
+          <t>史蒂夫·布鲁斯</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>5110</v>
+        <v>3447</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Pierre-Emerick Aubameyang</t>
+          <t>Nani</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -37709,28 +37717,30 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>1989/6/18</t>
-        </is>
-      </c>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
+          <t>1986/11/17</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
       <c r="I448" t="inlineStr"/>
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr"/>
       <c r="L448" t="inlineStr"/>
       <c r="M448" t="inlineStr"/>
-      <c r="N448" t="inlineStr"/>
-      <c r="O448" t="inlineStr"/>
-      <c r="P448" t="inlineStr"/>
+      <c r="N448" t="n">
+        <v>4</v>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>2007–08, 2008–09, 2010–11, 2012–13</t>
+        </is>
+      </c>
       <c r="Q448" t="inlineStr"/>
       <c r="R448" t="inlineStr"/>
       <c r="S448" t="inlineStr"/>
@@ -37740,16 +37750,8 @@
       <c r="W448" t="inlineStr"/>
       <c r="X448" t="inlineStr"/>
       <c r="Y448" t="inlineStr"/>
-      <c r="Z448" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="AA448" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
+      <c r="Z448" t="inlineStr"/>
+      <c r="AA448" t="inlineStr"/>
       <c r="AB448" t="inlineStr"/>
       <c r="AC448" t="inlineStr">
         <is>
@@ -37759,60 +37761,58 @@
       <c r="AD448" t="inlineStr"/>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>Arsenal;Chelsea</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
         <is>
-          <t>皮埃尔-埃默里克·奥巴梅扬</t>
+          <t>纳尼</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>2654</v>
+        <v>5110</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Paulo Ferreira</t>
+          <t>Pierre-Emerick Aubameyang</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>1979/1/18</t>
-        </is>
-      </c>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr"/>
+          <t>1989/6/18</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr"/>
-      <c r="N449" t="n">
-        <v>3</v>
-      </c>
-      <c r="O449" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="P449" t="inlineStr">
-        <is>
-          <t>2004–05, 2005–06, 2009–10</t>
-        </is>
-      </c>
+      <c r="N449" t="inlineStr"/>
+      <c r="O449" t="inlineStr"/>
+      <c r="P449" t="inlineStr"/>
       <c r="Q449" t="inlineStr"/>
       <c r="R449" t="inlineStr"/>
       <c r="S449" t="inlineStr"/>
@@ -37822,8 +37822,16 @@
       <c r="W449" t="inlineStr"/>
       <c r="X449" t="inlineStr"/>
       <c r="Y449" t="inlineStr"/>
-      <c r="Z449" t="inlineStr"/>
-      <c r="AA449" t="inlineStr"/>
+      <c r="Z449" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="AB449" t="inlineStr"/>
       <c r="AC449" t="inlineStr">
         <is>
@@ -37833,22 +37841,22 @@
       <c r="AD449" t="inlineStr"/>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal;Chelsea</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
         <is>
-          <t>保罗·费雷拉</t>
+          <t>皮埃尔-埃默里克·奥巴梅扬</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Ricardo Carvalho</t>
+          <t>Paulo Ferreira</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -37863,7 +37871,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>1978/5/18</t>
+          <t>1979/1/18</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -37912,49 +37920,55 @@
       </c>
       <c r="AF450" t="inlineStr">
         <is>
-          <t>里卡多·卡瓦略</t>
+          <t>保罗·费雷拉</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>3543</v>
+        <v>2653</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Wojciech Szczesny</t>
+          <t>Ricardo Carvalho</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>1990/4/18</t>
+          <t>1978/5/18</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
+      <c r="H451" t="inlineStr"/>
       <c r="I451" t="inlineStr"/>
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr"/>
       <c r="M451" t="inlineStr"/>
-      <c r="N451" t="inlineStr"/>
-      <c r="O451" t="inlineStr"/>
-      <c r="P451" t="inlineStr"/>
+      <c r="N451" t="n">
+        <v>3</v>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>2004–05, 2005–06, 2009–10</t>
+        </is>
+      </c>
       <c r="Q451" t="inlineStr"/>
       <c r="R451" t="inlineStr"/>
       <c r="S451" t="inlineStr"/>
@@ -37975,65 +37989,51 @@
       <c r="AD451" t="inlineStr"/>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
         <is>
-          <t>沃伊切赫·什琴斯尼</t>
+          <t>里卡多·卡瓦略</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>65970</v>
+        <v>3543</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Erling Haaland</t>
+          <t>Wojciech Szczesny</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2000/7/21</t>
-        </is>
-      </c>
-      <c r="F452" t="inlineStr">
-        <is>
-          <t>2022, 2023</t>
-        </is>
-      </c>
-      <c r="G452" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
-      <c r="H452" t="inlineStr"/>
-      <c r="I452" t="n">
-        <v>107</v>
-      </c>
+          <t>1990/4/18</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr"/>
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr"/>
-      <c r="L452" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="M452" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
+      <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr"/>
       <c r="N452" t="inlineStr"/>
       <c r="O452" t="inlineStr"/>
       <c r="P452" t="inlineStr"/>
@@ -38046,74 +38046,76 @@
       <c r="W452" t="inlineStr"/>
       <c r="X452" t="inlineStr"/>
       <c r="Y452" t="inlineStr"/>
-      <c r="Z452" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="AA452" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
+      <c r="Z452" t="inlineStr"/>
+      <c r="AA452" t="inlineStr"/>
       <c r="AB452" t="inlineStr"/>
       <c r="AC452" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD452" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD452" t="inlineStr"/>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
         <is>
-          <t>埃尔林·哈兰德</t>
+          <t>沃伊切赫·什琴斯尼</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>4911</v>
+        <v>65970</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Thibaut Courtois</t>
+          <t>Erling Haaland</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>1992/5/11</t>
-        </is>
-      </c>
-      <c r="F453" t="inlineStr"/>
-      <c r="G453" t="inlineStr"/>
-      <c r="H453" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="I453" t="inlineStr"/>
+          <t>2000/7/21</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>2022, 2023</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr"/>
+      <c r="I453" t="n">
+        <v>107</v>
+      </c>
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr"/>
-      <c r="L453" t="inlineStr"/>
-      <c r="M453" t="inlineStr"/>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
       <c r="N453" t="inlineStr"/>
       <c r="O453" t="inlineStr"/>
       <c r="P453" t="inlineStr"/>
@@ -38126,66 +38128,74 @@
       <c r="W453" t="inlineStr"/>
       <c r="X453" t="inlineStr"/>
       <c r="Y453" t="inlineStr"/>
-      <c r="Z453" t="inlineStr"/>
-      <c r="AA453" t="inlineStr"/>
+      <c r="Z453" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="AA453" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="AB453" t="inlineStr"/>
       <c r="AC453" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD453" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD453" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
         <is>
-          <t>蒂博·库尔图瓦</t>
+          <t>埃尔林·哈兰德</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>1072</v>
+        <v>4911</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Juninho Paulista</t>
+          <t>Thibaut Courtois</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>1973/2/22</t>
+          <t>1992/5/11</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
       <c r="G454" t="inlineStr"/>
-      <c r="H454" t="inlineStr"/>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
       <c r="I454" t="inlineStr"/>
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr"/>
-      <c r="L454" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="M454" t="inlineStr">
-        <is>
-          <t>Middlesbrough</t>
-        </is>
-      </c>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr"/>
       <c r="N454" t="inlineStr"/>
       <c r="O454" t="inlineStr"/>
       <c r="P454" t="inlineStr"/>
@@ -38209,37 +38219,37 @@
       <c r="AD454" t="inlineStr"/>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
         <is>
-          <t>儒尼尼奥·保利斯塔</t>
+          <t>蒂博·库尔图瓦</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>11044</v>
+        <v>1072</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Aymeric Laporte</t>
+          <t>Juninho Paulista</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>1994/5/27</t>
+          <t>1973/2/22</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -38248,21 +38258,19 @@
       <c r="I455" t="inlineStr"/>
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr"/>
-      <c r="L455" t="inlineStr"/>
-      <c r="M455" t="inlineStr"/>
-      <c r="N455" t="n">
-        <v>5</v>
-      </c>
-      <c r="O455" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="P455" t="inlineStr">
-        <is>
-          <t>2017–18, 2018–19, 2020–21, 2021–22, 2022–23</t>
-        </is>
-      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr"/>
+      <c r="O455" t="inlineStr"/>
+      <c r="P455" t="inlineStr"/>
       <c r="Q455" t="inlineStr"/>
       <c r="R455" t="inlineStr"/>
       <c r="S455" t="inlineStr"/>
@@ -38283,66 +38291,60 @@
       <c r="AD455" t="inlineStr"/>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
         <is>
-          <t>艾梅里克·拉波尔特</t>
+          <t>儒尼尼奥·保利斯塔</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>4138</v>
+        <v>11044</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Luis Suárez</t>
+          <t>Aymeric Laporte</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>1987/1/24</t>
-        </is>
-      </c>
-      <c r="F456" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="G456" t="inlineStr">
-        <is>
-          <t>31.0</t>
-        </is>
-      </c>
+          <t>1994/5/27</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr"/>
       <c r="I456" t="inlineStr"/>
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr"/>
-      <c r="L456" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="M456" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="N456" t="inlineStr"/>
-      <c r="O456" t="inlineStr"/>
-      <c r="P456" t="inlineStr"/>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr"/>
+      <c r="N456" t="n">
+        <v>5</v>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>2017–18, 2018–19, 2020–21, 2021–22, 2022–23</t>
+        </is>
+      </c>
       <c r="Q456" t="inlineStr"/>
       <c r="R456" t="inlineStr"/>
       <c r="S456" t="inlineStr"/>
@@ -38352,16 +38354,8 @@
       <c r="W456" t="inlineStr"/>
       <c r="X456" t="inlineStr"/>
       <c r="Y456" t="inlineStr"/>
-      <c r="Z456" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="AA456" t="inlineStr">
-        <is>
-          <t>31.0</t>
-        </is>
-      </c>
+      <c r="Z456" t="inlineStr"/>
+      <c r="AA456" t="inlineStr"/>
       <c r="AB456" t="inlineStr"/>
       <c r="AC456" t="inlineStr">
         <is>
@@ -38371,60 +38365,66 @@
       <c r="AD456" t="inlineStr"/>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
         <is>
-          <t>路易斯·苏亚雷斯</t>
+          <t>艾梅里克·拉波尔特</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>3664</v>
+        <v>4138</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Luis Suárez</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>1990/7/9</t>
-        </is>
-      </c>
-      <c r="F457" t="inlineStr"/>
-      <c r="G457" t="inlineStr"/>
+          <t>1987/1/24</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="H457" t="inlineStr"/>
       <c r="I457" t="inlineStr"/>
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr"/>
-      <c r="L457" t="inlineStr"/>
-      <c r="M457" t="inlineStr"/>
-      <c r="N457" t="n">
-        <v>3</v>
-      </c>
-      <c r="O457" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="P457" t="inlineStr">
-        <is>
-          <t>2008–09, 2010–11, 2012–13</t>
-        </is>
-      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr"/>
+      <c r="O457" t="inlineStr"/>
+      <c r="P457" t="inlineStr"/>
       <c r="Q457" t="inlineStr"/>
       <c r="R457" t="inlineStr"/>
       <c r="S457" t="inlineStr"/>
@@ -38434,8 +38434,16 @@
       <c r="W457" t="inlineStr"/>
       <c r="X457" t="inlineStr"/>
       <c r="Y457" t="inlineStr"/>
-      <c r="Z457" t="inlineStr"/>
-      <c r="AA457" t="inlineStr"/>
+      <c r="Z457" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="AA457" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="AB457" t="inlineStr"/>
       <c r="AC457" t="inlineStr">
         <is>
@@ -38445,22 +38453,22 @@
       <c r="AD457" t="inlineStr"/>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
         <is>
-          <t>拉斐尔</t>
+          <t>路易斯·苏亚雷斯</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>3446</v>
+        <v>3664</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -38470,12 +38478,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>1988/4/13</t>
+          <t>1990/7/9</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -38487,7 +38495,7 @@
       <c r="L458" t="inlineStr"/>
       <c r="M458" t="inlineStr"/>
       <c r="N458" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O458" t="inlineStr">
         <is>
@@ -38496,7 +38504,7 @@
       </c>
       <c r="P458" t="inlineStr">
         <is>
-          <t>2007–08, 2008–09, 2010–11, 2012–13</t>
+          <t>2008–09, 2010–11, 2012–13</t>
         </is>
       </c>
       <c r="Q458" t="inlineStr"/>
@@ -38524,32 +38532,32 @@
       </c>
       <c r="AF458" t="inlineStr">
         <is>
-          <t>安德森</t>
+          <t>拉斐尔</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>5051</v>
+        <v>3446</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>João Cancelo</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>1994/5/27</t>
+          <t>1988/4/13</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -38561,16 +38569,16 @@
       <c r="L459" t="inlineStr"/>
       <c r="M459" t="inlineStr"/>
       <c r="N459" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="P459" t="inlineStr">
         <is>
-          <t>2020–21, 2021–22, 2022–23</t>
+          <t>2007–08, 2008–09, 2010–11, 2012–13</t>
         </is>
       </c>
       <c r="Q459" t="inlineStr"/>
@@ -38593,54 +38601,60 @@
       <c r="AD459" t="inlineStr"/>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
         <is>
-          <t>若昂·坎塞洛</t>
+          <t>安德森</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>16723</v>
+        <v>5051</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Matz Sels</t>
+          <t>João Cancelo</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>1992/2/26</t>
+          <t>1994/5/27</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="inlineStr"/>
-      <c r="H460" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
+      <c r="H460" t="inlineStr"/>
       <c r="I460" t="inlineStr"/>
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr"/>
       <c r="L460" t="inlineStr"/>
       <c r="M460" t="inlineStr"/>
-      <c r="N460" t="inlineStr"/>
-      <c r="O460" t="inlineStr"/>
-      <c r="P460" t="inlineStr"/>
+      <c r="N460" t="n">
+        <v>3</v>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>2020–21, 2021–22, 2022–23</t>
+        </is>
+      </c>
       <c r="Q460" t="inlineStr"/>
       <c r="R460" t="inlineStr"/>
       <c r="S460" t="inlineStr"/>
@@ -38655,70 +38669,60 @@
       <c r="AB460" t="inlineStr"/>
       <c r="AC460" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD460" t="inlineStr">
-        <is>
-          <t>Nottingham Forest</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD460" t="inlineStr"/>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>Newcastle United;Nottingham Forest</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
         <is>
-          <t>马茨·塞尔斯</t>
+          <t>若昂·坎塞洛</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>1580</v>
+        <v>16723</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Jaap Stam</t>
+          <t>Matz Sels</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>1972/7/17</t>
+          <t>1992/2/26</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="inlineStr"/>
-      <c r="H461" t="inlineStr"/>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
       <c r="I461" t="inlineStr"/>
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr"/>
       <c r="L461" t="inlineStr"/>
       <c r="M461" t="inlineStr"/>
-      <c r="N461" t="n">
-        <v>3</v>
-      </c>
-      <c r="O461" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="P461" t="inlineStr">
-        <is>
-          <t>1998–99, 1999–2000, 2000–01</t>
-        </is>
-      </c>
+      <c r="N461" t="inlineStr"/>
+      <c r="O461" t="inlineStr"/>
+      <c r="P461" t="inlineStr"/>
       <c r="Q461" t="inlineStr"/>
       <c r="R461" t="inlineStr"/>
       <c r="S461" t="inlineStr"/>
@@ -38733,43 +38737,47 @@
       <c r="AB461" t="inlineStr"/>
       <c r="AC461" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD461" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD461" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Newcastle United;Nottingham Forest</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
         <is>
-          <t>雅普·斯塔姆</t>
+          <t>马茨·塞尔斯</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>2818</v>
+        <v>1580</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Tomasz Kuszczak</t>
+          <t>Jaap Stam</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>1982/3/20</t>
+          <t>1972/7/17</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -38790,7 +38798,7 @@
       </c>
       <c r="P462" t="inlineStr">
         <is>
-          <t>2006–07, 2007–08, 2010–11</t>
+          <t>1998–99, 1999–2000, 2000–01</t>
         </is>
       </c>
       <c r="Q462" t="inlineStr"/>
@@ -38813,37 +38821,37 @@
       <c r="AD462" t="inlineStr"/>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>Birmingham City;Manchester United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
         <is>
-          <t>托马什·库什恰克</t>
+          <t>雅普·斯塔姆</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>5575</v>
+        <v>2818</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Benjamin Mendy</t>
+          <t>Tomasz Kuszczak</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>1994/7/17</t>
+          <t>1982/3/20</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -38859,12 +38867,12 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="P463" t="inlineStr">
         <is>
-          <t>2017–18, 2018–19, 2020–21</t>
+          <t>2006–07, 2007–08, 2010–11</t>
         </is>
       </c>
       <c r="Q463" t="inlineStr"/>
@@ -38887,37 +38895,37 @@
       <c r="AD463" t="inlineStr"/>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Birmingham City;Manchester United</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
         <is>
-          <t>本杰明·门迪</t>
+          <t>托马什·库什恰克</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>48285</v>
+        <v>5575</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Aaron Ramsey</t>
+          <t>Benjamin Mendy</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>2003/1/21</t>
+          <t>1994/7/17</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -38928,40 +38936,28 @@
       <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr"/>
       <c r="M464" t="inlineStr"/>
-      <c r="N464" t="inlineStr"/>
-      <c r="O464" t="inlineStr"/>
-      <c r="P464" t="inlineStr"/>
-      <c r="Q464" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="R464" t="n">
-        <v>262</v>
-      </c>
-      <c r="S464" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="N464" t="n">
+        <v>3</v>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>2017–18, 2018–19, 2020–21</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr"/>
+      <c r="R464" t="inlineStr"/>
+      <c r="S464" t="inlineStr"/>
       <c r="T464" t="inlineStr"/>
-      <c r="U464" t="n">
-        <v>0</v>
-      </c>
-      <c r="V464" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U464" t="inlineStr"/>
+      <c r="V464" t="inlineStr"/>
       <c r="W464" t="inlineStr"/>
-      <c r="X464" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y464" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X464" t="inlineStr"/>
+      <c r="Y464" t="inlineStr"/>
       <c r="Z464" t="inlineStr"/>
       <c r="AA464" t="inlineStr"/>
       <c r="AB464" t="inlineStr"/>
@@ -38971,8 +38967,94 @@
         </is>
       </c>
       <c r="AD464" t="inlineStr"/>
-      <c r="AE464" t="inlineStr"/>
-      <c r="AF464" t="inlineStr"/>
+      <c r="AE464" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="AF464" t="inlineStr">
+        <is>
+          <t>本杰明·门迪</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>48285</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Aaron Ramsey</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>2003/1/21</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr"/>
+      <c r="N465" t="inlineStr"/>
+      <c r="O465" t="inlineStr"/>
+      <c r="P465" t="inlineStr"/>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="R465" t="n">
+        <v>262</v>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr"/>
+      <c r="U465" t="n">
+        <v>0</v>
+      </c>
+      <c r="V465" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W465" t="inlineStr"/>
+      <c r="X465" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y465" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z465" t="inlineStr"/>
+      <c r="AA465" t="inlineStr"/>
+      <c r="AB465" t="inlineStr"/>
+      <c r="AC465" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD465" t="inlineStr"/>
+      <c r="AE465" t="inlineStr"/>
+      <c r="AF465" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -2605,7 +2605,7 @@
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -4884,11 +4884,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1190</v>
+        <v>3452</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lee Bowyer</t>
+          <t>Danny Welbeck</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4898,18 +4898,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1977/1/3</t>
+          <t>1990/11/26</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>89</v>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -4917,66 +4919,48 @@
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Leeds United</t>
-        </is>
-      </c>
-      <c r="R48" t="n">
-        <v>203</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>Leeds United;West Ham United;Newcastle United;Birmingham City</t>
+          <t>Manchester United;Arsenal;Watford;Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>李·博耶</t>
+          <t>丹尼·维尔贝克</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3452</v>
+        <v>2839</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Danny Welbeck</t>
+          <t>Theo Walcott</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4991,15 +4975,13 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1990/11/26</t>
+          <t>1989/3/16</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="n">
-        <v>89</v>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -5007,15 +4989,37 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>270</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="n">
@@ -5023,32 +5027,28 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>Brighton &amp; Hove Albion</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>Manchester United;Arsenal;Watford;Brighton &amp; Hove Albion</t>
+          <t>Arsenal;Everton;Southampton</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>丹尼·维尔贝克</t>
+          <t>西奥·沃尔科特</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2839</v>
+        <v>1190</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Theo Walcott</t>
+          <t>Lee Bowyer</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1989/3/16</t>
+          <t>1977/1/3</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -5079,11 +5079,11 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5121,12 +5121,12 @@
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>Arsenal;Everton;Southampton</t>
+          <t>Leeds United;West Ham United;Newcastle United;Birmingham City</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>西奥·沃尔科特</t>
+          <t>李·博耶</t>
         </is>
       </c>
     </row>
@@ -9128,16 +9128,16 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>8143</v>
+        <v>5140</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>James Tarkowski</t>
+          <t>Virgil van Dijk</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1992/11/19</t>
+          <t>1991/7/8</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -9156,18 +9156,26 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="R98" t="n">
-        <v>194</v>
+        <v>270</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9204,32 +9212,32 @@
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>Everton FC</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>Burnley;Everton</t>
+          <t>Southampton;Liverpool</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>詹姆斯·塔科夫斯基</t>
+          <t>维吉尔·范迪克</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>5140</v>
+        <v>8143</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Virgil van Dijk</t>
+          <t>James Tarkowski</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -9239,7 +9247,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1991/7/8</t>
+          <t>1992/11/19</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -9248,26 +9256,18 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="R99" t="n">
-        <v>269</v>
+        <v>194</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
@@ -9304,17 +9304,17 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Everton FC</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>Southampton;Liverpool</t>
+          <t>Burnley;Everton</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>维吉尔·范迪克</t>
+          <t>詹姆斯·塔科夫斯基</t>
         </is>
       </c>
     </row>
@@ -14754,16 +14754,16 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>300</v>
+        <v>5067</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Garry Flitcroft</t>
+          <t>Bernardo Silva</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1972/11/6</t>
+          <t>1994/8/10</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -14784,20 +14784,30 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
+      <c r="N164" t="n">
+        <v>6</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>2017–18, 2018–19, 2020–21, 2021–22, 2022–23, 2023–24</t>
+        </is>
+      </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="R164" t="n">
-        <v>186</v>
+        <v>301</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="T164" t="inlineStr"/>
@@ -14825,18 +14835,22 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
         <is>
-          <t>加里·弗利特克罗夫特</t>
+          <t>贝尔纳多·席尔瓦</t>
         </is>
       </c>
     </row>
@@ -14908,16 +14922,16 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>5067</v>
+        <v>300</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Bernardo Silva</t>
+          <t>Garry Flitcroft</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -14927,7 +14941,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1994/8/10</t>
+          <t>1972/11/6</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -14938,30 +14952,20 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr"/>
-      <c r="N166" t="n">
-        <v>6</v>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>2017–18, 2018–19, 2020–21, 2021–22, 2022–23, 2023–24</t>
-        </is>
-      </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="R166" t="n">
-        <v>300</v>
+        <v>186</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="T166" t="inlineStr"/>
@@ -14985,26 +14989,22 @@
       <c r="Z166" t="inlineStr"/>
       <c r="AA166" t="inlineStr"/>
       <c r="AB166" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr"/>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
         <is>
-          <t>贝尔纳多·席尔瓦</t>
+          <t>加里·弗利特克罗夫特</t>
         </is>
       </c>
     </row>
@@ -15098,39 +15098,33 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2911</v>
+        <v>8163</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Pepe Reina</t>
+          <t>Lewis Dunk</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>1982/8/31</t>
+          <t>1991/11/21</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>18.0, 19.0, 20.0</t>
-        </is>
-      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="n">
-        <v>136</v>
-      </c>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
@@ -15139,15 +15133,15 @@
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="R168" t="n">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="T168" t="inlineStr"/>
@@ -15175,28 +15169,32 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD168" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>Liverpool;Aston Villa</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
         <is>
-          <t>佩佩·雷纳</t>
+          <t>路易斯·邓克</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>13565</v>
+        <v>2681</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Marcus Rashford</t>
+          <t>Wayne Routledge</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -15206,20 +15204,18 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>1997/10/31</t>
+          <t>1985/1/7</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
-      <c r="I169" t="n">
-        <v>89</v>
-      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
@@ -15229,11 +15225,11 @@
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="R169" t="n">
-        <v>287</v>
+        <v>198</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -15265,54 +15261,56 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>FC Barcelona</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr"/>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
         <is>
-          <t>马库斯·拉什福德</t>
+          <t>韦恩·劳特利奇</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2681</v>
+        <v>2911</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Wayne Routledge</t>
+          <t>Pepe Reina</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1985/1/7</t>
+          <t>1982/8/31</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>18.0, 19.0, 20.0</t>
+        </is>
+      </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
+      <c r="J170" t="n">
+        <v>136</v>
+      </c>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
@@ -15321,11 +15319,11 @@
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="R170" t="n">
-        <v>198</v>
+        <v>285</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -15363,27 +15361,27 @@
       <c r="AD170" t="inlineStr"/>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Liverpool;Aston Villa</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
         <is>
-          <t>韦恩·劳特利奇</t>
+          <t>佩佩·雷纳</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>339</v>
+        <v>13565</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mark Hughes</t>
+          <t>Marcus Rashford</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -15393,13 +15391,15 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1963/11/1</t>
+          <t>1997/10/31</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
+      <c r="I171" t="n">
+        <v>89</v>
+      </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
@@ -15407,15 +15407,37 @@
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="R171" t="n">
+        <v>287</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T171" t="inlineStr"/>
-      <c r="U171" t="inlineStr"/>
-      <c r="V171" t="inlineStr"/>
+      <c r="U171" t="n">
+        <v>0</v>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W171" t="inlineStr"/>
-      <c r="X171" t="inlineStr"/>
-      <c r="Y171" t="inlineStr"/>
+      <c r="X171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z171" t="inlineStr"/>
       <c r="AA171" t="inlineStr"/>
       <c r="AB171" t="n">
@@ -15423,43 +15445,47 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD171" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>Manchester United;Chelsea;Southampton;Everton;Blackburn Rovers</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
         <is>
-          <t>马克·休斯</t>
+          <t>马库斯·拉什福德</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>8163</v>
+        <v>339</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Lewis Dunk</t>
+          <t>Mark Hughes</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1991/11/21</t>
+          <t>1963/11/1</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -15473,60 +15499,34 @@
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>Brighton &amp; Hove Albion</t>
-        </is>
-      </c>
-      <c r="R172" t="n">
-        <v>296</v>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
+      <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
-      <c r="U172" t="n">
-        <v>0</v>
-      </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr"/>
       <c r="W172" t="inlineStr"/>
-      <c r="X172" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X172" t="inlineStr"/>
+      <c r="Y172" t="inlineStr"/>
       <c r="Z172" t="inlineStr"/>
       <c r="AA172" t="inlineStr"/>
       <c r="AB172" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>Brighton &amp; Hove Albion</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr"/>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Manchester United;Chelsea;Southampton;Everton;Blackburn Rovers</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
         <is>
-          <t>路易斯·邓克</t>
+          <t>马克·休斯</t>
         </is>
       </c>
     </row>
@@ -15818,26 +15818,26 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1869</v>
+        <v>4608</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Craig Bellamy</t>
+          <t>Luke Shaw</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1979/7/13</t>
+          <t>1995/7/12</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -15851,59 +15851,85 @@
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="R177" t="n">
+        <v>234</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="T177" t="inlineStr"/>
-      <c r="U177" t="inlineStr"/>
-      <c r="V177" t="inlineStr"/>
+      <c r="U177" t="n">
+        <v>0</v>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W177" t="inlineStr"/>
-      <c r="X177" t="inlineStr"/>
-      <c r="Y177" t="inlineStr"/>
+      <c r="X177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z177" t="inlineStr"/>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>Coventry City;Newcastle United;Blackburn Rovers;Liverpool;West Ham United;Manchester City;Cardiff City</t>
+          <t>Manchester United;Southampton</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
         <is>
-          <t>克雷格·贝拉米</t>
+          <t>卢克·肖</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>4608</v>
+        <v>1869</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Luke Shaw</t>
+          <t>Craig Bellamy</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1995/7/12</t>
+          <t>1979/7/13</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -15917,37 +15943,15 @@
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="R178" t="n">
-        <v>233</v>
-      </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
-      <c r="U178" t="n">
-        <v>0</v>
-      </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
       <c r="W178" t="inlineStr"/>
-      <c r="X178" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X178" t="inlineStr"/>
+      <c r="Y178" t="inlineStr"/>
       <c r="Z178" t="inlineStr"/>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="n">
@@ -15955,22 +15959,18 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr"/>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>Manchester United;Southampton</t>
+          <t>Coventry City;Newcastle United;Blackburn Rovers;Liverpool;West Ham United;Manchester City;Cardiff City</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
         <is>
-          <t>卢克·肖</t>
+          <t>克雷格·贝拉米</t>
         </is>
       </c>
     </row>
@@ -16532,26 +16532,26 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>4288</v>
+        <v>9566</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Kevin De Bruyne</t>
+          <t>Harry Maguire</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1991/6/28</t>
+          <t>1993/3/5</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -16560,108 +16560,64 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>2019, 2021</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="N187" t="n">
-        <v>6</v>
-      </c>
-      <c r="O187" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="P187" t="inlineStr">
-        <is>
-          <t>2017–18, 2018–19, 2020–21, 2021–22, 2022–23, 2023–24</t>
-        </is>
-      </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="R187" t="n">
-        <v>285</v>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
-      <c r="U187" t="n">
-        <v>0</v>
-      </c>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
       <c r="W187" t="inlineStr"/>
-      <c r="X187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X187" t="inlineStr"/>
+      <c r="Y187" t="inlineStr"/>
       <c r="Z187" t="inlineStr"/>
       <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD187" t="inlineStr">
-        <is>
-          <t>SSC Napoli</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr"/>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>Chelsea;Manchester City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>凯文·德布劳内</t>
+          <t>哈里·马奎尔</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2058</v>
+        <v>4288</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Carlton Cole</t>
+          <t>Kevin De Bruyne</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>1983/10/12</t>
+          <t>1991/6/28</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -16670,18 +16626,36 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>2019, 2021</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>6</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>2017–18, 2018–19, 2020–21, 2021–22, 2022–23, 2023–24</t>
+        </is>
+      </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="R188" t="n">
-        <v>216</v>
+        <v>285</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -16713,18 +16687,22 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD188" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>SSC Napoli</t>
+        </is>
+      </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea;Manchester City</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
         <is>
-          <t>卡尔顿·科尔</t>
+          <t>凯文·德布劳内</t>
         </is>
       </c>
     </row>
@@ -16968,11 +16946,11 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1772</v>
+        <v>2058</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Matthew Etherington</t>
+          <t>Carlton Cole</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -16982,12 +16960,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>1981/8/14</t>
+          <t>1983/10/12</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -17001,15 +16979,37 @@
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="R192" t="n">
+        <v>216</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T192" t="inlineStr"/>
-      <c r="U192" t="inlineStr"/>
-      <c r="V192" t="inlineStr"/>
+      <c r="U192" t="n">
+        <v>0</v>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W192" t="inlineStr"/>
-      <c r="X192" t="inlineStr"/>
-      <c r="Y192" t="inlineStr"/>
+      <c r="X192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z192" t="inlineStr"/>
       <c r="AA192" t="inlineStr"/>
       <c r="AB192" t="n">
@@ -17023,22 +17023,22 @@
       <c r="AD192" t="inlineStr"/>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
         <is>
-          <t>马修·埃瑟林顿</t>
+          <t>卡尔顿·科尔</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1131</v>
+        <v>1772</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Matt Upson</t>
+          <t>Matthew Etherington</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -17048,12 +17048,12 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>1979/4/18</t>
+          <t>1981/8/14</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -17089,22 +17089,22 @@
       <c r="AD193" t="inlineStr"/>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>Arsenal;Birmingham City;West Ham United;Stoke City;Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
         <is>
-          <t>马特·厄普森</t>
+          <t>马修·埃瑟林顿</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>9566</v>
+        <v>1131</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Harry Maguire</t>
+          <t>Matt Upson</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -17119,7 +17119,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>1993/3/5</t>
+          <t>1979/4/18</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -17155,12 +17155,12 @@
       <c r="AD194" t="inlineStr"/>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal;Birmingham City;West Ham United;Stoke City;Leicester City</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
         <is>
-          <t>哈里·马奎尔</t>
+          <t>马特·厄普森</t>
         </is>
       </c>
     </row>
@@ -24274,26 +24274,26 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>228</v>
+        <v>12136</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>David Wetherall</t>
+          <t>Granit Xhaka</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>1971/3/14</t>
+          <t>1992/9/27</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -24309,11 +24309,11 @@
       <c r="P284" t="inlineStr"/>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="R284" t="n">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
@@ -24345,43 +24345,47 @@
       </c>
       <c r="AC284" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD284" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>Sunderland AFC</t>
+        </is>
+      </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Sunderland;Arsenal</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
         <is>
-          <t>大卫·韦瑟雷尔</t>
+          <t>格拉尼特·扎卡</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>12136</v>
+        <v>228</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Granit Xhaka</t>
+          <t>David Wetherall</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>1992/9/27</t>
+          <t>1971/3/14</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -24397,11 +24401,11 @@
       <c r="P285" t="inlineStr"/>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="R285" t="n">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="S285" t="inlineStr">
         <is>
@@ -24429,26 +24433,22 @@
       <c r="Z285" t="inlineStr"/>
       <c r="AA285" t="inlineStr"/>
       <c r="AB285" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AC285" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD285" t="inlineStr">
-        <is>
-          <t>Sunderland AFC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD285" t="inlineStr"/>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>Sunderland;Arsenal</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
         <is>
-          <t>格拉尼特·扎卡</t>
+          <t>大卫·韦瑟雷尔</t>
         </is>
       </c>
     </row>
@@ -25286,66 +25286,46 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>2662</v>
+        <v>3512</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Didier Drogba</t>
+          <t>Adam Smith</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Cote D’Ivoire</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>1978/3/11</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>2006, 2009</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>20.0, 29.0</t>
-        </is>
-      </c>
+          <t>1991/4/29</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr"/>
-      <c r="I296" t="n">
-        <v>104</v>
-      </c>
+      <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr"/>
-      <c r="N296" t="n">
-        <v>4</v>
-      </c>
-      <c r="O296" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="P296" t="inlineStr">
-        <is>
-          <t>2004–05, 2005–06, 2009–10, 2014–15</t>
-        </is>
-      </c>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="R296" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S296" t="inlineStr">
         <is>
@@ -25370,78 +25350,94 @@
           <t>no</t>
         </is>
       </c>
-      <c r="Z296" t="inlineStr">
-        <is>
-          <t>2006, 2009</t>
-        </is>
-      </c>
-      <c r="AA296" t="inlineStr">
-        <is>
-          <t>20.0, 29.0</t>
-        </is>
-      </c>
+      <c r="Z296" t="inlineStr"/>
+      <c r="AA296" t="inlineStr"/>
       <c r="AB296" t="n">
         <v>254</v>
       </c>
       <c r="AC296" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD296" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD296" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth</t>
+        </is>
+      </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
         <is>
-          <t>迪迪埃·德罗巴</t>
+          <t>亚当·史密斯</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>3512</v>
+        <v>2662</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Adam Smith</t>
+          <t>Didier Drogba</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Cote D’Ivoire</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>1991/4/29</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
+          <t>1978/3/11</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>2006, 2009</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>20.0, 29.0</t>
+        </is>
+      </c>
       <c r="H297" t="inlineStr"/>
-      <c r="I297" t="inlineStr"/>
+      <c r="I297" t="n">
+        <v>104</v>
+      </c>
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr"/>
-      <c r="O297" t="inlineStr"/>
-      <c r="P297" t="inlineStr"/>
+      <c r="N297" t="n">
+        <v>4</v>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>2004–05, 2005–06, 2009–10, 2014–15</t>
+        </is>
+      </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="R297" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="S297" t="inlineStr">
         <is>
@@ -25466,29 +25462,33 @@
           <t>no</t>
         </is>
       </c>
-      <c r="Z297" t="inlineStr"/>
-      <c r="AA297" t="inlineStr"/>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>2006, 2009</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>20.0, 29.0</t>
+        </is>
+      </c>
       <c r="AB297" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AC297" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD297" t="inlineStr">
-        <is>
-          <t>AFC Bournemouth</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD297" t="inlineStr"/>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
         <is>
-          <t>亚当·史密斯</t>
+          <t>迪迪埃·德罗巴</t>
         </is>
       </c>
     </row>
@@ -25936,26 +25936,26 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>958</v>
+        <v>5758</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Matt Oakley</t>
+          <t>Lucas Digne</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>1977/8/17</t>
+          <t>1993/7/20</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
@@ -25969,37 +25969,15 @@
       <c r="N304" t="inlineStr"/>
       <c r="O304" t="inlineStr"/>
       <c r="P304" t="inlineStr"/>
-      <c r="Q304" t="inlineStr">
-        <is>
-          <t>Southampton</t>
-        </is>
-      </c>
-      <c r="R304" t="n">
-        <v>232</v>
-      </c>
-      <c r="S304" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q304" t="inlineStr"/>
+      <c r="R304" t="inlineStr"/>
+      <c r="S304" t="inlineStr"/>
       <c r="T304" t="inlineStr"/>
-      <c r="U304" t="n">
-        <v>0</v>
-      </c>
-      <c r="V304" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U304" t="inlineStr"/>
+      <c r="V304" t="inlineStr"/>
       <c r="W304" t="inlineStr"/>
-      <c r="X304" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y304" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X304" t="inlineStr"/>
+      <c r="Y304" t="inlineStr"/>
       <c r="Z304" t="inlineStr"/>
       <c r="AA304" t="inlineStr"/>
       <c r="AB304" t="n">
@@ -26007,18 +25985,22 @@
       </c>
       <c r="AC304" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD304" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD304" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Aston Villa;Everton</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
         <is>
-          <t>马特·奥克利</t>
+          <t>卢卡斯·迪涅</t>
         </is>
       </c>
     </row>
@@ -26090,26 +26072,26 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>5758</v>
+        <v>958</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Lucas Digne</t>
+          <t>Matt Oakley</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>1993/7/20</t>
+          <t>1977/8/17</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -26123,15 +26105,37 @@
       <c r="N306" t="inlineStr"/>
       <c r="O306" t="inlineStr"/>
       <c r="P306" t="inlineStr"/>
-      <c r="Q306" t="inlineStr"/>
-      <c r="R306" t="inlineStr"/>
-      <c r="S306" t="inlineStr"/>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="R306" t="n">
+        <v>232</v>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T306" t="inlineStr"/>
-      <c r="U306" t="inlineStr"/>
-      <c r="V306" t="inlineStr"/>
+      <c r="U306" t="n">
+        <v>0</v>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W306" t="inlineStr"/>
-      <c r="X306" t="inlineStr"/>
-      <c r="Y306" t="inlineStr"/>
+      <c r="X306" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z306" t="inlineStr"/>
       <c r="AA306" t="inlineStr"/>
       <c r="AB306" t="n">
@@ -26139,47 +26143,43 @@
       </c>
       <c r="AC306" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD306" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD306" t="inlineStr"/>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>Aston Villa;Everton</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
         <is>
-          <t>卢卡斯·迪涅</t>
+          <t>马特·奥克利</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>2041</v>
+        <v>4499</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Ricardo Gardner</t>
+          <t>Nathan Aké</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>1978/9/25</t>
+          <t>1995/2/18</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -26190,40 +26190,28 @@
       <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr"/>
       <c r="M307" t="inlineStr"/>
-      <c r="N307" t="inlineStr"/>
-      <c r="O307" t="inlineStr"/>
-      <c r="P307" t="inlineStr"/>
-      <c r="Q307" t="inlineStr">
-        <is>
-          <t>Bolton Wanderers</t>
-        </is>
-      </c>
-      <c r="R307" t="n">
-        <v>251</v>
-      </c>
-      <c r="S307" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="N307" t="n">
+        <v>4</v>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>2020–21, 2021–22, 2022–23, 2023–24</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr"/>
+      <c r="R307" t="inlineStr"/>
+      <c r="S307" t="inlineStr"/>
       <c r="T307" t="inlineStr"/>
-      <c r="U307" t="n">
-        <v>0</v>
-      </c>
-      <c r="V307" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U307" t="inlineStr"/>
+      <c r="V307" t="inlineStr"/>
       <c r="W307" t="inlineStr"/>
-      <c r="X307" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y307" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X307" t="inlineStr"/>
+      <c r="Y307" t="inlineStr"/>
       <c r="Z307" t="inlineStr"/>
       <c r="AA307" t="inlineStr"/>
       <c r="AB307" t="n">
@@ -26231,43 +26219,47 @@
       </c>
       <c r="AC307" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD307" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD307" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Manchester City;Bournemouth</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
         <is>
-          <t>里卡多·加德纳</t>
+          <t>内森·阿克</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>4499</v>
+        <v>2041</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Nathan Aké</t>
+          <t>Ricardo Gardner</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>1995/2/18</t>
+          <t>1978/9/25</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -26278,51 +26270,59 @@
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr"/>
-      <c r="N308" t="n">
-        <v>4</v>
-      </c>
-      <c r="O308" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="P308" t="inlineStr">
-        <is>
-          <t>2020–21, 2021–22, 2022–23, 2023–24</t>
-        </is>
-      </c>
-      <c r="Q308" t="inlineStr"/>
-      <c r="R308" t="inlineStr"/>
-      <c r="S308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="R308" t="n">
+        <v>251</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T308" t="inlineStr"/>
-      <c r="U308" t="inlineStr"/>
-      <c r="V308" t="inlineStr"/>
+      <c r="U308" t="n">
+        <v>0</v>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W308" t="inlineStr"/>
-      <c r="X308" t="inlineStr"/>
-      <c r="Y308" t="inlineStr"/>
+      <c r="X308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z308" t="inlineStr"/>
       <c r="AA308" t="inlineStr"/>
       <c r="AB308" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AC308" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD308" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD308" t="inlineStr"/>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>Manchester City;Bournemouth</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
         <is>
-          <t>内森·阿克</t>
+          <t>里卡多·加德纳</t>
         </is>
       </c>
     </row>
@@ -26394,26 +26394,26 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>3102</v>
+        <v>4985</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>John Obi Mikel</t>
+          <t>Bernd Leno</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>1987/4/22</t>
+          <t>1992/3/4</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -26427,37 +26427,15 @@
       <c r="N310" t="inlineStr"/>
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="inlineStr"/>
-      <c r="Q310" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="R310" t="n">
-        <v>249</v>
-      </c>
-      <c r="S310" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q310" t="inlineStr"/>
+      <c r="R310" t="inlineStr"/>
+      <c r="S310" t="inlineStr"/>
       <c r="T310" t="inlineStr"/>
-      <c r="U310" t="n">
-        <v>0</v>
-      </c>
-      <c r="V310" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U310" t="inlineStr"/>
+      <c r="V310" t="inlineStr"/>
       <c r="W310" t="inlineStr"/>
-      <c r="X310" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y310" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X310" t="inlineStr"/>
+      <c r="Y310" t="inlineStr"/>
       <c r="Z310" t="inlineStr"/>
       <c r="AA310" t="inlineStr"/>
       <c r="AB310" t="n">
@@ -26465,33 +26443,37 @@
       </c>
       <c r="AC310" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD310" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD310" t="inlineStr">
+        <is>
+          <t>Fulham FC</t>
+        </is>
+      </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>Stoke City;Chelsea</t>
+          <t>Fulham;Arsenal</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
         <is>
-          <t>约翰·奥比·米克尔</t>
+          <t>伯恩德·莱诺</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>670</v>
+        <v>3102</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Muzzy Izzet</t>
+          <t>John Obi Mikel</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Turkiye</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -26501,7 +26483,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1974/10/31</t>
+          <t>1987/4/22</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -26517,11 +26499,11 @@
       <c r="P311" t="inlineStr"/>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="R311" t="n">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -26549,7 +26531,7 @@
       <c r="Z311" t="inlineStr"/>
       <c r="AA311" t="inlineStr"/>
       <c r="AB311" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AC311" t="inlineStr">
         <is>
@@ -26559,37 +26541,37 @@
       <c r="AD311" t="inlineStr"/>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City;Chelsea</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
         <is>
-          <t>穆齐·伊泽特</t>
+          <t>约翰·奥比·米克尔</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>4985</v>
+        <v>670</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Bernd Leno</t>
+          <t>Muzzy Izzet</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Turkiye</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>1992/3/4</t>
+          <t>1974/10/31</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -26603,15 +26585,37 @@
       <c r="N312" t="inlineStr"/>
       <c r="O312" t="inlineStr"/>
       <c r="P312" t="inlineStr"/>
-      <c r="Q312" t="inlineStr"/>
-      <c r="R312" t="inlineStr"/>
-      <c r="S312" t="inlineStr"/>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>Leicester City</t>
+        </is>
+      </c>
+      <c r="R312" t="n">
+        <v>222</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T312" t="inlineStr"/>
-      <c r="U312" t="inlineStr"/>
-      <c r="V312" t="inlineStr"/>
+      <c r="U312" t="n">
+        <v>0</v>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W312" t="inlineStr"/>
-      <c r="X312" t="inlineStr"/>
-      <c r="Y312" t="inlineStr"/>
+      <c r="X312" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z312" t="inlineStr"/>
       <c r="AA312" t="inlineStr"/>
       <c r="AB312" t="n">
@@ -26619,22 +26623,18 @@
       </c>
       <c r="AC312" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD312" t="inlineStr">
-        <is>
-          <t>Fulham FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD312" t="inlineStr"/>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>Fulham;Arsenal</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
         <is>
-          <t>伯恩德·莱诺</t>
+          <t>穆齐·伊泽特</t>
         </is>
       </c>
     </row>
@@ -27480,16 +27480,16 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>598</v>
+        <v>22542</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Robbie Earle</t>
+          <t>Pascal Groß</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -27499,7 +27499,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>1965/1/27</t>
+          <t>1991/6/15</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
@@ -27513,34 +27513,60 @@
       <c r="N324" t="inlineStr"/>
       <c r="O324" t="inlineStr"/>
       <c r="P324" t="inlineStr"/>
-      <c r="Q324" t="inlineStr"/>
-      <c r="R324" t="inlineStr"/>
-      <c r="S324" t="inlineStr"/>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="R324" t="n">
+        <v>245</v>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="T324" t="inlineStr"/>
-      <c r="U324" t="inlineStr"/>
-      <c r="V324" t="inlineStr"/>
+      <c r="U324" t="n">
+        <v>0</v>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W324" t="inlineStr"/>
-      <c r="X324" t="inlineStr"/>
-      <c r="Y324" t="inlineStr"/>
+      <c r="X324" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z324" t="inlineStr"/>
       <c r="AA324" t="inlineStr"/>
       <c r="AB324" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AC324" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD324" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>Wimbledon</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
         <is>
-          <t>罗比·厄尔</t>
+          <t>帕斯卡尔·格罗斯</t>
         </is>
       </c>
     </row>
@@ -27612,16 +27638,16 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>22542</v>
+        <v>598</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Pascal Groß</t>
+          <t>Robbie Earle</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -27631,7 +27657,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>1991/6/15</t>
+          <t>1965/1/27</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
@@ -27645,37 +27671,15 @@
       <c r="N326" t="inlineStr"/>
       <c r="O326" t="inlineStr"/>
       <c r="P326" t="inlineStr"/>
-      <c r="Q326" t="inlineStr">
-        <is>
-          <t>Brighton &amp; Hove Albion</t>
-        </is>
-      </c>
-      <c r="R326" t="n">
-        <v>244</v>
-      </c>
-      <c r="S326" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="Q326" t="inlineStr"/>
+      <c r="R326" t="inlineStr"/>
+      <c r="S326" t="inlineStr"/>
       <c r="T326" t="inlineStr"/>
-      <c r="U326" t="n">
-        <v>0</v>
-      </c>
-      <c r="V326" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U326" t="inlineStr"/>
+      <c r="V326" t="inlineStr"/>
       <c r="W326" t="inlineStr"/>
-      <c r="X326" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y326" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X326" t="inlineStr"/>
+      <c r="Y326" t="inlineStr"/>
       <c r="Z326" t="inlineStr"/>
       <c r="AA326" t="inlineStr"/>
       <c r="AB326" t="n">
@@ -27683,22 +27687,18 @@
       </c>
       <c r="AC326" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD326" t="inlineStr">
-        <is>
-          <t>Brighton &amp; Hove Albion</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD326" t="inlineStr"/>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wimbledon</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
         <is>
-          <t>帕斯卡尔·格罗斯</t>
+          <t>罗比·厄尔</t>
         </is>
       </c>
     </row>
@@ -32141,7 +32141,7 @@
         </is>
       </c>
       <c r="R383" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="S383" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         </is>
       </c>
       <c r="R390" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="S390" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         </is>
       </c>
       <c r="R425" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="S425" t="inlineStr">
         <is>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -20926,16 +20926,16 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1502</v>
+        <v>24630</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Kanu</t>
+          <t>Richarlison</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>1976/8/1</t>
+          <t>1997/5/10</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -20975,43 +20975,47 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD242" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Tottenham Hotspur;Everton</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
         <is>
-          <t>卡努</t>
+          <t>理查利森</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>80</v>
+        <v>1502</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Jason Wilcox</t>
+          <t>Kanu</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>1971/7/15</t>
+          <t>1976/8/1</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -21025,37 +21029,15 @@
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr"/>
-      <c r="Q243" t="inlineStr">
-        <is>
-          <t>Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="R243" t="n">
-        <v>192</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr"/>
+      <c r="S243" t="inlineStr"/>
       <c r="T243" t="inlineStr"/>
-      <c r="U243" t="n">
-        <v>0</v>
-      </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U243" t="inlineStr"/>
+      <c r="V243" t="inlineStr"/>
       <c r="W243" t="inlineStr"/>
-      <c r="X243" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y243" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X243" t="inlineStr"/>
+      <c r="Y243" t="inlineStr"/>
       <c r="Z243" t="inlineStr"/>
       <c r="AA243" t="inlineStr"/>
       <c r="AB243" t="n">
@@ -21069,27 +21051,27 @@
       <c r="AD243" t="inlineStr"/>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>Leicester City;Blackburn Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
         <is>
-          <t>贾森·威尔考克斯</t>
+          <t>卡努</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>3979</v>
+        <v>80</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>James McCarthy</t>
+          <t>Jason Wilcox</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -21099,7 +21081,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>1990/11/12</t>
+          <t>1971/7/15</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -21113,19 +21095,41 @@
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr"/>
-      <c r="R244" t="inlineStr"/>
-      <c r="S244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="R244" t="n">
+        <v>192</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T244" t="inlineStr"/>
-      <c r="U244" t="inlineStr"/>
-      <c r="V244" t="inlineStr"/>
+      <c r="U244" t="n">
+        <v>0</v>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W244" t="inlineStr"/>
-      <c r="X244" t="inlineStr"/>
-      <c r="Y244" t="inlineStr"/>
+      <c r="X244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z244" t="inlineStr"/>
       <c r="AA244" t="inlineStr"/>
       <c r="AB244" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AC244" t="inlineStr">
         <is>
@@ -21135,27 +21139,27 @@
       <c r="AD244" t="inlineStr"/>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>Wigan Athletic;Everton;Crystal Palace</t>
+          <t>Leicester City;Blackburn Rovers</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
         <is>
-          <t>詹姆斯·麦卡锡</t>
+          <t>贾森·威尔考克斯</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>24630</v>
+        <v>9576</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Richarlison</t>
+          <t>Dominic Calvert-Lewin</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -21165,7 +21169,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>1997/5/10</t>
+          <t>1997/3/16</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -21179,15 +21183,37 @@
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
-      <c r="R245" t="inlineStr"/>
-      <c r="S245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="R245" t="n">
+        <v>239</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T245" t="inlineStr"/>
-      <c r="U245" t="inlineStr"/>
-      <c r="V245" t="inlineStr"/>
+      <c r="U245" t="n">
+        <v>0</v>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W245" t="inlineStr"/>
-      <c r="X245" t="inlineStr"/>
-      <c r="Y245" t="inlineStr"/>
+      <c r="X245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z245" t="inlineStr"/>
       <c r="AA245" t="inlineStr"/>
       <c r="AB245" t="n">
@@ -21200,42 +21226,42 @@
       </c>
       <c r="AD245" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Everton</t>
+          <t>Leeds United;Everton</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
         <is>
-          <t>理查利森</t>
+          <t>多米尼克·卡尔弗特-卢因</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>9576</v>
+        <v>3979</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Dominic Calvert-Lewin</t>
+          <t>James McCarthy</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>1997/3/16</t>
+          <t>1990/11/12</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -21249,60 +21275,34 @@
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr"/>
-      <c r="Q246" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="R246" t="n">
-        <v>239</v>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
+      <c r="S246" t="inlineStr"/>
       <c r="T246" t="inlineStr"/>
-      <c r="U246" t="n">
-        <v>0</v>
-      </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U246" t="inlineStr"/>
+      <c r="V246" t="inlineStr"/>
       <c r="W246" t="inlineStr"/>
-      <c r="X246" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X246" t="inlineStr"/>
+      <c r="Y246" t="inlineStr"/>
       <c r="Z246" t="inlineStr"/>
       <c r="AA246" t="inlineStr"/>
       <c r="AB246" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD246" t="inlineStr">
-        <is>
-          <t>Leeds United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr"/>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>Leeds United;Everton</t>
+          <t>Wigan Athletic;Everton;Crystal Palace</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
         <is>
-          <t>多米尼克·卡尔弗特-卢因</t>
+          <t>詹姆斯·麦卡锡</t>
         </is>
       </c>
     </row>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -1781,7 +1781,7 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Arsenal;Newcastle United</t>
+          <t>Tottenham Hotspur;Arsenal;Portsmouth;Newcastle United</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Aston Villa;Manchester United;Everton</t>
+          <t>Aston Villa;Manchester United;Everton;Watford</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2437,7 +2437,7 @@
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Newcastle United;Manchester City;Portsmouth;Everton</t>
+          <t>Newcastle United;Manchester City;Portsmouth;Everton;Bournemouth</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2605,7 +2605,7 @@
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>Southampton;West Ham United;Burnley</t>
+          <t>Southampton;West Ham United;Nottingham Forest;Burnley</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -3973,7 +3973,7 @@
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Manchester United;Portsmouth;West Ham United</t>
+          <t>Nottingham Forest;Tottenham Hotspur;Manchester United;Portsmouth;West Ham United</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4505,7 +4505,7 @@
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>Manchester United;Newcastle United</t>
+          <t>Manchester United;Newcastle United;Birmingham City</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -4931,7 +4931,7 @@
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
       <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>Leeds United;Tottenham Hotspur;Blackburn Rovers</t>
+          <t>Leeds United;Tottenham Hotspur;Blackburn Rovers;Burnley</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -6556,26 +6556,26 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>146</v>
+        <v>3600</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nigel Martyn</t>
+          <t>Séamus Coleman</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1966/8/11</t>
+          <t>1988/10/11</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -6588,16 +6588,14 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="n">
-        <v>141</v>
-      </c>
+      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="R67" t="n">
-        <v>207</v>
+        <v>372</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6625,47 +6623,51 @@
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Everton FC</t>
+        </is>
+      </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>Crystal Palace;Leeds United;Everton</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>奈杰尔·马丁</t>
+          <t>谢默斯·科尔曼</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3600</v>
+        <v>146</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Séamus Coleman</t>
+          <t>Nigel Martyn</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1988/10/11</t>
+          <t>1966/8/11</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -6678,14 +6680,16 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>141</v>
+      </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>372</v>
+        <v>207</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6717,22 +6721,18 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>Everton FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr"/>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Crystal Palace;Leeds United;Everton</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>谢默斯·科尔曼</t>
+          <t>奈杰尔·马丁</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
       <c r="AD89" t="inlineStr"/>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>Charlton Athletic;West Ham United;Fulham;Liverpool</t>
+          <t>Charlton Athletic;Tottenham Hotspur;West Ham United;Fulham;Liverpool;Leicester City</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -9195,7 +9195,7 @@
       <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="R99" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
@@ -10158,16 +10158,16 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1208</v>
+        <v>5178</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Michael Owen</t>
+          <t>Mohamed Salah</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -10177,29 +10177,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1979/12/14</t>
+          <t>1992/6/15</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>1997, 1998</t>
+          <t>2017, 2018, 2021, 2024</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>22.0, 23.0, 29.0, 32.0</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2017, 2024</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="R110" t="n">
-        <v>216</v>
+        <v>314</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10242,46 +10242,50 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>1997, 1998</t>
+          <t>2017, 2018, 2021, 2024</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>18.0, 18.0</t>
+          <t>32.0, 22.0, 23.0, 29.0</t>
         </is>
       </c>
       <c r="AB110" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>Liverpool;Newcastle United;Manchester United;Stoke City</t>
+          <t>Chelsea;Liverpool</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>迈克尔·欧文</t>
+          <t>穆罕默德·萨拉赫</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>5178</v>
+        <v>1208</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mohamed Salah</t>
+          <t>Michael Owen</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -10291,29 +10295,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1992/6/15</t>
+          <t>1979/12/14</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2017, 2018, 2021, 2024</t>
+          <t>1997, 1998</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>22.0, 23.0, 29.0, 32.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2017, 2024</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -10329,7 +10333,7 @@
         </is>
       </c>
       <c r="R111" t="n">
-        <v>313</v>
+        <v>216</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10356,12 +10360,12 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>2017, 2018, 2021, 2024</t>
+          <t>1997, 1998</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>32.0, 22.0, 23.0, 29.0</t>
+          <t>18.0, 18.0</t>
         </is>
       </c>
       <c r="AB111" t="n">
@@ -10369,22 +10373,18 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD111" t="inlineStr">
-        <is>
-          <t>Liverpool FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr"/>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>Chelsea;Liverpool</t>
+          <t>Liverpool;Newcastle United;Manchester United;Stoke City</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>穆罕默德·萨拉赫</t>
+          <t>迈克尔·欧文</t>
         </is>
       </c>
     </row>
@@ -11533,7 +11533,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Tottenham Hotspur; Norwich City</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -11544,26 +11544,26 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>566</v>
+        <v>4717</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Darren Anderton</t>
+          <t>Alex Iwobi</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1972/3/3</t>
+          <t>1996/5/3</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -11577,37 +11577,15 @@
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>Tottenham Hotspur</t>
-        </is>
-      </c>
-      <c r="R126" t="n">
-        <v>297</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr"/>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="inlineStr"/>
       <c r="AA126" t="inlineStr"/>
       <c r="AB126" t="n">
@@ -11615,18 +11593,22 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>Fulham FC</t>
+        </is>
+      </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Birmingham City;Portsmouth</t>
+          <t>Arsenal;Everton;Fulham</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
         <is>
-          <t>达伦·安德顿</t>
+          <t>亚历克斯·伊沃比</t>
         </is>
       </c>
     </row>
@@ -11720,11 +11702,11 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125</v>
+        <v>566</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Peter Atherton</t>
+          <t>Darren Anderton</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -11734,12 +11716,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1970/4/6</t>
+          <t>1972/3/3</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -11755,11 +11737,11 @@
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="R128" t="n">
-        <v>214</v>
+        <v>297</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -11787,7 +11769,7 @@
       <c r="Z128" t="inlineStr"/>
       <c r="AA128" t="inlineStr"/>
       <c r="AB128" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
@@ -11797,37 +11779,37 @@
       <c r="AD128" t="inlineStr"/>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>Coventry City;Sheffield Wednesday;Blackburn Rovers</t>
+          <t>Tottenham Hotspur;Birmingham City;Portsmouth</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>彼得·阿瑟顿</t>
+          <t>达伦·安德顿</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>4421</v>
+        <v>1710</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Gylfi Sigurdsson</t>
+          <t>Sami Hyypiä</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1989/9/8</t>
+          <t>1973/10/7</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -11841,15 +11823,37 @@
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="R129" t="n">
+        <v>318</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T129" t="inlineStr"/>
-      <c r="U129" t="inlineStr"/>
-      <c r="V129" t="inlineStr"/>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr"/>
-      <c r="Y129" t="inlineStr"/>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z129" t="inlineStr"/>
       <c r="AA129" t="inlineStr"/>
       <c r="AB129" t="n">
@@ -11857,47 +11861,43 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>Víkingur Reykjavík</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr"/>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>Swansea City;Tottenham Hotspur;Everton</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>吉尔菲·西于尔兹松</t>
+          <t>萨米·海皮亚</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>4717</v>
+        <v>4421</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Alex Iwobi</t>
+          <t>Gylfi Sigurdsson</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>1996/5/3</t>
+          <t>1989/9/8</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -11932,32 +11932,32 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Fulham FC</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>Arsenal;Everton;Fulham</t>
+          <t>Swansea City;Tottenham Hotspur;Everton</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>亚历克斯·伊沃比</t>
+          <t>吉尔菲·西于尔兹松</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1710</v>
+        <v>125</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Sami Hyypiä</t>
+          <t>Peter Atherton</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1973/10/7</t>
+          <t>1970/4/6</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -11983,11 +11983,11 @@
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="R131" t="n">
-        <v>318</v>
+        <v>214</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -12025,12 +12025,12 @@
       <c r="AD131" t="inlineStr"/>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Coventry City;Sheffield Wednesday;Blackburn Rovers</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>萨米·海皮亚</t>
+          <t>彼得·阿瑟顿</t>
         </is>
       </c>
     </row>
@@ -12205,7 +12205,7 @@
       <c r="AD133" t="inlineStr"/>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>Manchester United;Stoke City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -12371,7 +12371,7 @@
       <c r="AD135" t="inlineStr"/>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>Southampton;Chelsea;Fulham;Manchester City;Sunderland</t>
+          <t>Southampton;Chelsea;Fulham;Manchester City;West Ham United;Sunderland</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -13895,7 +13895,7 @@
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Aston Villa;Blackburn Rovers;Middlesbrough;Sheffield United</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -13961,7 +13961,7 @@
       <c r="AD153" t="inlineStr"/>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Southampton;Liverpool;Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Crystal Palace;Manchester United;Cardiff City</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Burnley;Southampton;Swansea City</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -14314,16 +14314,16 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1775</v>
+        <v>4115</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Simon Davies</t>
+          <t>Ross Barkley</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -14333,7 +14333,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1979/10/23</t>
+          <t>1993/12/5</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -14359,37 +14359,41 @@
       <c r="Z158" t="inlineStr"/>
       <c r="AA158" t="inlineStr"/>
       <c r="AB158" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Everton;Chelsea;Aston Villa;Luton Town</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
         <is>
-          <t>西蒙·戴维斯</t>
+          <t>罗斯·巴克利</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>4198</v>
+        <v>2517</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Craig Dawson</t>
+          <t>Phil Bardsley</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -14399,7 +14403,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1990/5/6</t>
+          <t>1985/6/28</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -14429,43 +14433,43 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr"/>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>West Bromwich Albion;Watford;West Ham United;Wolverhampton Wanderers</t>
+          <t>Manchester United;Sunderland;Stoke City;Burnley</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
         <is>
-          <t>克雷格·道森</t>
+          <t>菲尔·巴兹利</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2517</v>
+        <v>1775</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Phil Bardsley</t>
+          <t>Simon Davies</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1985/6/28</t>
+          <t>1979/10/23</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -14501,22 +14505,22 @@
       <c r="AD160" t="inlineStr"/>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>Manchester United;Sunderland;Stoke City;Burnley</t>
+          <t>Fulham;Everton;Tottenham Hotspur</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
         <is>
-          <t>菲尔·巴兹利</t>
+          <t>西蒙·戴维斯</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>4115</v>
+        <v>4198</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ross Barkley</t>
+          <t>Craig Dawson</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -14526,12 +14530,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>1993/12/5</t>
+          <t>1990/5/6</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -14564,19 +14568,15 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
+      <c r="AD161" t="inlineStr"/>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>Aston Villa;Chelsea</t>
+          <t>West Bromwich Albion;Watford;West Ham United;Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
         <is>
-          <t>罗斯·巴克利</t>
+          <t>克雷格·道森</t>
         </is>
       </c>
     </row>
@@ -14659,7 +14659,7 @@
       <c r="AD162" t="inlineStr"/>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Newcastle United;Aston Villa;West Ham United</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -14937,7 +14937,7 @@
       <c r="AD165" t="inlineStr"/>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Blackburn Rovers;Manchester City;Sheffield United</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -15091,7 +15091,7 @@
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Newcastle United;Crystal Palace</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -15102,11 +15102,11 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2681</v>
+        <v>8163</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Wayne Routledge</t>
+          <t>Lewis Dunk</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>1985/1/7</t>
+          <t>1991/11/21</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -15137,15 +15137,15 @@
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="R168" t="n">
-        <v>198</v>
+        <v>297</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="T168" t="inlineStr"/>
@@ -15169,22 +15169,26 @@
       <c r="Z168" t="inlineStr"/>
       <c r="AA168" t="inlineStr"/>
       <c r="AB168" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD168" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
         <is>
-          <t>韦恩·劳特利奇</t>
+          <t>路易斯·邓克</t>
         </is>
       </c>
     </row>
@@ -15256,26 +15260,26 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>8163</v>
+        <v>2911</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Lewis Dunk</t>
+          <t>Pepe Reina</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1991/11/21</t>
+          <t>1982/8/31</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -15284,22 +15288,28 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>18.0, 19.0, 20.0</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
+      <c r="P170" t="n">
+        <v>136</v>
+      </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="R170" t="n">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="T170" t="inlineStr"/>
@@ -15327,22 +15337,18 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>Brighton &amp; Hove Albion</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr"/>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Liverpool;Aston Villa</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
         <is>
-          <t>路易斯·邓克</t>
+          <t>佩佩·雷纳</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15437,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Manchester United;Aston Villa</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -15442,26 +15448,26 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2911</v>
+        <v>2681</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Pepe Reina</t>
+          <t>Wayne Routledge</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1982/8/31</t>
+          <t>1985/1/7</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -15470,24 +15476,18 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>18.0, 19.0, 20.0</t>
-        </is>
-      </c>
+      <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
-      <c r="P172" t="n">
-        <v>136</v>
-      </c>
+      <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="R172" t="n">
-        <v>285</v>
+        <v>198</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -15525,12 +15525,12 @@
       <c r="AD172" t="inlineStr"/>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>Liverpool;Aston Villa</t>
+          <t>Swansea City;Crystal Palace;Tottenham Hotspur;Aston Villa;Fulham;Newcastle United;Portsmouth</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
         <is>
-          <t>佩佩·雷纳</t>
+          <t>韦恩·劳特利奇</t>
         </is>
       </c>
     </row>
@@ -15672,11 +15672,11 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>262</v>
+        <v>4608</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jamie Redknapp</t>
+          <t>Luke Shaw</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -15686,12 +15686,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1973/6/25</t>
+          <t>1995/7/12</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -15707,15 +15707,15 @@
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="R175" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="T175" t="inlineStr"/>
@@ -15743,28 +15743,32 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Manchester United;Southampton</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
         <is>
-          <t>杰米·雷德克纳普</t>
+          <t>卢克·肖</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>111</v>
+        <v>262</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Graham Stuart</t>
+          <t>Jamie Redknapp</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -15779,7 +15783,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1970/10/24</t>
+          <t>1973/6/25</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -15793,19 +15797,41 @@
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="R176" t="n">
+        <v>231</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T176" t="inlineStr"/>
-      <c r="U176" t="inlineStr"/>
-      <c r="V176" t="inlineStr"/>
+      <c r="U176" t="n">
+        <v>0</v>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W176" t="inlineStr"/>
-      <c r="X176" t="inlineStr"/>
-      <c r="Y176" t="inlineStr"/>
+      <c r="X176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z176" t="inlineStr"/>
       <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
@@ -15815,22 +15841,22 @@
       <c r="AD176" t="inlineStr"/>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>Everton;Charlton Athletic</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
         <is>
-          <t>格雷厄姆·斯图尔特</t>
+          <t>杰米·雷德克纳普</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>4608</v>
+        <v>111</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Luke Shaw</t>
+          <t>Graham Stuart</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -15840,12 +15866,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1995/7/12</t>
+          <t>1970/10/24</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -15859,37 +15885,15 @@
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="R177" t="n">
-        <v>234</v>
-      </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr"/>
-      <c r="U177" t="n">
-        <v>0</v>
-      </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
       <c r="W177" t="inlineStr"/>
-      <c r="X177" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X177" t="inlineStr"/>
+      <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="inlineStr"/>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="n">
@@ -15897,22 +15901,18 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr"/>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>Manchester United;Southampton</t>
+          <t>Chelsea;Everton;Charlton Athletic;Norwich City</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
         <is>
-          <t>卢克·肖</t>
+          <t>格雷厄姆·斯图尔特</t>
         </is>
       </c>
     </row>
@@ -16039,7 +16039,7 @@
       <c r="AD179" t="inlineStr"/>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Ipswich Town;Newcastle United;Wigan Athletic;Sunderland</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -16241,7 +16241,7 @@
       <c r="AD182" t="inlineStr"/>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton;Birmingham City;Blackburn Rovers</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -16252,16 +16252,16 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1246</v>
+        <v>9566</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Claus Lundekvam</t>
+          <t>Harry Maguire</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>1973/2/22</t>
+          <t>1993/3/5</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -16285,37 +16285,15 @@
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>Southampton</t>
-        </is>
-      </c>
-      <c r="R183" t="n">
-        <v>290</v>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
-      <c r="U183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
       <c r="W183" t="inlineStr"/>
-      <c r="X183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X183" t="inlineStr"/>
+      <c r="Y183" t="inlineStr"/>
       <c r="Z183" t="inlineStr"/>
       <c r="AA183" t="inlineStr"/>
       <c r="AB183" t="n">
@@ -16323,33 +16301,37 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Hull City;Leicester City;Manchester United</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
         <is>
-          <t>克劳斯·伦德克瓦姆</t>
+          <t>哈里·马奎尔</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>3517</v>
+        <v>1246</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>James Tomkins</t>
+          <t>Claus Lundekvam</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -16359,7 +16341,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1989/3/29</t>
+          <t>1973/2/22</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -16373,19 +16355,41 @@
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
-      <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="R184" t="n">
+        <v>290</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T184" t="inlineStr"/>
-      <c r="U184" t="inlineStr"/>
-      <c r="V184" t="inlineStr"/>
+      <c r="U184" t="n">
+        <v>0</v>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W184" t="inlineStr"/>
-      <c r="X184" t="inlineStr"/>
-      <c r="Y184" t="inlineStr"/>
+      <c r="X184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z184" t="inlineStr"/>
       <c r="AA184" t="inlineStr"/>
       <c r="AB184" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AC184" t="inlineStr">
         <is>
@@ -16395,12 +16399,12 @@
       <c r="AD184" t="inlineStr"/>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>West Ham United;Crystal Palace</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
         <is>
-          <t>詹姆斯·汤姆金斯</t>
+          <t>克劳斯·伦德克瓦姆</t>
         </is>
       </c>
     </row>
@@ -16472,32 +16476,34 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>9566</v>
+        <v>1598</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Harry Maguire</t>
+          <t>Louis Saha</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1993/3/5</t>
+          <t>1978/8/8</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
+      <c r="I186" t="n">
+        <v>84</v>
+      </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
@@ -16521,55 +16527,49 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr"/>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Newcastle United;Fulham;Manchester United;Everton;Tottenham Hotspur;Sunderland</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
         <is>
-          <t>哈里·马奎尔</t>
+          <t>路易斯·萨哈</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1598</v>
+        <v>3517</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Louis Saha</t>
+          <t>James Tomkins</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1978/8/8</t>
+          <t>1989/3/29</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
-      <c r="I187" t="n">
-        <v>84</v>
-      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
@@ -16599,12 +16599,12 @@
       <c r="AD187" t="inlineStr"/>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>Newcastle United;Fulham;Manchester United;Everton;Tottenham Hotspur;Sunderland</t>
+          <t>West Ham United;Crystal Palace</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>路易斯·萨哈</t>
+          <t>詹姆斯·汤姆金斯</t>
         </is>
       </c>
     </row>
@@ -16665,7 +16665,7 @@
       <c r="AD188" t="inlineStr"/>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Tottenham Hotspur;West Ham United;Stoke City</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -16973,7 +16973,7 @@
       <c r="AD192" t="inlineStr"/>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea;Charlton Athletic;Aston Villa;West Ham United</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -17457,7 +17457,7 @@
       <c r="AD198" t="inlineStr"/>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Leicester City;Middlesbrough;Sheffield United;Leeds United</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -17602,26 +17602,26 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2508</v>
+        <v>4333</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Kasper Schmeichel</t>
+          <t>Michael Keane</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>1986/11/5</t>
+          <t>1993/1/11</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -17634,16 +17634,14 @@
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
-      <c r="P201" t="n">
-        <v>83</v>
-      </c>
+      <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="R201" t="n">
-        <v>276</v>
+        <v>227</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -17671,7 +17669,7 @@
       <c r="Z201" t="inlineStr"/>
       <c r="AA201" t="inlineStr"/>
       <c r="AB201" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AC201" t="inlineStr">
         <is>
@@ -17680,17 +17678,17 @@
       </c>
       <c r="AD201" t="inlineStr">
         <is>
-          <t>Celtic FC</t>
+          <t>Everton FC</t>
         </is>
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Everton;Burnley</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
         <is>
-          <t>卡斯帕·舒梅切尔</t>
+          <t>迈克尔·基恩</t>
         </is>
       </c>
     </row>
@@ -17762,60 +17760,72 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>8983</v>
+        <v>2508</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Riyad Mahrez</t>
+          <t>Kasper Schmeichel</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>1991/2/21</t>
-        </is>
-      </c>
-      <c r="F203" t="n">
-        <v>5</v>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>Leicester City (1), Manchester City (4)</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>2015–16, 2018–19, 2020–21, 2021–22, 2022–23</t>
-        </is>
-      </c>
-      <c r="I203" t="n">
-        <v>82</v>
-      </c>
+          <t>1986/11/5</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
-      <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr"/>
+      <c r="P203" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>Leicester City</t>
+        </is>
+      </c>
+      <c r="R203" t="n">
+        <v>276</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T203" t="inlineStr"/>
-      <c r="U203" t="inlineStr"/>
-      <c r="V203" t="inlineStr"/>
+      <c r="U203" t="n">
+        <v>0</v>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W203" t="inlineStr"/>
-      <c r="X203" t="inlineStr"/>
-      <c r="Y203" t="inlineStr"/>
+      <c r="X203" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z203" t="inlineStr"/>
       <c r="AA203" t="inlineStr"/>
       <c r="AB203" t="n">
@@ -17828,17 +17838,17 @@
       </c>
       <c r="AD203" t="inlineStr">
         <is>
-          <t>Al-Ahli SFC</t>
+          <t>Celtic FC</t>
         </is>
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>Leicester City;Manchester City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
         <is>
-          <t>里亚德·马赫雷斯</t>
+          <t>卡斯帕·舒梅切尔</t>
         </is>
       </c>
     </row>
@@ -17910,32 +17920,44 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>4333</v>
+        <v>8983</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Michael Keane</t>
+          <t>Riyad Mahrez</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>1993/1/11</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
+          <t>1991/2/21</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>5</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Leicester City (1), Manchester City (4)</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>2015–16, 2018–19, 2020–21, 2021–22, 2022–23</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>82</v>
+      </c>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
@@ -17943,37 +17965,15 @@
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="R205" t="n">
-        <v>227</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr"/>
-      <c r="U205" t="n">
-        <v>0</v>
-      </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
       <c r="W205" t="inlineStr"/>
-      <c r="X205" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X205" t="inlineStr"/>
+      <c r="Y205" t="inlineStr"/>
       <c r="Z205" t="inlineStr"/>
       <c r="AA205" t="inlineStr"/>
       <c r="AB205" t="n">
@@ -17986,17 +17986,17 @@
       </c>
       <c r="AD205" t="inlineStr">
         <is>
-          <t>Everton FC</t>
+          <t>Al-Ahli SFC</t>
         </is>
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>Everton;Burnley</t>
+          <t>Leicester City;Manchester City</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
         <is>
-          <t>迈克尔·基恩</t>
+          <t>里亚德·马赫雷斯</t>
         </is>
       </c>
     </row>
@@ -18255,7 +18255,7 @@
       <c r="AD209" t="inlineStr"/>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Aston Villa;Wigan Athletic;Newcastle United</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -18559,7 +18559,7 @@
       <c r="AD213" t="inlineStr"/>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Bolton Wanderers;Bradford City;Portsmouth;Newcastle United</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -18739,7 +18739,7 @@
       <c r="AD215" t="inlineStr"/>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Newcastle United;Derby County</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -18899,7 +18899,7 @@
       <c r="AD217" t="inlineStr"/>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>Blackburn Rovers;West Ham United</t>
+          <t>Blackburn Rovers;West Ham United;Everton</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -19293,7 +19293,7 @@
       <c r="AD222" t="inlineStr"/>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Manchester United;West Ham United</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -19353,10 +19353,14 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD223" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>Melbourne Victory</t>
+        </is>
+      </c>
       <c r="AE223" t="inlineStr">
         <is>
           <t>Chelsea;Manchester United</t>
@@ -19447,7 +19451,7 @@
       <c r="AD224" t="inlineStr"/>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Chelsea;Leicester City</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -19458,32 +19462,34 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>4604</v>
+        <v>3756</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Nathaniel Clyne</t>
+          <t>Chris Wood</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1991/4/5</t>
+          <t>1991/12/7</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
+      <c r="I225" t="n">
+        <v>91</v>
+      </c>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
@@ -19507,18 +19513,22 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD225" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>Crystal Palace;Liverpool;Southampton;Bournemouth</t>
+          <t>Nottingham Forest;Burnley;Newcastle United;Leicester City;West Bromwich Albion</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
         <is>
-          <t>内森尼尔·克莱因</t>
+          <t>克里斯·伍德</t>
         </is>
       </c>
     </row>
@@ -19590,11 +19600,11 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>3909</v>
+        <v>4604</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Ben Mee</t>
+          <t>Nathaniel Clyne</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -19609,7 +19619,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1989/9/21</t>
+          <t>1991/4/5</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -19623,37 +19633,15 @@
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="R227" t="n">
-        <v>217</v>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr"/>
+      <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
-      <c r="U227" t="n">
-        <v>0</v>
-      </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr"/>
       <c r="W227" t="inlineStr"/>
-      <c r="X227" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X227" t="inlineStr"/>
+      <c r="Y227" t="inlineStr"/>
       <c r="Z227" t="inlineStr"/>
       <c r="AA227" t="inlineStr"/>
       <c r="AB227" t="n">
@@ -19666,32 +19654,32 @@
       </c>
       <c r="AD227" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>Brentford;Burnley</t>
+          <t>Crystal Palace;Liverpool;Southampton;Bournemouth</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
         <is>
-          <t>本·米</t>
+          <t>内森尼尔·克莱因</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>259</v>
+        <v>3909</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Dominic Matteo</t>
+          <t>Ben Mee</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -19701,7 +19689,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>1974/4/28</t>
+          <t>1989/9/21</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -19715,34 +19703,60 @@
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
-      <c r="R228" t="inlineStr"/>
-      <c r="S228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="R228" t="n">
+        <v>217</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T228" t="inlineStr"/>
-      <c r="U228" t="inlineStr"/>
-      <c r="V228" t="inlineStr"/>
+      <c r="U228" t="n">
+        <v>0</v>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W228" t="inlineStr"/>
-      <c r="X228" t="inlineStr"/>
-      <c r="Y228" t="inlineStr"/>
+      <c r="X228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z228" t="inlineStr"/>
       <c r="AA228" t="inlineStr"/>
       <c r="AB228" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD228" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>Liverpool;Leeds United;Blackburn Rovers;Stoke City</t>
+          <t>Brentford;Burnley</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
         <is>
-          <t>多米尼克·马特奥</t>
+          <t>本·米</t>
         </is>
       </c>
     </row>
@@ -19917,7 +19931,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>Blackburn Rovers;Southampton</t>
+          <t>Norwich City; Southampton; Burnley</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -20104,34 +20118,32 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>3756</v>
+        <v>259</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Chris Wood</t>
+          <t>Dominic Matteo</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>1991/12/7</t>
+          <t>1974/4/28</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
-      <c r="I233" t="n">
-        <v>91</v>
-      </c>
+      <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr"/>
@@ -20155,22 +20167,18 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD233" t="inlineStr">
-        <is>
-          <t>Nottingham Forest</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr"/>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Liverpool;Leeds United;Blackburn Rovers;Stoke City</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
         <is>
-          <t>克里斯·伍德</t>
+          <t>多米尼克·马特奥</t>
         </is>
       </c>
     </row>
@@ -20253,7 +20261,7 @@
       <c r="AD234" t="inlineStr"/>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Liverpool;Manchester City</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -20565,7 +20573,7 @@
       <c r="AD237" t="inlineStr"/>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Manchester United;Arsenal</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -20653,7 +20661,7 @@
       <c r="AD238" t="inlineStr"/>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leeds United;Liverpool</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -21001,7 +21009,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Everton</t>
+          <t>Tottenham Hotspur;Everton;Watford</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -21067,7 +21075,7 @@
       <c r="AD243" t="inlineStr"/>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Portsmouth;Arsenal;West Bromwich Albion</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -21233,7 +21241,7 @@
       <c r="Z245" t="inlineStr"/>
       <c r="AA245" t="inlineStr"/>
       <c r="AB245" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AC245" t="inlineStr">
         <is>
@@ -21379,7 +21387,7 @@
       <c r="AD247" t="inlineStr"/>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Sunderland;Middlesbrough;Wigan Athletic</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -21460,11 +21468,11 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>533</v>
+        <v>8454</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Matthew Le Tissier</t>
+          <t>Callum Wilson</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -21474,19 +21482,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>1968/10/14</t>
+          <t>1992/2/27</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
@@ -21495,37 +21503,15 @@
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
       <c r="P249" t="inlineStr"/>
-      <c r="Q249" t="inlineStr">
-        <is>
-          <t>Southampton</t>
-        </is>
-      </c>
-      <c r="R249" t="n">
-        <v>270</v>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q249" t="inlineStr"/>
+      <c r="R249" t="inlineStr"/>
+      <c r="S249" t="inlineStr"/>
       <c r="T249" t="inlineStr"/>
-      <c r="U249" t="n">
-        <v>0</v>
-      </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U249" t="inlineStr"/>
+      <c r="V249" t="inlineStr"/>
       <c r="W249" t="inlineStr"/>
-      <c r="X249" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X249" t="inlineStr"/>
+      <c r="Y249" t="inlineStr"/>
       <c r="Z249" t="inlineStr"/>
       <c r="AA249" t="inlineStr"/>
       <c r="AB249" t="n">
@@ -21533,33 +21519,37 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD249" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bournemouth;Newcastle United;West Ham United</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
         <is>
-          <t>马修·勒蒂西耶</t>
+          <t>卡勒姆·威尔逊</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>3744</v>
+        <v>533</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Chris Brunt</t>
+          <t>Matthew Le Tissier</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Northern Ireland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -21569,13 +21559,15 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>1984/12/14</t>
+          <t>1968/10/14</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
+      <c r="I250" t="n">
+        <v>101</v>
+      </c>
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr"/>
@@ -21585,11 +21577,11 @@
       <c r="P250" t="inlineStr"/>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="R250" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -21617,7 +21609,7 @@
       <c r="Z250" t="inlineStr"/>
       <c r="AA250" t="inlineStr"/>
       <c r="AB250" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AC250" t="inlineStr">
         <is>
@@ -21627,12 +21619,12 @@
       <c r="AD250" t="inlineStr"/>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
         <is>
-          <t>克里斯·布伦特</t>
+          <t>马修·勒蒂西耶</t>
         </is>
       </c>
     </row>
@@ -21693,7 +21685,7 @@
       <c r="AD251" t="inlineStr"/>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City;Newcastle United;Queens Park Rangers;Burnley</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -21781,7 +21773,7 @@
       <c r="AD252" t="inlineStr"/>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Everton;Newcastle United</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -21792,34 +21784,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>8454</v>
+        <v>3744</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Callum Wilson</t>
+          <t>Chris Brunt</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Northern Ireland</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>1992/2/27</t>
+          <t>1984/12/14</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
-      <c r="I253" t="n">
-        <v>93</v>
-      </c>
+      <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
@@ -21827,15 +21817,37 @@
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="inlineStr"/>
-      <c r="Q253" t="inlineStr"/>
-      <c r="R253" t="inlineStr"/>
-      <c r="S253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>West Bromwich Albion</t>
+        </is>
+      </c>
+      <c r="R253" t="n">
+        <v>269</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T253" t="inlineStr"/>
-      <c r="U253" t="inlineStr"/>
-      <c r="V253" t="inlineStr"/>
+      <c r="U253" t="n">
+        <v>0</v>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W253" t="inlineStr"/>
-      <c r="X253" t="inlineStr"/>
-      <c r="Y253" t="inlineStr"/>
+      <c r="X253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z253" t="inlineStr"/>
       <c r="AA253" t="inlineStr"/>
       <c r="AB253" t="n">
@@ -21843,22 +21855,18 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>West Ham United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr"/>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
         <is>
-          <t>卡勒姆·威尔逊</t>
+          <t>克里斯·布伦特</t>
         </is>
       </c>
     </row>
@@ -21941,7 +21949,7 @@
       <c r="AD254" t="inlineStr"/>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Liverpool;Manchester City;Newcastle United</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -22901,7 +22909,7 @@
       <c r="AD266" t="inlineStr"/>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Aston Villa; Manchester City</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -23509,7 +23517,7 @@
       <c r="AD273" t="inlineStr"/>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Chelsea;Aston Villa;Southampton;Leicester City</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -23673,7 +23681,7 @@
       <c r="AD275" t="inlineStr"/>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Manchester United;Middlesbrough</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -23805,7 +23813,7 @@
       <c r="AD277" t="inlineStr"/>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Manchester United;Everton</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -24132,60 +24140,38 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1659</v>
+        <v>12136</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Thierry Henry</t>
+          <t>Granit Xhaka</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>1977/8/17</t>
+          <t>1992/9/27</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr"/>
-      <c r="I282" t="n">
-        <v>175</v>
-      </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>2001, 2003, 2004, 2005</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>24.0, 25.0, 27.0, 30.0</t>
-        </is>
-      </c>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr"/>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>2003, 2005</t>
-        </is>
-      </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="O282" t="inlineStr">
-        <is>
-          <t>Premier League 20 Seasons Awards</t>
-        </is>
-      </c>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
       <c r="P282" t="inlineStr"/>
       <c r="Q282" t="inlineStr">
         <is>
@@ -24193,7 +24179,7 @@
         </is>
       </c>
       <c r="R282" t="n">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
@@ -24218,78 +24204,96 @@
           <t>no</t>
         </is>
       </c>
-      <c r="Z282" t="inlineStr">
-        <is>
-          <t>2001, 2003, 2004, 2005</t>
-        </is>
-      </c>
-      <c r="AA282" t="inlineStr">
-        <is>
-          <t>24.0, 30.0, 25.0, 27.0</t>
-        </is>
-      </c>
+      <c r="Z282" t="inlineStr"/>
+      <c r="AA282" t="inlineStr"/>
       <c r="AB282" t="n">
         <v>258</v>
       </c>
       <c r="AC282" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD282" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>Sunderland AFC</t>
+        </is>
+      </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sunderland;Arsenal</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
         <is>
-          <t>蒂埃里·亨利</t>
+          <t>格拉尼特·扎卡</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>228</v>
+        <v>1659</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>David Wetherall</t>
+          <t>Thierry Henry</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>1971/3/14</t>
+          <t>1977/8/17</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr"/>
-      <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
+      <c r="I283" t="n">
+        <v>175</v>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>2001, 2003, 2004, 2005</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>24.0, 25.0, 27.0, 30.0</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
-      <c r="N283" t="inlineStr"/>
-      <c r="O283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2003, 2005</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Premier League 20 Seasons Awards</t>
+        </is>
+      </c>
       <c r="P283" t="inlineStr"/>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="R283" t="n">
-        <v>201</v>
+        <v>258</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
@@ -24314,10 +24318,18 @@
           <t>no</t>
         </is>
       </c>
-      <c r="Z283" t="inlineStr"/>
-      <c r="AA283" t="inlineStr"/>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>2001, 2003, 2004, 2005</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>24.0, 30.0, 25.0, 27.0</t>
+        </is>
+      </c>
       <c r="AB283" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AC283" t="inlineStr">
         <is>
@@ -24327,12 +24339,12 @@
       <c r="AD283" t="inlineStr"/>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
         <is>
-          <t>大卫·韦瑟雷尔</t>
+          <t>蒂埃里·亨利</t>
         </is>
       </c>
     </row>
@@ -24404,26 +24416,26 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>12136</v>
+        <v>228</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Granit Xhaka</t>
+          <t>David Wetherall</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>1992/9/27</t>
+          <t>1971/3/14</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -24439,11 +24451,11 @@
       <c r="P285" t="inlineStr"/>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="R285" t="n">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="S285" t="inlineStr">
         <is>
@@ -24475,22 +24487,18 @@
       </c>
       <c r="AC285" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD285" t="inlineStr">
-        <is>
-          <t>Sunderland AFC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD285" t="inlineStr"/>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>Sunderland;Arsenal</t>
+          <t>Leeds United;Bradford City</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
         <is>
-          <t>格拉尼特·扎卡</t>
+          <t>大卫·韦瑟雷尔</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24563,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Portsmouth;Stoke City;Everton;Chelsea;Bournemouth</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -25343,7 +25351,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Bournemouth;Tottenham Hotspur</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -25533,7 +25541,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Everton;Aston Villa</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -25610,34 +25618,32 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>2553</v>
+        <v>5758</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Yakubu</t>
+          <t>Lucas Digne</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>1982/11/22</t>
+          <t>1993/7/20</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr"/>
-      <c r="I299" t="n">
-        <v>95</v>
-      </c>
+      <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr"/>
@@ -25657,53 +25663,59 @@
       <c r="Z299" t="inlineStr"/>
       <c r="AA299" t="inlineStr"/>
       <c r="AB299" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD299" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Aston Villa;Everton</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
         <is>
-          <t>雅库布</t>
+          <t>卢卡斯·迪涅</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>1429</v>
+        <v>2553</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Jonathan Greening</t>
+          <t>Yakubu</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>1979/1/2</t>
+          <t>1982/11/22</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr"/>
-      <c r="I300" t="inlineStr"/>
+      <c r="I300" t="n">
+        <v>95</v>
+      </c>
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr"/>
@@ -25733,12 +25745,12 @@
       <c r="AD300" t="inlineStr"/>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>Manchester United;Middlesbrough;West Bromwich Albion;Fulham</t>
+          <t>Portsmouth;Middlesbrough;Everton;Blackburn Rovers</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
         <is>
-          <t>乔纳森·格里宁</t>
+          <t>雅库布</t>
         </is>
       </c>
     </row>
@@ -25810,41 +25822,31 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>4499</v>
+        <v>1429</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Nathan Aké</t>
+          <t>Jonathan Greening</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>1995/2/18</t>
-        </is>
-      </c>
-      <c r="F302" t="n">
-        <v>4</v>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>2020–21, 2021–22, 2022–23, 2023–24</t>
-        </is>
-      </c>
+          <t>1979/1/2</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr"/>
@@ -25869,37 +25871,33 @@
       </c>
       <c r="AC302" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD302" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD302" t="inlineStr"/>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>Manchester City;Bournemouth</t>
+          <t>Manchester United;Middlesbrough;West Bromwich Albion;Fulham</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
         <is>
-          <t>内森·阿克</t>
+          <t>乔纳森·格里宁</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>5758</v>
+        <v>4499</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Lucas Digne</t>
+          <t>Nathan Aké</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -25909,12 +25907,22 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>1993/7/20</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr"/>
-      <c r="G303" t="inlineStr"/>
-      <c r="H303" t="inlineStr"/>
+          <t>1995/2/18</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>4</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>2020–21, 2021–22, 2022–23, 2023–24</t>
+        </is>
+      </c>
       <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr"/>
@@ -25944,17 +25952,17 @@
       </c>
       <c r="AD303" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>Aston Villa;Everton</t>
+          <t>Chelsea;Watford;Bournemouth;Manchester City</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
         <is>
-          <t>卢卡斯·迪涅</t>
+          <t>内森·阿克</t>
         </is>
       </c>
     </row>
@@ -26037,7 +26045,7 @@
       <c r="AD304" t="inlineStr"/>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Blackburn Rovers;Birmingham City</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -26301,7 +26309,7 @@
       <c r="AD307" t="inlineStr"/>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Southampton;Derby County</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -26448,26 +26456,26 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>3102</v>
+        <v>4985</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>John Obi Mikel</t>
+          <t>Bernd Leno</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>1987/4/22</t>
+          <t>1992/3/4</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -26481,81 +26489,63 @@
       <c r="N310" t="inlineStr"/>
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="inlineStr"/>
-      <c r="Q310" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="R310" t="n">
-        <v>249</v>
-      </c>
-      <c r="S310" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q310" t="inlineStr"/>
+      <c r="R310" t="inlineStr"/>
+      <c r="S310" t="inlineStr"/>
       <c r="T310" t="inlineStr"/>
-      <c r="U310" t="n">
-        <v>0</v>
-      </c>
-      <c r="V310" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U310" t="inlineStr"/>
+      <c r="V310" t="inlineStr"/>
       <c r="W310" t="inlineStr"/>
-      <c r="X310" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y310" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X310" t="inlineStr"/>
+      <c r="Y310" t="inlineStr"/>
       <c r="Z310" t="inlineStr"/>
       <c r="AA310" t="inlineStr"/>
       <c r="AB310" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AC310" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD310" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD310" t="inlineStr">
+        <is>
+          <t>Fulham FC</t>
+        </is>
+      </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>Stoke City;Chelsea</t>
+          <t>Fulham;Arsenal</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
         <is>
-          <t>约翰·奥比·米克尔</t>
+          <t>伯恩德·莱诺</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>4985</v>
+        <v>3102</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Bernd Leno</t>
+          <t>John Obi Mikel</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1992/3/4</t>
+          <t>1987/4/22</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -26569,15 +26559,37 @@
       <c r="N311" t="inlineStr"/>
       <c r="O311" t="inlineStr"/>
       <c r="P311" t="inlineStr"/>
-      <c r="Q311" t="inlineStr"/>
-      <c r="R311" t="inlineStr"/>
-      <c r="S311" t="inlineStr"/>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="R311" t="n">
+        <v>249</v>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T311" t="inlineStr"/>
-      <c r="U311" t="inlineStr"/>
-      <c r="V311" t="inlineStr"/>
+      <c r="U311" t="n">
+        <v>0</v>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W311" t="inlineStr"/>
-      <c r="X311" t="inlineStr"/>
-      <c r="Y311" t="inlineStr"/>
+      <c r="X311" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z311" t="inlineStr"/>
       <c r="AA311" t="inlineStr"/>
       <c r="AB311" t="n">
@@ -26585,22 +26597,18 @@
       </c>
       <c r="AC311" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD311" t="inlineStr">
-        <is>
-          <t>Fulham FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD311" t="inlineStr"/>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>Fulham;Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
         <is>
-          <t>伯恩德·莱诺</t>
+          <t>约翰·奥比·米克尔</t>
         </is>
       </c>
     </row>
@@ -26764,26 +26772,26 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>3137</v>
+        <v>24797</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Lucas Leiva</t>
+          <t>Dwight McNeil</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1987/1/9</t>
+          <t>1999/11/22</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
@@ -26797,56 +26805,38 @@
       <c r="N314" t="inlineStr"/>
       <c r="O314" t="inlineStr"/>
       <c r="P314" t="inlineStr"/>
-      <c r="Q314" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="R314" t="n">
-        <v>247</v>
-      </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q314" t="inlineStr"/>
+      <c r="R314" t="inlineStr"/>
+      <c r="S314" t="inlineStr"/>
       <c r="T314" t="inlineStr"/>
-      <c r="U314" t="n">
-        <v>0</v>
-      </c>
-      <c r="V314" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U314" t="inlineStr"/>
+      <c r="V314" t="inlineStr"/>
       <c r="W314" t="inlineStr"/>
-      <c r="X314" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y314" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X314" t="inlineStr"/>
+      <c r="Y314" t="inlineStr"/>
       <c r="Z314" t="inlineStr"/>
       <c r="AA314" t="inlineStr"/>
       <c r="AB314" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AC314" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD314" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD314" t="inlineStr">
+        <is>
+          <t>Everton FC</t>
+        </is>
+      </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Everton;Burnley</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
         <is>
-          <t>卢卡斯·莱瓦</t>
+          <t>德怀特·麦克尼尔</t>
         </is>
       </c>
     </row>
@@ -26940,26 +26930,26 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>583</v>
+        <v>3137</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Neil Sullivan</t>
+          <t>Lucas Leiva</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1970/2/24</t>
+          <t>1987/1/9</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -26973,15 +26963,37 @@
       <c r="N316" t="inlineStr"/>
       <c r="O316" t="inlineStr"/>
       <c r="P316" t="inlineStr"/>
-      <c r="Q316" t="inlineStr"/>
-      <c r="R316" t="inlineStr"/>
-      <c r="S316" t="inlineStr"/>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="R316" t="n">
+        <v>247</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T316" t="inlineStr"/>
-      <c r="U316" t="inlineStr"/>
-      <c r="V316" t="inlineStr"/>
+      <c r="U316" t="n">
+        <v>0</v>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W316" t="inlineStr"/>
-      <c r="X316" t="inlineStr"/>
-      <c r="Y316" t="inlineStr"/>
+      <c r="X316" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z316" t="inlineStr"/>
       <c r="AA316" t="inlineStr"/>
       <c r="AB316" t="n">
@@ -26995,12 +27007,12 @@
       <c r="AD316" t="inlineStr"/>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>Wimbledon;Tottenham Hotspur;Chelsea;Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
         <is>
-          <t>尼尔·沙利文</t>
+          <t>卢卡斯·莱瓦</t>
         </is>
       </c>
     </row>
@@ -27055,10 +27067,14 @@
       </c>
       <c r="AC317" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD317" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>Al Wasl SC</t>
+        </is>
+      </c>
       <c r="AE317" t="inlineStr">
         <is>
           <t>Chelsea;Stoke City;Everton;West Ham United</t>
@@ -27072,26 +27088,26 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>24797</v>
+        <v>583</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Dwight McNeil</t>
+          <t>Neil Sullivan</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>1999/11/22</t>
+          <t>1970/2/24</t>
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
@@ -27121,22 +27137,18 @@
       </c>
       <c r="AC318" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD318" t="inlineStr">
-        <is>
-          <t>Everton FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr"/>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>Everton;Burnley</t>
+          <t>Wimbledon;Tottenham Hotspur;Chelsea;Leeds United</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
         <is>
-          <t>德怀特·麦克尼尔</t>
+          <t>尼尔·沙利文</t>
         </is>
       </c>
     </row>
@@ -27189,7 +27201,7 @@
       <c r="Z319" t="inlineStr"/>
       <c r="AA319" t="inlineStr"/>
       <c r="AB319" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AC319" t="inlineStr">
         <is>
@@ -27302,16 +27314,16 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>2928</v>
+        <v>22542</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Stephen Ireland</t>
+          <t>Pascal Groß</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -27321,7 +27333,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>1986/8/22</t>
+          <t>1991/6/15</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -27335,113 +27347,107 @@
       <c r="N321" t="inlineStr"/>
       <c r="O321" t="inlineStr"/>
       <c r="P321" t="inlineStr"/>
-      <c r="Q321" t="inlineStr"/>
-      <c r="R321" t="inlineStr"/>
-      <c r="S321" t="inlineStr"/>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="R321" t="n">
+        <v>245</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="T321" t="inlineStr"/>
-      <c r="U321" t="inlineStr"/>
-      <c r="V321" t="inlineStr"/>
+      <c r="U321" t="n">
+        <v>0</v>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W321" t="inlineStr"/>
-      <c r="X321" t="inlineStr"/>
-      <c r="Y321" t="inlineStr"/>
+      <c r="X321" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z321" t="inlineStr"/>
       <c r="AA321" t="inlineStr"/>
       <c r="AB321" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AC321" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD321" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>Manchester City;Aston Villa;Newcastle United;Stoke City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
         <is>
-          <t>斯蒂芬·爱尔兰</t>
+          <t>帕斯卡尔·格罗斯</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>4503</v>
+        <v>2928</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Eden Hazard</t>
+          <t>Stephen Ireland</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>1991/1/7</t>
+          <t>1986/8/22</t>
         </is>
       </c>
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr"/>
-      <c r="I322" t="n">
-        <v>85</v>
-      </c>
+      <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr"/>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
       <c r="O322" t="inlineStr"/>
       <c r="P322" t="inlineStr"/>
-      <c r="Q322" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="R322" t="n">
-        <v>245</v>
-      </c>
-      <c r="S322" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q322" t="inlineStr"/>
+      <c r="R322" t="inlineStr"/>
+      <c r="S322" t="inlineStr"/>
       <c r="T322" t="inlineStr"/>
-      <c r="U322" t="n">
-        <v>0</v>
-      </c>
-      <c r="V322" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U322" t="inlineStr"/>
+      <c r="V322" t="inlineStr"/>
       <c r="W322" t="inlineStr"/>
-      <c r="X322" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y322" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X322" t="inlineStr"/>
+      <c r="Y322" t="inlineStr"/>
       <c r="Z322" t="inlineStr"/>
       <c r="AA322" t="inlineStr"/>
       <c r="AB322" t="n">
@@ -27455,12 +27461,12 @@
       <c r="AD322" t="inlineStr"/>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City;Aston Villa;Newcastle United;Stoke City</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
         <is>
-          <t>埃登·阿扎尔</t>
+          <t>斯蒂芬·爱尔兰</t>
         </is>
       </c>
     </row>
@@ -27538,42 +27544,52 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>22542</v>
+        <v>4503</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Pascal Groß</t>
+          <t>Eden Hazard</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>1991/6/15</t>
+          <t>1991/1/7</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
+      <c r="I324" t="n">
+        <v>85</v>
+      </c>
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr"/>
-      <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
       <c r="O324" t="inlineStr"/>
       <c r="P324" t="inlineStr"/>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="R324" t="n">
@@ -27581,7 +27597,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="T324" t="inlineStr"/>
@@ -27609,22 +27625,18 @@
       </c>
       <c r="AC324" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD324" t="inlineStr">
-        <is>
-          <t>Brighton &amp; Hove Albion</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr"/>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
         <is>
-          <t>帕斯卡尔·格罗斯</t>
+          <t>埃登·阿扎尔</t>
         </is>
       </c>
     </row>
@@ -27685,7 +27697,7 @@
       <c r="AD325" t="inlineStr"/>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Leeds United;Newcastle United;Middlesbrough;Tottenham Hotspur;Stoke City</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -27850,26 +27862,26 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>523</v>
+        <v>5865</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Francis Benali</t>
+          <t>Youri Tielemans</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>1968/12/30</t>
+          <t>1997/5/7</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -27883,37 +27895,15 @@
       <c r="N328" t="inlineStr"/>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="inlineStr"/>
-      <c r="Q328" t="inlineStr">
-        <is>
-          <t>Southampton</t>
-        </is>
-      </c>
-      <c r="R328" t="n">
-        <v>243</v>
-      </c>
-      <c r="S328" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q328" t="inlineStr"/>
+      <c r="R328" t="inlineStr"/>
+      <c r="S328" t="inlineStr"/>
       <c r="T328" t="inlineStr"/>
-      <c r="U328" t="n">
-        <v>0</v>
-      </c>
-      <c r="V328" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U328" t="inlineStr"/>
+      <c r="V328" t="inlineStr"/>
       <c r="W328" t="inlineStr"/>
-      <c r="X328" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y328" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X328" t="inlineStr"/>
+      <c r="Y328" t="inlineStr"/>
       <c r="Z328" t="inlineStr"/>
       <c r="AA328" t="inlineStr"/>
       <c r="AB328" t="n">
@@ -27921,18 +27911,22 @@
       </c>
       <c r="AC328" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD328" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD328" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Aston Villa;Leicester City</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
         <is>
-          <t>弗朗西斯·贝纳利</t>
+          <t>尤里·蒂勒曼斯</t>
         </is>
       </c>
     </row>
@@ -28070,26 +28064,26 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2289</v>
+        <v>523</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>El Hadji Diouf</t>
+          <t>Francis Benali</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>1981/1/15</t>
+          <t>1968/12/30</t>
         </is>
       </c>
       <c r="F331" t="inlineStr"/>
@@ -28103,19 +28097,41 @@
       <c r="N331" t="inlineStr"/>
       <c r="O331" t="inlineStr"/>
       <c r="P331" t="inlineStr"/>
-      <c r="Q331" t="inlineStr"/>
-      <c r="R331" t="inlineStr"/>
-      <c r="S331" t="inlineStr"/>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="R331" t="n">
+        <v>243</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T331" t="inlineStr"/>
-      <c r="U331" t="inlineStr"/>
-      <c r="V331" t="inlineStr"/>
+      <c r="U331" t="n">
+        <v>0</v>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W331" t="inlineStr"/>
-      <c r="X331" t="inlineStr"/>
-      <c r="Y331" t="inlineStr"/>
+      <c r="X331" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z331" t="inlineStr"/>
       <c r="AA331" t="inlineStr"/>
       <c r="AB331" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AC331" t="inlineStr">
         <is>
@@ -28125,27 +28141,27 @@
       <c r="AD331" t="inlineStr"/>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
         <is>
-          <t>埃尔哈吉·迪乌夫</t>
+          <t>弗朗西斯·贝纳利</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>3448</v>
+        <v>2289</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Tom Cleverley</t>
+          <t>El Hadji Diouf</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -28155,7 +28171,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>1989/8/12</t>
+          <t>1981/1/15</t>
         </is>
       </c>
       <c r="F332" t="inlineStr"/>
@@ -28191,12 +28207,12 @@
       <c r="AD332" t="inlineStr"/>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>Wigan Athletic;Manchester United;Aston Villa;Everton;Watford</t>
+          <t>Liverpool;Bolton Wanderers;Sunderland;Blackburn Rovers</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
         <is>
-          <t>汤姆·克莱弗利</t>
+          <t>埃尔哈吉·迪乌夫</t>
         </is>
       </c>
     </row>
@@ -28429,7 +28445,7 @@
       <c r="AD335" t="inlineStr"/>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Tottenham Hotspur;Hull City</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -28440,16 +28456,16 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>5865</v>
+        <v>3448</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Youri Tielemans</t>
+          <t>Tom Cleverley</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -28459,7 +28475,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>1997/5/7</t>
+          <t>1989/8/12</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
@@ -28489,22 +28505,18 @@
       </c>
       <c r="AC336" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD336" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD336" t="inlineStr"/>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>Aston Villa;Leicester City</t>
+          <t>Wigan Athletic;Manchester United;Aston Villa;Everton;Watford</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
         <is>
-          <t>尤里·蒂勒曼斯</t>
+          <t>汤姆·克莱弗利</t>
         </is>
       </c>
     </row>
@@ -28565,7 +28577,7 @@
       <c r="AD337" t="inlineStr"/>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Birmingham City;Blackburn Rovers;Crystal Palace</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -29109,7 +29121,7 @@
       <c r="AD344" t="inlineStr"/>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Aston Villa;Bolton Wanderers</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -29568,26 +29580,26 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>1045</v>
+        <v>8868</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Ian Harte</t>
+          <t>Jarrod Bowen</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>1977/8/31</t>
+          <t>1996/12/20</t>
         </is>
       </c>
       <c r="F351" t="inlineStr"/>
@@ -29603,15 +29615,15 @@
       <c r="P351" t="inlineStr"/>
       <c r="Q351" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="R351" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -29639,33 +29651,37 @@
       </c>
       <c r="AC351" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD351" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD351" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>Bournemouth;Leeds United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
         <is>
-          <t>伊恩·哈特</t>
+          <t>贾罗德·鲍文</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>755</v>
+        <v>1045</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Simon Charlton</t>
+          <t>Ian Harte</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -29675,7 +29691,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>1971/10/25</t>
+          <t>1977/8/31</t>
         </is>
       </c>
       <c r="F352" t="inlineStr"/>
@@ -29689,19 +29705,41 @@
       <c r="N352" t="inlineStr"/>
       <c r="O352" t="inlineStr"/>
       <c r="P352" t="inlineStr"/>
-      <c r="Q352" t="inlineStr"/>
-      <c r="R352" t="inlineStr"/>
-      <c r="S352" t="inlineStr"/>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="R352" t="n">
+        <v>213</v>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T352" t="inlineStr"/>
-      <c r="U352" t="inlineStr"/>
-      <c r="V352" t="inlineStr"/>
+      <c r="U352" t="n">
+        <v>0</v>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W352" t="inlineStr"/>
-      <c r="X352" t="inlineStr"/>
-      <c r="Y352" t="inlineStr"/>
+      <c r="X352" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z352" t="inlineStr"/>
       <c r="AA352" t="inlineStr"/>
       <c r="AB352" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AC352" t="inlineStr">
         <is>
@@ -29711,12 +29749,12 @@
       <c r="AD352" t="inlineStr"/>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>Southampton;Birmingham City;Norwich City</t>
+          <t>Leeds United;Sunderland;Reading</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
         <is>
-          <t>西蒙·查尔顿</t>
+          <t>伊恩·哈特</t>
         </is>
       </c>
     </row>
@@ -29777,7 +29815,7 @@
       <c r="AD353" t="inlineStr"/>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Fulham;Liverpool;Portsmouth</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -29788,112 +29826,50 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>2522</v>
+        <v>14716</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo</t>
+          <t>Harvey Barnes</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>1985/2/5</t>
-        </is>
-      </c>
-      <c r="F354" t="n">
-        <v>3</v>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>2006–07, 2007–08, 2008–09</t>
-        </is>
-      </c>
-      <c r="I354" t="n">
-        <v>103</v>
-      </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>31.0</t>
-        </is>
-      </c>
+          <t>1997/12/9</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
       <c r="L354" t="inlineStr"/>
-      <c r="M354" t="inlineStr">
-        <is>
-          <t>2006, 2007</t>
-        </is>
-      </c>
-      <c r="N354" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="O354" t="inlineStr">
-        <is>
-          <t>Premier League 20 Seasons Awards</t>
-        </is>
-      </c>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
+      <c r="O354" t="inlineStr"/>
       <c r="P354" t="inlineStr"/>
-      <c r="Q354" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="R354" t="n">
-        <v>236</v>
-      </c>
-      <c r="S354" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q354" t="inlineStr"/>
+      <c r="R354" t="inlineStr"/>
+      <c r="S354" t="inlineStr"/>
       <c r="T354" t="inlineStr"/>
-      <c r="U354" t="n">
-        <v>0</v>
-      </c>
-      <c r="V354" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U354" t="inlineStr"/>
+      <c r="V354" t="inlineStr"/>
       <c r="W354" t="inlineStr"/>
-      <c r="X354" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y354" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="Z354" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="AA354" t="inlineStr">
-        <is>
-          <t>31.0</t>
-        </is>
-      </c>
+      <c r="X354" t="inlineStr"/>
+      <c r="Y354" t="inlineStr"/>
+      <c r="Z354" t="inlineStr"/>
+      <c r="AA354" t="inlineStr"/>
       <c r="AB354" t="n">
         <v>236</v>
       </c>
@@ -29904,27 +29880,27 @@
       </c>
       <c r="AD354" t="inlineStr">
         <is>
-          <t>Al-Nassr FC</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Newcastle United;Leicester City</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
         <is>
-          <t>克里斯蒂亚诺·罗纳尔多</t>
+          <t>哈维·巴恩斯</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>8868</v>
+        <v>755</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Jarrod Bowen</t>
+          <t>Simon Charlton</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -29934,12 +29910,12 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>1996/12/20</t>
+          <t>1971/10/25</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
@@ -29953,37 +29929,15 @@
       <c r="N355" t="inlineStr"/>
       <c r="O355" t="inlineStr"/>
       <c r="P355" t="inlineStr"/>
-      <c r="Q355" t="inlineStr">
-        <is>
-          <t>West Ham United</t>
-        </is>
-      </c>
-      <c r="R355" t="n">
-        <v>229</v>
-      </c>
-      <c r="S355" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="Q355" t="inlineStr"/>
+      <c r="R355" t="inlineStr"/>
+      <c r="S355" t="inlineStr"/>
       <c r="T355" t="inlineStr"/>
-      <c r="U355" t="n">
-        <v>0</v>
-      </c>
-      <c r="V355" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U355" t="inlineStr"/>
+      <c r="V355" t="inlineStr"/>
       <c r="W355" t="inlineStr"/>
-      <c r="X355" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y355" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X355" t="inlineStr"/>
+      <c r="Y355" t="inlineStr"/>
       <c r="Z355" t="inlineStr"/>
       <c r="AA355" t="inlineStr"/>
       <c r="AB355" t="n">
@@ -29991,113 +29945,175 @@
       </c>
       <c r="AC355" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD355" t="inlineStr">
-        <is>
-          <t>West Ham United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD355" t="inlineStr"/>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Southampton;Birmingham City;Norwich City</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
         <is>
-          <t>贾罗德·鲍文</t>
+          <t>西蒙·查尔顿</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1253</v>
+        <v>2522</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Michael Gray</t>
+          <t>Cristiano Ronaldo</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>1974/8/3</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
-      <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
+          <t>1985/2/5</t>
+        </is>
+      </c>
+      <c r="F356" t="n">
+        <v>3</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>2006–07, 2007–08, 2008–09</t>
+        </is>
+      </c>
+      <c r="I356" t="n">
+        <v>103</v>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr"/>
-      <c r="M356" t="inlineStr"/>
-      <c r="N356" t="inlineStr"/>
-      <c r="O356" t="inlineStr"/>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>2006, 2007</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>Premier League 20 Seasons Awards</t>
+        </is>
+      </c>
       <c r="P356" t="inlineStr"/>
-      <c r="Q356" t="inlineStr"/>
-      <c r="R356" t="inlineStr"/>
-      <c r="S356" t="inlineStr"/>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="R356" t="n">
+        <v>236</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T356" t="inlineStr"/>
-      <c r="U356" t="inlineStr"/>
-      <c r="V356" t="inlineStr"/>
+      <c r="U356" t="n">
+        <v>0</v>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W356" t="inlineStr"/>
-      <c r="X356" t="inlineStr"/>
-      <c r="Y356" t="inlineStr"/>
-      <c r="Z356" t="inlineStr"/>
-      <c r="AA356" t="inlineStr"/>
+      <c r="X356" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="AB356" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AC356" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD356" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD356" t="inlineStr">
+        <is>
+          <t>Al-Nassr FC</t>
+        </is>
+      </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
         <is>
-          <t>迈克尔·格雷</t>
+          <t>克里斯蒂亚诺·罗纳尔多</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>14716</v>
+        <v>1558</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Harvey Barnes</t>
+          <t>David Weir</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>1997/12/9</t>
+          <t>1970/5/10</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -30111,15 +30127,37 @@
       <c r="N357" t="inlineStr"/>
       <c r="O357" t="inlineStr"/>
       <c r="P357" t="inlineStr"/>
-      <c r="Q357" t="inlineStr"/>
-      <c r="R357" t="inlineStr"/>
-      <c r="S357" t="inlineStr"/>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="R357" t="n">
+        <v>235</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T357" t="inlineStr"/>
-      <c r="U357" t="inlineStr"/>
-      <c r="V357" t="inlineStr"/>
+      <c r="U357" t="n">
+        <v>0</v>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W357" t="inlineStr"/>
-      <c r="X357" t="inlineStr"/>
-      <c r="Y357" t="inlineStr"/>
+      <c r="X357" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z357" t="inlineStr"/>
       <c r="AA357" t="inlineStr"/>
       <c r="AB357" t="n">
@@ -30127,37 +30165,33 @@
       </c>
       <c r="AC357" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD357" t="inlineStr">
-        <is>
-          <t>Newcastle United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD357" t="inlineStr"/>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>Newcastle United;Leicester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
         <is>
-          <t>哈维·巴恩斯</t>
+          <t>大卫·威尔</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1558</v>
+        <v>1253</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>David Weir</t>
+          <t>Michael Gray</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -30167,7 +30201,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>1970/5/10</t>
+          <t>1974/8/3</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
@@ -30181,37 +30215,15 @@
       <c r="N358" t="inlineStr"/>
       <c r="O358" t="inlineStr"/>
       <c r="P358" t="inlineStr"/>
-      <c r="Q358" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="R358" t="n">
-        <v>235</v>
-      </c>
-      <c r="S358" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q358" t="inlineStr"/>
+      <c r="R358" t="inlineStr"/>
+      <c r="S358" t="inlineStr"/>
       <c r="T358" t="inlineStr"/>
-      <c r="U358" t="n">
-        <v>0</v>
-      </c>
-      <c r="V358" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U358" t="inlineStr"/>
+      <c r="V358" t="inlineStr"/>
       <c r="W358" t="inlineStr"/>
-      <c r="X358" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y358" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X358" t="inlineStr"/>
+      <c r="Y358" t="inlineStr"/>
       <c r="Z358" t="inlineStr"/>
       <c r="AA358" t="inlineStr"/>
       <c r="AB358" t="n">
@@ -30225,12 +30237,12 @@
       <c r="AD358" t="inlineStr"/>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sunderland;Blackburn Rovers</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
         <is>
-          <t>大卫·威尔</t>
+          <t>迈克尔·格雷</t>
         </is>
       </c>
     </row>
@@ -30285,10 +30297,14 @@
       </c>
       <c r="AC359" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD359" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD359" t="inlineStr">
+        <is>
+          <t>Celtic FC</t>
+        </is>
+      </c>
       <c r="AE359" t="inlineStr">
         <is>
           <t>Arsenal;Liverpool</t>
@@ -30527,7 +30543,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>Newcastle United;Brighton &amp; Hove Albion</t>
+          <t>Fulham;Brighton &amp; Hove Albion;Newcastle United</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -30604,26 +30620,26 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>2024</v>
+        <v>14164</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Tugay</t>
+          <t>Aaron Wan-Bissaka</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Turkiye</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>1970/8/24</t>
+          <t>1997/11/26</t>
         </is>
       </c>
       <c r="F364" t="inlineStr"/>
@@ -30637,37 +30653,15 @@
       <c r="N364" t="inlineStr"/>
       <c r="O364" t="inlineStr"/>
       <c r="P364" t="inlineStr"/>
-      <c r="Q364" t="inlineStr">
-        <is>
-          <t>Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="R364" t="n">
-        <v>233</v>
-      </c>
-      <c r="S364" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q364" t="inlineStr"/>
+      <c r="R364" t="inlineStr"/>
+      <c r="S364" t="inlineStr"/>
       <c r="T364" t="inlineStr"/>
-      <c r="U364" t="n">
-        <v>0</v>
-      </c>
-      <c r="V364" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U364" t="inlineStr"/>
+      <c r="V364" t="inlineStr"/>
       <c r="W364" t="inlineStr"/>
-      <c r="X364" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y364" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X364" t="inlineStr"/>
+      <c r="Y364" t="inlineStr"/>
       <c r="Z364" t="inlineStr"/>
       <c r="AA364" t="inlineStr"/>
       <c r="AB364" t="n">
@@ -30675,43 +30669,47 @@
       </c>
       <c r="AC364" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD364" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD364" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Ham United;Manchester United;Crystal Palace</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
         <is>
-          <t>图盖</t>
+          <t>阿隆·万-比萨卡</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>2047</v>
+        <v>2024</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Jonathan Walters</t>
+          <t>Tugay</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Turkiye</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>1983/9/20</t>
+          <t>1970/8/24</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
@@ -30727,11 +30725,11 @@
       <c r="P365" t="inlineStr"/>
       <c r="Q365" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="R365" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="S365" t="inlineStr">
         <is>
@@ -30769,37 +30767,37 @@
       <c r="AD365" t="inlineStr"/>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>Burnley;Stoke City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
         <is>
-          <t>乔纳森·沃尔特斯</t>
+          <t>图盖</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>2012</v>
+        <v>2047</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Olof Mellberg</t>
+          <t>Jonathan Walters</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>1977/9/3</t>
+          <t>1983/9/20</t>
         </is>
       </c>
       <c r="F366" t="inlineStr"/>
@@ -30815,11 +30813,11 @@
       <c r="P366" t="inlineStr"/>
       <c r="Q366" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="R366" t="n">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="S366" t="inlineStr">
         <is>
@@ -30847,7 +30845,7 @@
       <c r="Z366" t="inlineStr"/>
       <c r="AA366" t="inlineStr"/>
       <c r="AB366" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AC366" t="inlineStr">
         <is>
@@ -30857,27 +30855,27 @@
       <c r="AD366" t="inlineStr"/>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Burnley;Stoke City</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
         <is>
-          <t>奥洛夫·梅尔伯格</t>
+          <t>乔纳森·沃尔特斯</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>14164</v>
+        <v>2012</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Aaron Wan-Bissaka</t>
+          <t>Olof Mellberg</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -30887,7 +30885,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>1997/11/26</t>
+          <t>1977/9/3</t>
         </is>
       </c>
       <c r="F367" t="inlineStr"/>
@@ -30901,15 +30899,37 @@
       <c r="N367" t="inlineStr"/>
       <c r="O367" t="inlineStr"/>
       <c r="P367" t="inlineStr"/>
-      <c r="Q367" t="inlineStr"/>
-      <c r="R367" t="inlineStr"/>
-      <c r="S367" t="inlineStr"/>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="R367" t="n">
+        <v>232</v>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T367" t="inlineStr"/>
-      <c r="U367" t="inlineStr"/>
-      <c r="V367" t="inlineStr"/>
+      <c r="U367" t="n">
+        <v>0</v>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W367" t="inlineStr"/>
-      <c r="X367" t="inlineStr"/>
-      <c r="Y367" t="inlineStr"/>
+      <c r="X367" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z367" t="inlineStr"/>
       <c r="AA367" t="inlineStr"/>
       <c r="AB367" t="n">
@@ -30917,22 +30937,18 @@
       </c>
       <c r="AC367" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD367" t="inlineStr">
-        <is>
-          <t>West Ham United</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD367" t="inlineStr"/>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>West Ham United;Manchester United</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
         <is>
-          <t>阿隆·万-比萨卡</t>
+          <t>奥洛夫·梅尔伯格</t>
         </is>
       </c>
     </row>
@@ -31026,26 +31042,26 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>4487</v>
+        <v>51423</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Matthew Lowton</t>
+          <t>John McGinn</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>1989/6/9</t>
+          <t>1994/10/18</t>
         </is>
       </c>
       <c r="F369" t="inlineStr"/>
@@ -31059,19 +31075,41 @@
       <c r="N369" t="inlineStr"/>
       <c r="O369" t="inlineStr"/>
       <c r="P369" t="inlineStr"/>
-      <c r="Q369" t="inlineStr"/>
-      <c r="R369" t="inlineStr"/>
-      <c r="S369" t="inlineStr"/>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="R369" t="n">
+        <v>232</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="T369" t="inlineStr"/>
-      <c r="U369" t="inlineStr"/>
-      <c r="V369" t="inlineStr"/>
+      <c r="U369" t="n">
+        <v>0</v>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W369" t="inlineStr"/>
-      <c r="X369" t="inlineStr"/>
-      <c r="Y369" t="inlineStr"/>
+      <c r="X369" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z369" t="inlineStr"/>
       <c r="AA369" t="inlineStr"/>
       <c r="AB369" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AC369" t="inlineStr">
         <is>
@@ -31080,42 +31118,42 @@
       </c>
       <c r="AD369" t="inlineStr">
         <is>
-          <t>Precision FC</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>Aston Villa;Burnley</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
         <is>
-          <t>马修·洛顿</t>
+          <t>约翰·麦金</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>128</v>
+        <v>11071</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Phil Babb</t>
+          <t>Raúl Jiménez</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>1970/11/30</t>
+          <t>1991/5/5</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
@@ -31141,22 +31179,26 @@
       <c r="Z370" t="inlineStr"/>
       <c r="AA370" t="inlineStr"/>
       <c r="AB370" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AC370" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD370" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD370" t="inlineStr">
+        <is>
+          <t>Fulham FC</t>
+        </is>
+      </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>Coventry City;Liverpool;Sunderland</t>
+          <t>Wolverhampton Wanderers; Fulham</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
         <is>
-          <t>菲尔·巴布</t>
+          <t>劳尔·希门尼斯</t>
         </is>
       </c>
     </row>
@@ -31228,26 +31270,26 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1495</v>
+        <v>128</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Jermaine Pennant</t>
+          <t>Phil Babb</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>1983/1/15</t>
+          <t>1970/11/30</t>
         </is>
       </c>
       <c r="F372" t="inlineStr"/>
@@ -31283,37 +31325,37 @@
       <c r="AD372" t="inlineStr"/>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>Arsenal;Watford;Leeds United;Birmingham City;Portsmouth;Liverpool;Stoke City</t>
+          <t>Coventry City;Liverpool;Sunderland</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
         <is>
-          <t>杰梅因·彭南特</t>
+          <t>菲尔·巴布</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>51423</v>
+        <v>4487</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>John McGinn</t>
+          <t>Matthew Lowton</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>1994/10/18</t>
+          <t>1989/6/9</t>
         </is>
       </c>
       <c r="F373" t="inlineStr"/>
@@ -31327,37 +31369,15 @@
       <c r="N373" t="inlineStr"/>
       <c r="O373" t="inlineStr"/>
       <c r="P373" t="inlineStr"/>
-      <c r="Q373" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
-      <c r="R373" t="n">
-        <v>231</v>
-      </c>
-      <c r="S373" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="Q373" t="inlineStr"/>
+      <c r="R373" t="inlineStr"/>
+      <c r="S373" t="inlineStr"/>
       <c r="T373" t="inlineStr"/>
-      <c r="U373" t="n">
-        <v>0</v>
-      </c>
-      <c r="V373" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U373" t="inlineStr"/>
+      <c r="V373" t="inlineStr"/>
       <c r="W373" t="inlineStr"/>
-      <c r="X373" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y373" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X373" t="inlineStr"/>
+      <c r="Y373" t="inlineStr"/>
       <c r="Z373" t="inlineStr"/>
       <c r="AA373" t="inlineStr"/>
       <c r="AB373" t="n">
@@ -31370,42 +31390,42 @@
       </c>
       <c r="AD373" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Precision FC</t>
         </is>
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Aston Villa;Burnley</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
         <is>
-          <t>约翰·麦金</t>
+          <t>马修·洛顿</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>11071</v>
+        <v>1495</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Raúl Jiménez</t>
+          <t>Jermaine Pennant</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>1991/5/5</t>
+          <t>1983/1/15</t>
         </is>
       </c>
       <c r="F374" t="inlineStr"/>
@@ -31435,62 +31455,48 @@
       </c>
       <c r="AC374" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD374" t="inlineStr">
-        <is>
-          <t>Fulham FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD374" t="inlineStr"/>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Arsenal;Watford;Leeds United;Birmingham City;Portsmouth;Liverpool;Stoke City</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
         <is>
-          <t>劳尔·希门尼斯</t>
+          <t>杰梅因·彭南特</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>4148</v>
+        <v>13274</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Yaya Touré</t>
+          <t>Ezri Konsa</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Cote D’Ivoire</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>1983/5/13</t>
-        </is>
-      </c>
-      <c r="F375" t="n">
-        <v>3</v>
-      </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>2011–12, 2013–14, 2017–18</t>
-        </is>
-      </c>
+          <t>1997/10/23</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr"/>
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr"/>
@@ -31501,15 +31507,15 @@
       <c r="P375" t="inlineStr"/>
       <c r="Q375" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="R375" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="T375" t="inlineStr"/>
@@ -31533,52 +31539,66 @@
       <c r="Z375" t="inlineStr"/>
       <c r="AA375" t="inlineStr"/>
       <c r="AB375" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AC375" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD375" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD375" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
         <is>
-          <t>亚亚·图雷</t>
+          <t>埃兹里·孔萨</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>13274</v>
+        <v>4148</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Ezri Konsa</t>
+          <t>Yaya Touré</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Cote D’Ivoire</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>1997/10/23</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
-      <c r="H376" t="inlineStr"/>
+          <t>1983/5/13</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>3</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>2011–12, 2013–14, 2017–18</t>
+        </is>
+      </c>
       <c r="I376" t="inlineStr"/>
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr"/>
@@ -31589,7 +31609,7 @@
       <c r="P376" t="inlineStr"/>
       <c r="Q376" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="R376" t="n">
@@ -31597,7 +31617,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="T376" t="inlineStr"/>
@@ -31625,22 +31645,18 @@
       </c>
       <c r="AC376" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD376" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD376" t="inlineStr"/>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
         <is>
-          <t>埃兹里·孔萨</t>
+          <t>亚亚·图雷</t>
         </is>
       </c>
     </row>
@@ -32159,7 +32175,7 @@
       <c r="AD382" t="inlineStr"/>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>Queens Park Rangers;Newcastle United</t>
+          <t>Newcastle United;West Ham United;Queens Park Rangers</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -32209,7 +32225,7 @@
         </is>
       </c>
       <c r="R383" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="S383" t="inlineStr">
         <is>
@@ -32299,7 +32315,7 @@
         </is>
       </c>
       <c r="R384" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="S384" t="inlineStr">
         <is>
@@ -32339,7 +32355,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Aston Villa;Arsenal</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -33127,7 +33143,7 @@
         </is>
       </c>
       <c r="R393" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S393" t="inlineStr">
         <is>
@@ -33431,7 +33447,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday;Newcastle United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -34901,7 +34917,7 @@
       <c r="AD413" t="inlineStr"/>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>Watford;West Ham United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -34987,7 +35003,7 @@
       <c r="AD414" t="inlineStr"/>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>Wigan Athletic;West Bromwich Albion</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -35835,7 +35851,7 @@
         </is>
       </c>
       <c r="R424" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -36813,7 +36829,7 @@
         </is>
       </c>
       <c r="R435" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="S435" t="inlineStr">
         <is>
@@ -37525,7 +37541,7 @@
       <c r="AD444" t="inlineStr"/>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Manchester United;Newcastle United;Aston Villa</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -39067,10 +39083,14 @@
       <c r="AB464" t="inlineStr"/>
       <c r="AC464" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD464" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD464" t="inlineStr">
+        <is>
+          <t>Pogoń Szczecin</t>
+        </is>
+      </c>
       <c r="AE464" t="inlineStr">
         <is>
           <t>Manchester City</t>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         </is>
       </c>
       <c r="R168" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         </is>
       </c>
       <c r="R201" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         </is>
       </c>
       <c r="R321" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="S321" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         </is>
       </c>
       <c r="R351" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S351" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
       <c r="Z362" t="inlineStr"/>
       <c r="AA362" t="inlineStr"/>
       <c r="AB362" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AC362" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         </is>
       </c>
       <c r="R385" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="S385" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         </is>
       </c>
       <c r="R396" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="S396" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         </is>
       </c>
       <c r="R416" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="S416" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         </is>
       </c>
       <c r="R425" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S425" t="inlineStr">
         <is>

--- a/backend/data/premier_league_players_merged_final.xlsx
+++ b/backend/data/premier_league_players_merged_final.xlsx
@@ -2902,16 +2902,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1717</v>
+        <v>3955</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>John O'Shea</t>
+          <t>Kyle Walker</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2921,20 +2921,20 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1981/4/30</t>
+          <t>1990/5/28</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2002–03, 2006–07, 2007–08, 2008–09, 2010–11</t>
+          <t>2017–18, 2018–19, 2020–21, 2021–22, 2022–23, 2023–24</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -2947,11 +2947,11 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2960,11 +2960,11 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2987,33 +2987,37 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Burnley FC</t>
+        </is>
+      </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>Manchester United;Sunderland</t>
+          <t>Tottenham Hotspur;Aston Villa;Manchester City;Burnley</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>约翰·奥谢</t>
+          <t>凯尔·沃克</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3955</v>
+        <v>1717</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kyle Walker</t>
+          <t>John O'Shea</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3023,20 +3027,20 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1990/5/28</t>
+          <t>1981/4/30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2017–18, 2018–19, 2020–21, 2021–22, 2022–23, 2023–24</t>
+          <t>2002–03, 2006–07, 2007–08, 2008–09, 2010–11</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3049,11 +3053,11 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3062,11 +3066,11 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="U28" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -3085,26 +3089,22 @@
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>Burnley FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Aston Villa;Manchester City;Burnley</t>
+          <t>Manchester United;Sunderland</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>凯尔·沃克</t>
+          <t>约翰·奥谢</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -12530,11 +12530,11 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>8897</v>
+        <v>15202</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Aaron Cresswell</t>
+          <t>Declan Rice</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -12544,12 +12544,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>1989/12/15</t>
+          <t>1999/1/14</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="R138" t="n">
-        <v>312</v>
+        <v>204</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
       <c r="Z138" t="inlineStr"/>
       <c r="AA138" t="inlineStr"/>
       <c r="AB138" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
@@ -12606,17 +12606,17 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Arsenal FC</t>
         </is>
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Arsenal;West Ham United</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
         <is>
-          <t>阿隆·克雷斯韦尔</t>
+          <t>德克兰·赖斯</t>
         </is>
       </c>
     </row>
@@ -12706,11 +12706,11 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>544</v>
+        <v>8897</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ian Walker</t>
+          <t>Aaron Cresswell</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -12720,12 +12720,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>1971/10/31</t>
+          <t>1989/12/15</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -12741,11 +12741,11 @@
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="R140" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -12777,28 +12777,32 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Leicester City;Bolton Wanderers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
         <is>
-          <t>伊恩·沃克</t>
+          <t>阿隆·克雷斯韦尔</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>15202</v>
+        <v>544</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Declan Rice</t>
+          <t>Ian Walker</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -12808,12 +12812,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>1999/1/14</t>
+          <t>1971/10/31</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -12829,11 +12833,11 @@
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="R141" t="n">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -12865,22 +12869,18 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>Arsenal FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr"/>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>Arsenal;West Ham United</t>
+          <t>Tottenham Hotspur;Leicester City;Bolton Wanderers</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>德克兰·赖斯</t>
+          <t>伊恩·沃克</t>
         </is>
       </c>
     </row>
@@ -14516,31 +14516,41 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>4198</v>
+        <v>5067</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Craig Dawson</t>
+          <t>Bernardo Silva</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>1990/5/6</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
+          <t>1994/8/10</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>6</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2017–18, 2018–19, 2020–21, 2021–22, 2022–23, 2023–24</t>
+        </is>
+      </c>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
@@ -14549,15 +14559,37 @@
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="R161" t="n">
+        <v>303</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="T161" t="inlineStr"/>
-      <c r="U161" t="inlineStr"/>
-      <c r="V161" t="inlineStr"/>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W161" t="inlineStr"/>
-      <c r="X161" t="inlineStr"/>
-      <c r="Y161" t="inlineStr"/>
+      <c r="X161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z161" t="inlineStr"/>
       <c r="AA161" t="inlineStr"/>
       <c r="AB161" t="n">
@@ -14568,40 +14600,44 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AD161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>West Bromwich Albion;Watford;West Ham United;Wolverhampton Wanderers</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
         <is>
-          <t>克雷格·道森</t>
+          <t>贝尔纳多·席尔瓦</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1597</v>
+        <v>4198</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Nolberto Solano</t>
+          <t>Craig Dawson</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>1974/12/12</t>
+          <t>1990/5/6</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -14615,56 +14651,34 @@
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>Newcastle United</t>
-        </is>
-      </c>
-      <c r="R162" t="n">
-        <v>230</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
-      <c r="U162" t="n">
-        <v>0</v>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
       <c r="W162" t="inlineStr"/>
-      <c r="X162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X162" t="inlineStr"/>
+      <c r="Y162" t="inlineStr"/>
       <c r="Z162" t="inlineStr"/>
       <c r="AA162" t="inlineStr"/>
       <c r="AB162" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr"/>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>Newcastle United;Aston Villa;West Ham United</t>
+          <t>West Bromwich Albion;Watford;West Ham United;Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
         <is>
-          <t>诺尔伯托·索拉诺</t>
+          <t>克雷格·道森</t>
         </is>
       </c>
     </row>
@@ -14758,16 +14772,16 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>5067</v>
+        <v>1597</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Bernardo Silva</t>
+          <t>Nolberto Solano</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -14777,22 +14791,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1994/8/10</t>
-        </is>
-      </c>
-      <c r="F164" t="n">
-        <v>6</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>2017–18, 2018–19, 2020–21, 2021–22, 2022–23, 2023–24</t>
-        </is>
-      </c>
+          <t>1974/12/12</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
@@ -14803,15 +14807,15 @@
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="R164" t="n">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="T164" t="inlineStr"/>
@@ -14839,22 +14843,18 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr"/>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United;Aston Villa;West Ham United</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
         <is>
-          <t>贝尔纳多·席尔瓦</t>
+          <t>诺尔伯托·索拉诺</t>
         </is>
       </c>
     </row>
@@ -20862,26 +20862,26 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1168</v>
+        <v>24630</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Chris Powell</t>
+          <t>Richarlison</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>1969/9/8</t>
+          <t>1997/5/10</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -20895,37 +20895,15 @@
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="inlineStr">
-        <is>
-          <t>Charlton Athletic</t>
-        </is>
-      </c>
-      <c r="R241" t="n">
-        <v>187</v>
-      </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr"/>
+      <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr"/>
-      <c r="U241" t="n">
-        <v>0</v>
-      </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U241" t="inlineStr"/>
+      <c r="V241" t="inlineStr"/>
       <c r="W241" t="inlineStr"/>
-      <c r="X241" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X241" t="inlineStr"/>
+      <c r="Y241" t="inlineStr"/>
       <c r="Z241" t="inlineStr"/>
       <c r="AA241" t="inlineStr"/>
       <c r="AB241" t="n">
@@ -20933,43 +20911,47 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>Leicester City;Charlton Athletic</t>
+          <t>Tottenham Hotspur;Everton;Watford</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
         <is>
-          <t>克里斯·鲍威尔</t>
+          <t>理查利森</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>24630</v>
+        <v>1168</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Richarlison</t>
+          <t>Chris Powell</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>1997/5/10</t>
+          <t>1969/9/8</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -20983,38 +20965,56 @@
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr"/>
-      <c r="Q242" t="inlineStr"/>
-      <c r="R242" t="inlineStr"/>
-      <c r="S242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="R242" t="n">
+        <v>187</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T242" t="inlineStr"/>
-      <c r="U242" t="inlineStr"/>
-      <c r="V242" t="inlineStr"/>
+      <c r="U242" t="n">
+        <v>0</v>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W242" t="inlineStr"/>
-      <c r="X242" t="inlineStr"/>
-      <c r="Y242" t="inlineStr"/>
+      <c r="X242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z242" t="inlineStr"/>
       <c r="AA242" t="inlineStr"/>
       <c r="AB242" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD242" t="inlineStr">
-        <is>
-          <t>Tottenham Hotspur</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr"/>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur;Everton;Watford</t>
+          <t>Leicester City;Charlton Athletic</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
         <is>
-          <t>理查利森</t>
+          <t>克里斯·鲍威尔</t>
         </is>
       </c>
     </row>
@@ -24992,11 +24992,11 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>3</v>
+        <v>3512</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Tony Adams</t>
+          <t>Adam Smith</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>1966/10/10</t>
+          <t>1991/4/29</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
@@ -25023,19 +25023,15 @@
       <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr"/>
       <c r="N292" t="inlineStr"/>
-      <c r="O292" t="inlineStr">
-        <is>
-          <t>Premier League 10 Seasons Awards</t>
-        </is>
-      </c>
+      <c r="O292" t="inlineStr"/>
       <c r="P292" t="inlineStr"/>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="R292" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="S292" t="inlineStr">
         <is>
@@ -25067,83 +25063,71 @@
       </c>
       <c r="AC292" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD292" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD292" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth</t>
+        </is>
+      </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth;Tottenham Hotspur</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
         <is>
-          <t>托尼·亚当斯</t>
+          <t>亚当·史密斯</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>2662</v>
+        <v>3</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Didier Drogba</t>
+          <t>Tony Adams</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Cote D’Ivoire</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>1978/3/11</t>
-        </is>
-      </c>
-      <c r="F293" t="n">
-        <v>4</v>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>2004–05, 2005–06, 2009–10, 2014–15</t>
-        </is>
-      </c>
-      <c r="I293" t="n">
-        <v>104</v>
-      </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>2006, 2009</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>20.0, 29.0</t>
-        </is>
-      </c>
+          <t>1966/10/10</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr"/>
-      <c r="O293" t="inlineStr"/>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>Premier League 10 Seasons Awards</t>
+        </is>
+      </c>
       <c r="P293" t="inlineStr"/>
       <c r="Q293" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="R293" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="S293" t="inlineStr">
         <is>
@@ -25168,18 +25152,10 @@
           <t>no</t>
         </is>
       </c>
-      <c r="Z293" t="inlineStr">
-        <is>
-          <t>2006, 2009</t>
-        </is>
-      </c>
-      <c r="AA293" t="inlineStr">
-        <is>
-          <t>20.0, 29.0</t>
-        </is>
-      </c>
+      <c r="Z293" t="inlineStr"/>
+      <c r="AA293" t="inlineStr"/>
       <c r="AB293" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AC293" t="inlineStr">
         <is>
@@ -25189,37 +25165,37 @@
       <c r="AD293" t="inlineStr"/>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
         <is>
-          <t>迪迪埃·德罗巴</t>
+          <t>托尼·亚当斯</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>5272</v>
+        <v>20559</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Pierre-Emile Højbjerg</t>
+          <t>Alisson Becker</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>1995/8/5</t>
+          <t>1992/10/2</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -25228,20 +25204,48 @@
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>20.0, 21.0</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr"/>
       <c r="N294" t="inlineStr"/>
       <c r="O294" t="inlineStr"/>
-      <c r="P294" t="inlineStr"/>
-      <c r="Q294" t="inlineStr"/>
-      <c r="R294" t="inlineStr"/>
-      <c r="S294" t="inlineStr"/>
+      <c r="P294" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="R294" t="n">
+        <v>254</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T294" t="inlineStr"/>
-      <c r="U294" t="inlineStr"/>
-      <c r="V294" t="inlineStr"/>
+      <c r="U294" t="n">
+        <v>0</v>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W294" t="inlineStr"/>
-      <c r="X294" t="inlineStr"/>
-      <c r="Y294" t="inlineStr"/>
+      <c r="X294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z294" t="inlineStr"/>
       <c r="AA294" t="inlineStr"/>
       <c r="AB294" t="n">
@@ -25254,42 +25258,42 @@
       </c>
       <c r="AD294" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>Southampton;Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
         <is>
-          <t>皮埃尔-埃米尔·霍伊别尔</t>
+          <t>阿利松·贝克尔</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>3512</v>
+        <v>5272</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Adam Smith</t>
+          <t>Pierre-Emile Højbjerg</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>1991/4/29</t>
+          <t>1995/8/5</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -25303,37 +25307,15 @@
       <c r="N295" t="inlineStr"/>
       <c r="O295" t="inlineStr"/>
       <c r="P295" t="inlineStr"/>
-      <c r="Q295" t="inlineStr">
-        <is>
-          <t>Bournemouth</t>
-        </is>
-      </c>
-      <c r="R295" t="n">
-        <v>253</v>
-      </c>
-      <c r="S295" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q295" t="inlineStr"/>
+      <c r="R295" t="inlineStr"/>
+      <c r="S295" t="inlineStr"/>
       <c r="T295" t="inlineStr"/>
-      <c r="U295" t="n">
-        <v>0</v>
-      </c>
-      <c r="V295" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U295" t="inlineStr"/>
+      <c r="V295" t="inlineStr"/>
       <c r="W295" t="inlineStr"/>
-      <c r="X295" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y295" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X295" t="inlineStr"/>
+      <c r="Y295" t="inlineStr"/>
       <c r="Z295" t="inlineStr"/>
       <c r="AA295" t="inlineStr"/>
       <c r="AB295" t="n">
@@ -25346,64 +25328,78 @@
       </c>
       <c r="AD295" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>Bournemouth;Tottenham Hotspur</t>
+          <t>Southampton;Tottenham Hotspur</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
         <is>
-          <t>亚当·史密斯</t>
+          <t>皮埃尔-埃米尔·霍伊别尔</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>20559</v>
+        <v>2662</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Alisson Becker</t>
+          <t>Didier Drogba</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Cote D’Ivoire</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>1992/10/2</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="inlineStr"/>
-      <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t>20.0, 21.0</t>
-        </is>
-      </c>
+          <t>1978/3/11</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>4</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>2004–05, 2005–06, 2009–10, 2014–15</t>
+        </is>
+      </c>
+      <c r="I296" t="n">
+        <v>104</v>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>2006, 2009</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>20.0, 29.0</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr"/>
       <c r="N296" t="inlineStr"/>
       <c r="O296" t="inlineStr"/>
-      <c r="P296" t="n">
-        <v>106</v>
-      </c>
+      <c r="P296" t="inlineStr"/>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="R296" t="n">
@@ -25432,29 +25428,33 @@
           <t>no</t>
         </is>
       </c>
-      <c r="Z296" t="inlineStr"/>
-      <c r="AA296" t="inlineStr"/>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>2006, 2009</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>20.0, 29.0</t>
+        </is>
+      </c>
       <c r="AB296" t="n">
         <v>254</v>
       </c>
       <c r="AC296" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD296" t="inlineStr">
-        <is>
-          <t>Liverpool FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD296" t="inlineStr"/>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
         <is>
-          <t>阿利松·贝克尔</t>
+          <t>迪迪埃·德罗巴</t>
         </is>
       </c>
     </row>
@@ -29224,26 +29224,26 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>3982</v>
+        <v>20486</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Mohamed Diamé</t>
+          <t>Leandro Trossard</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>1987/6/14</t>
+          <t>1994/12/4</t>
         </is>
       </c>
       <c r="F346" t="inlineStr"/>
@@ -29273,33 +29273,37 @@
       </c>
       <c r="AC346" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AD346" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AD346" t="inlineStr">
+        <is>
+          <t>Arsenal FC</t>
+        </is>
+      </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>Wigan Athletic;West Ham United;Hull City;Newcastle United</t>
+          <t>Arsenal;Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
         <is>
-          <t>穆罕默德·迪亚梅</t>
+          <t>利安德罗·特罗萨德</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>329</v>
+        <v>3982</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Keith Gillespie</t>
+          <t>Mohamed Diamé</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Northern Ireland</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -29309,7 +29313,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>1975/2/18</t>
+          <t>1987/6/14</t>
         </is>
       </c>
       <c r="F347" t="inlineStr"/>
@@ -29335,7 +29339,7 @@
       <c r="Z347" t="inlineStr"/>
       <c r="AA347" t="inlineStr"/>
       <c r="AB347" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AC347" t="inlineStr">
         <is>
@@ -29345,37 +29349,37 @@
       <c r="AD347" t="inlineStr"/>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>Manchester United;Newcastle United;Blackburn Rovers;Leicester City;Sheffield United</t>
+          <t>Wigan Athletic;West Ham United;Hull City;Newcastle United</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
         <is>
-          <t>基思·吉莱斯皮</t>
+          <t>穆罕默德·迪亚梅</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>3394</v>
+        <v>329</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Brede Hangeland</t>
+          <t>Keith Gillespie</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Northern Ireland</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>1981/6/20</t>
+          <t>1975/2/18</t>
         </is>
       </c>
       <c r="F348" t="inlineStr"/>
@@ -29389,37 +29393,15 @@
       <c r="N348" t="inlineStr"/>
       <c r="O348" t="inlineStr"/>
       <c r="P348" t="inlineStr"/>
-      <c r="Q348" t="inlineStr">
-        <is>
-          <t>Fulham</t>
-        </is>
-      </c>
-      <c r="R348" t="n">
-        <v>217</v>
-      </c>
-      <c r="S348" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="Q348" t="inlineStr"/>
+      <c r="R348" t="inlineStr"/>
+      <c r="S348" t="inlineStr"/>
       <c r="T348" t="inlineStr"/>
-      <c r="U348" t="n">
-        <v>0</v>
-      </c>
-      <c r="V348" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="U348" t="inlineStr"/>
+      <c r="V348" t="inlineStr"/>
       <c r="W348" t="inlineStr"/>
-      <c r="X348" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y348" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="X348" t="inlineStr"/>
+      <c r="Y348" t="inlineStr"/>
       <c r="Z348" t="inlineStr"/>
       <c r="AA348" t="inlineStr"/>
       <c r="AB348" t="n">
@@ -29433,12 +29415,12 @@
       <c r="AD348" t="inlineStr"/>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Manchester United;Newcastle United;Blackburn Rovers;Leicester City;Sheffield United</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
         <is>
-          <t>布雷德·汉格兰</t>
+          <t>基思·吉莱斯皮</t>
         </is>
       </c>
     </row>
@@ -29510,26 +29492,26 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>20486</v>
+        <v>3394</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Leandro Trossard</t>
+          <t>Brede Hangeland</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>1994/12/4</t>
+          <t>1981/6/20</t>
         </is>
       </c>
       <c r="F350" t="inlineStr"/>
@@ -29543,15 +29525,37 @@
       <c r="N350" t="inlineStr"/>
       <c r="O350" t="inlineStr"/>
       <c r="P350" t="inlineStr"/>
-      <c r="Q350" t="inlineStr"/>
-      <c r="R350" t="inlineStr"/>
-      <c r="S350" t="inlineStr"/>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="R350" t="n">
+        <v>217</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T350" t="inlineStr"/>
-      <c r="U350" t="inlineStr"/>
-      <c r="V350" t="inlineStr"/>
+      <c r="U350" t="n">
+        <v>0</v>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="W350" t="inlineStr"/>
-      <c r="X350" t="inlineStr"/>
-      <c r="Y350" t="inlineStr"/>
+      <c r="X350" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Z350" t="inlineStr"/>
       <c r="AA350" t="inlineStr"/>
       <c r="AB350" t="n">
@@ -29559,22 +29563,18 @@
       </c>
       <c r="AC350" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AD350" t="inlineStr">
-        <is>
-          <t>Arsenal FC</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AD350" t="inlineStr"/>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>Arsenal;Brighton &amp; Hove Albion</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
         <is>
-          <t>利安德罗·特罗萨德</t>
+          <t>布雷德·汉格兰</t>
         </is>
       </c>
     </row>
@@ -32581,7 +32581,7 @@
         </is>
       </c>
       <c r="R387" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="S387" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         </is>
       </c>
       <c r="R390" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S390" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         </is>
       </c>
       <c r="R422" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="S422" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         </is>
       </c>
       <c r="R427" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S427" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         </is>
       </c>
       <c r="R428" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         </is>
       </c>
       <c r="R431" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="S431" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
       <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr">
         <is>
-          <t>13.0, 16.0</t>
+          <t>13.0, 16.0, 20.0</t>
         </is>
       </c>
       <c r="M439" t="inlineStr"/>
